--- a/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
+++ b/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>START HERE. Total CAPEX, Year-1 OPEX, and the peak cash the business actually needs to fund — tied against the AED 2,000,000 shareholder capital.</t>
+          <t>START HERE. Total CAPEX, Year-1 OPEX, and the peak cash the business actually needs to fund — tied against the AED 200,000 shareholder capital.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
+    <row r="30" ht="39" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>•</t>
@@ -1072,168 +1072,180 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>The AED 2,000,000 shareholder capital is NOT used as a target or a cap. Everything here is built bottom-up from what the business needs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+          <t>Shareholder capital is AED 200,000 as confirmed. NOTE: the Business Profile states AED 2,000,000 — the two must be reconciled before the pack goes to the bank. This model uses AED 200,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Nothing here is sized to the capital figure. Everything is built bottom-up from what the business needs, then compared against the capital available on 'Funding Summary'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>COLOUR LEGEND</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Hardcoded input — edit freely.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Yellow fill</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Key lever, or a figure you supplied.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Formula. Do not overwrite.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Link to another tab in this workbook.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>WHAT IS DELIBERATELY EXCLUDED</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="39" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="39" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>OTA commission (Airbnb / Booking.com, 15–18%). Under a commission-only model this is deducted from gross booking revenue before the owner's split — it is not an Orizuru operating cost. Add it only if your management contracts make Orizuru bear it.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Tourism Dirham. Collected from the guest, remitted to DET. Pure pass-through.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Corporate Tax itself (9% above AED 375,000 taxable profit) — a tax on profit, not OPEX. The compliance and filing cost IS included.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Depreciation on the CAPEX. Non-cash; belongs in the P&amp;L, not an OPEX cash budget.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Unit furnishing. Owner-funded under this model. The operating layer Orizuru does fund is in CAPEX.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Bank minimum balance. A blocked asset, not a cost — shown as a memo on 'CAPEX Detail'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A4:F4"/>
@@ -1241,21 +1253,22 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B41:F41"/>
@@ -1682,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2105,12 +2118,12 @@
       </c>
       <c r="B29" s="17" t="n"/>
       <c r="C29" s="28" t="n">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="D29" s="17" t="n"/>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>Per the Business Profile — AED 2,000,000, funded by shareholders.</t>
+          <t>AED 200,000 as confirmed. The Business Profile states AED 2,000,000 — reconcile before submission.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2141,7 @@
       <c r="D30" s="30" t="n"/>
       <c r="E30" s="32" t="inlineStr">
         <is>
-          <t>Positive means the shareholder capital covers Year 1 with room to spare — that surplus is what funds portfolio expansion and Year-2 runway.</t>
+          <t>Negative means the ramp above cannot be funded from AED 200,000. Fix it by slowing the unit ramp, taking the Low CAPEX case, or re-charging unit-level OPEX to owners — see note 6 below.</t>
         </is>
       </c>
     </row>
@@ -2178,14 +2191,30 @@
         </is>
       </c>
     </row>
+    <row r="38" ht="86" customHeight="1">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>•  AT AED 200,000 THE BASE CASE DOES NOT FUND ITSELF. Base CAPEX (121,158) plus the peak operating cash deficit (76,726) plus a 20% buffer comes to 237,461 against 200,000 available — a shortfall of about 37,000. Two levers close it: (a) take the Low CAPEX case, deferring the full website build and brand spend until cash turns positive, which alone gets you to roughly 20,000 of headroom; (b) re-charge unit-level OPEX (housekeeping, DET permit renewals, consumables) to owners and guests, which is standard Dubai practice. Doing both leaves about 38,000 of headroom and is the recommended path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>•  DO NOT TRY TO FIX IT BY SLOWING THE RAMP. This is counter-intuitive but the model is unambiguous: cutting the ramp from 80 units to 46 by Month 12 makes the peak cash deficit WORSE, not better (119,632 vs 76,726). Fixed OPEX — office, licence, staff, technology — runs regardless, so a slower ramp simply means paying it for longer before revenue catches up. If capital is tight, cut CAPEX and re-charge OPEX; do not cut growth.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A38:E38"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
@@ -4472,10 +4501,10 @@
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16" ht="47" customHeight="1">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>•  The Business Profile states AED 2,000,000 of shareholder capital. Per HJ this CAPEX is NOT sized to that number — it is built bottom-up from what the business needs, and the balance is available as working capital and runway.</t>
+          <t>•  Shareholder capital is AED 200,000 as confirmed. The Business Profile states AED 2,000,000 — reconcile the two before submission. This CAPEX is not sized to either figure; it is built bottom-up from what the business needs. At AED 200,000, CAPEX alone consumes a significant share of the capital — see 'Funding Summary'.</t>
         </is>
       </c>
     </row>

--- a/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
+++ b/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
@@ -1393,11 +1393,11 @@
       </c>
       <c r="E7" s="22">
         <f>C7*D7*$B$4</f>
-        <v/>
+        <v>367.25</v>
       </c>
       <c r="F7" s="22">
         <f>E7*12</f>
-        <v/>
+        <v>4407</v>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
@@ -1424,11 +1424,11 @@
       </c>
       <c r="E8" s="22">
         <f>C8*D8*$B$4</f>
-        <v/>
+        <v>146.9</v>
       </c>
       <c r="F8" s="22">
         <f>E8*12</f>
-        <v/>
+        <v>1762.8000000000002</v>
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
@@ -1455,11 +1455,11 @@
       </c>
       <c r="E9" s="22">
         <f>C9*D9*$B$4</f>
-        <v/>
+        <v>183.625</v>
       </c>
       <c r="F9" s="22">
         <f>E9*12</f>
-        <v/>
+        <v>2203.5</v>
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="E10" s="22">
         <f>C10*D10*$B$4</f>
-        <v/>
+        <v>146.9</v>
       </c>
       <c r="F10" s="22">
         <f>E10*12</f>
-        <v/>
+        <v>1762.8000000000002</v>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
@@ -1517,11 +1517,11 @@
       </c>
       <c r="E11" s="22">
         <f>C11*D11*$B$4</f>
-        <v/>
+        <v>73.45</v>
       </c>
       <c r="F11" s="22">
         <f>E11*12</f>
-        <v/>
+        <v>881.4000000000001</v>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
@@ -1548,11 +1548,11 @@
       </c>
       <c r="E12" s="22">
         <f>C12*D12*$B$4</f>
-        <v/>
+        <v>110.175</v>
       </c>
       <c r="F12" s="22">
         <f>E12*12</f>
-        <v/>
+        <v>1322.1</v>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
@@ -1579,11 +1579,11 @@
       </c>
       <c r="E13" s="22">
         <f>C13*D13*$B$4</f>
-        <v/>
+        <v>179.9525</v>
       </c>
       <c r="F13" s="22">
         <f>E13*12</f>
-        <v/>
+        <v>2159.43</v>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
@@ -1610,11 +1610,11 @@
       </c>
       <c r="E14" s="22">
         <f>C14*D14*$B$4</f>
-        <v/>
+        <v>66.105</v>
       </c>
       <c r="F14" s="22">
         <f>E14*12</f>
-        <v/>
+        <v>793.26</v>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="E15" s="22">
         <f>C15*D15*$B$4</f>
-        <v/>
+        <v>44.07</v>
       </c>
       <c r="F15" s="22">
         <f>E15*12</f>
-        <v/>
+        <v>528.84</v>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
@@ -1664,11 +1664,11 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="19">
         <f>SUM(E7:E15)</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="F16" s="19">
         <f>SUM(F7:F15)</f>
-        <v/>
+        <v>15821.130000000001</v>
       </c>
       <c r="G16" s="5" t="n"/>
     </row>
@@ -1773,15 +1773,15 @@
       </c>
       <c r="B6" s="15">
         <f>'CAPEX Detail'!G50</f>
-        <v/>
+        <v>60824</v>
       </c>
       <c r="C6" s="15">
         <f>'CAPEX Detail'!H50</f>
-        <v/>
+        <v>101824</v>
       </c>
       <c r="D6" s="15">
         <f>'CAPEX Detail'!I50</f>
-        <v/>
+        <v>166324</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -1797,15 +1797,15 @@
       </c>
       <c r="B7" s="15">
         <f>'Unit Setup (1 Unit)'!D17</f>
-        <v/>
+        <v>6105</v>
       </c>
       <c r="C7" s="15">
         <f>'Unit Setup (1 Unit)'!E17</f>
-        <v/>
+        <v>9152</v>
       </c>
       <c r="D7" s="15">
         <f>'Unit Setup (1 Unit)'!F17</f>
-        <v/>
+        <v>13640</v>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
@@ -1821,15 +1821,15 @@
       </c>
       <c r="B8" s="15">
         <f>'CAPEX Detail'!G52</f>
-        <v/>
+        <v>6082.400000000001</v>
       </c>
       <c r="C8" s="15">
         <f>'CAPEX Detail'!H52</f>
-        <v/>
+        <v>10182.400000000001</v>
       </c>
       <c r="D8" s="15">
         <f>'CAPEX Detail'!I52</f>
-        <v/>
+        <v>16632.4</v>
       </c>
       <c r="E8" s="17" t="n"/>
     </row>
@@ -1841,15 +1841,15 @@
       </c>
       <c r="B9" s="19">
         <f>SUM(B6:B8)</f>
-        <v/>
+        <v>73011.4</v>
       </c>
       <c r="C9" s="19">
         <f>SUM(C6:C8)</f>
-        <v/>
+        <v>121158.4</v>
       </c>
       <c r="D9" s="19">
         <f>SUM(D6:D8)</f>
-        <v/>
+        <v>196596.4</v>
       </c>
       <c r="E9" s="5" t="n"/>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="15">
         <f>'OPEX Summary'!B14</f>
-        <v/>
+        <v>691253.3145</v>
       </c>
       <c r="D12" s="17" t="n"/>
       <c r="E12" s="21" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="B13" s="17" t="n"/>
       <c r="C13" s="22">
         <f>C12/12</f>
-        <v/>
+        <v>57604.442875</v>
       </c>
       <c r="D13" s="17" t="n"/>
       <c r="E13" s="21" t="inlineStr">
@@ -1909,7 +1909,7 @@
       <c r="B14" s="17" t="n"/>
       <c r="C14" s="15">
         <f>'OPEX Monthly'!N86</f>
-        <v/>
+        <v>105622.916875</v>
       </c>
       <c r="D14" s="17" t="n"/>
       <c r="E14" s="21" t="inlineStr">
@@ -1938,7 +1938,7 @@
       <c r="B17" s="17" t="n"/>
       <c r="C17" s="24">
         <f>'OPEX Monthly'!N8</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="D17" s="17" t="n"/>
       <c r="E17" s="21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="15">
         <f>'OPEX Monthly'!O10</f>
-        <v/>
+        <v>3755160</v>
       </c>
       <c r="D18" s="17" t="n"/>
       <c r="E18" s="21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="15">
         <f>'OPEX Monthly'!O11</f>
-        <v/>
+        <v>751032</v>
       </c>
       <c r="D19" s="17" t="n"/>
       <c r="E19" s="21" t="inlineStr">
@@ -1992,7 +1992,7 @@
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="22">
         <f>C12</f>
-        <v/>
+        <v>691253.3145</v>
       </c>
       <c r="D20" s="17" t="n"/>
       <c r="E20" s="21" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="25">
         <f>C19-C20</f>
-        <v/>
+        <v>59778.68550000002</v>
       </c>
       <c r="D21" s="17" t="n"/>
       <c r="E21" s="21" t="inlineStr">
@@ -2024,7 +2024,7 @@
       <c r="B22" s="17" t="n"/>
       <c r="C22" s="26">
         <f>IF(C19=0,0,C20/C19)</f>
-        <v/>
+        <v>0.9204046092576614</v>
       </c>
       <c r="D22" s="17" t="n"/>
       <c r="E22" s="21" t="inlineStr">
@@ -2053,7 +2053,7 @@
       <c r="B25" s="17" t="n"/>
       <c r="C25" s="15">
         <f>MIN(0,MIN('OPEX Monthly'!C92:N92))</f>
-        <v/>
+        <v>-76726.00524999999</v>
       </c>
       <c r="D25" s="17" t="n"/>
       <c r="E25" s="21" t="inlineStr">
@@ -2071,7 +2071,7 @@
       <c r="B26" s="17" t="n"/>
       <c r="C26" s="22">
         <f>C9</f>
-        <v/>
+        <v>121158.4</v>
       </c>
       <c r="D26" s="17" t="n"/>
       <c r="E26" s="17" t="n"/>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C27" s="22">
         <f>(ABS(C25)+C26)*B27</f>
-        <v/>
+        <v>39576.881049999996</v>
       </c>
       <c r="D27" s="17" t="n"/>
       <c r="E27" s="16" t="inlineStr">
@@ -2105,7 +2105,7 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="19">
         <f>ABS(C25)+C26+C27</f>
-        <v/>
+        <v>237461.28629999998</v>
       </c>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
@@ -2136,7 +2136,7 @@
       <c r="B30" s="30" t="n"/>
       <c r="C30" s="31">
         <f>C29-C28</f>
-        <v/>
+        <v>-37461.28629999998</v>
       </c>
       <c r="D30" s="30" t="n"/>
       <c r="E30" s="32" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B5" s="38">
         <f>MATCH($B$4,$J$4:$J$6,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J5" s="37" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="F11" s="44">
         <f>INDEX(C11:E11,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>450</v>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F12" s="46">
         <f>INDEX(C12:E12,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="F13" s="48">
         <f>INDEX(C13:E13,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>30.4</v>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
@@ -2498,19 +2498,19 @@
       </c>
       <c r="C14" s="22">
         <f>C11*C12*C13</f>
-        <v/>
+        <v>7508.799999999999</v>
       </c>
       <c r="D14" s="22">
         <f>D11*D12*D13</f>
-        <v/>
+        <v>10260</v>
       </c>
       <c r="E14" s="22">
         <f>E11*E12*E13</f>
-        <v/>
+        <v>13710.4</v>
       </c>
       <c r="F14" s="44">
         <f>INDEX(C14:E14,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>10260</v>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F15" s="46">
         <f>INDEX(C15:E15,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
@@ -2561,19 +2561,19 @@
       </c>
       <c r="C16" s="22">
         <f>C14*C15</f>
-        <v/>
+        <v>1126.32</v>
       </c>
       <c r="D16" s="22">
         <f>D14*D15</f>
-        <v/>
+        <v>2052</v>
       </c>
       <c r="E16" s="22">
         <f>E14*E15</f>
-        <v/>
+        <v>3427.6</v>
       </c>
       <c r="F16" s="44">
         <f>INDEX(C16:E16,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>2052</v>
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F18" s="44">
         <f>INDEX(C18:E18,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F19" s="50">
         <f>INDEX(C19:E19,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F20" s="44">
         <f>INDEX(C20:E20,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F21" s="44">
         <f>INDEX(C21:E21,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="F22" s="52">
         <f>INDEX(C22:E22,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>0.058</v>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F23" s="44">
         <f>INDEX(C23:E23,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="F25" s="50">
         <f>INDEX(C25:E25,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F26" s="44">
         <f>INDEX(C26:E26,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="F27" s="44">
         <f>INDEX(C27:E27,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F28" s="44">
         <f>INDEX(C28:E28,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="F29" s="44">
         <f>INDEX(C29:E29,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="F31" s="50">
         <f>INDEX(C31:E31,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G31" s="21" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F32" s="44">
         <f>INDEX(C32:E32,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>240</v>
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="F33" s="44">
         <f>INDEX(C33:E33,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="F34" s="44">
         <f>INDEX(C34:E34,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="F35" s="44">
         <f>INDEX(C35:E35,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F36" s="44">
         <f>INDEX(C36:E36,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="F37" s="44">
         <f>INDEX(C37:E37,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F39" s="52">
         <f>INDEX(C39:E39,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F40" s="50">
         <f>INDEX(C40:E40,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="F42" s="44">
         <f>INDEX(C42:E42,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="F43" s="44">
         <f>INDEX(C43:E43,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="F44" s="44">
         <f>INDEX(C44:E44,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -3352,14 +3352,14 @@
       </c>
       <c r="D45" s="15">
         <f>'AI Subscriptions'!E16</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="E45" s="28" t="n">
         <v>3200</v>
       </c>
       <c r="F45" s="44">
         <f>INDEX(C45:E45,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F46" s="44">
         <f>INDEX(C46:E46,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="F47" s="44">
         <f>INDEX(C47:E47,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="F48" s="44">
         <f>INDEX(C48:E48,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F49" s="44">
         <f>INDEX(C49:E49,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="G49" s="21" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F51" s="44">
         <f>INDEX(C51:E51,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>1520</v>
       </c>
       <c r="G51" s="21" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="F52" s="44">
         <f>INDEX(C52:E52,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="G52" s="21" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F53" s="44">
         <f>INDEX(C53:E53,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="G53" s="21" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F54" s="44">
         <f>INDEX(C54:E54,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="G54" s="21" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="F55" s="44">
         <f>INDEX(C55:E55,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="G55" s="21" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F57" s="44">
         <f>INDEX(C57:E57,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="G57" s="21" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F58" s="44">
         <f>INDEX(C58:E58,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="G58" s="21" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="F59" s="44">
         <f>INDEX(C59:E59,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="G59" s="21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F60" s="44">
         <f>INDEX(C60:E60,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="G60" s="21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F61" s="44">
         <f>INDEX(C61:E61,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="G61" s="21" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="F62" s="44">
         <f>INDEX(C62:E62,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="G62" s="21" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="F63" s="52">
         <f>INDEX(C63:E63,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>0.026</v>
       </c>
       <c r="G63" s="21" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F65" s="44">
         <f>INDEX(C65:E65,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G65" s="21" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F66" s="44">
         <f>INDEX(C66:E66,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="G66" s="21" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F67" s="44">
         <f>INDEX(C67:E67,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="G67" s="21" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F68" s="44">
         <f>INDEX(C68:E68,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="G68" s="21" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F69" s="44">
         <f>INDEX(C69:E69,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="G69" s="21" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F70" s="44">
         <f>INDEX(C70:E70,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>19000</v>
       </c>
       <c r="G70" s="21" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="F71" s="44">
         <f>INDEX(C71:E71,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>5500</v>
       </c>
       <c r="G71" s="21" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="F72" s="44">
         <f>INDEX(C72:E72,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="G72" s="21" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F74" s="46">
         <f>INDEX(C74:E74,1,Assumptions!$B$5)</f>
-        <v/>
+        <v>0.05</v>
       </c>
       <c r="G74" s="21" t="inlineStr">
         <is>
@@ -4277,19 +4277,19 @@
       </c>
       <c r="B5" s="15">
         <f>'CAPEX Detail'!G45</f>
-        <v/>
+        <v>29437</v>
       </c>
       <c r="C5" s="15">
         <f>'CAPEX Detail'!H45</f>
-        <v/>
+        <v>45337</v>
       </c>
       <c r="D5" s="15">
         <f>'CAPEX Detail'!I45</f>
-        <v/>
+        <v>62837</v>
       </c>
       <c r="E5" s="54">
         <f>IF($C$12=0,0,C5/$C$12)</f>
-        <v/>
+        <v>0.37419609370873175</v>
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
@@ -4305,19 +4305,19 @@
       </c>
       <c r="B6" s="15">
         <f>'CAPEX Detail'!G46</f>
-        <v/>
+        <v>10287</v>
       </c>
       <c r="C6" s="15">
         <f>'CAPEX Detail'!H46</f>
-        <v/>
+        <v>19787</v>
       </c>
       <c r="D6" s="15">
         <f>'CAPEX Detail'!I46</f>
-        <v/>
+        <v>37887</v>
       </c>
       <c r="E6" s="54">
         <f>IF($C$12=0,0,C6/$C$12)</f>
-        <v/>
+        <v>0.16331513126617717</v>
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -4333,19 +4333,19 @@
       </c>
       <c r="B7" s="15">
         <f>'CAPEX Detail'!G47</f>
-        <v/>
+        <v>6200</v>
       </c>
       <c r="C7" s="15">
         <f>'CAPEX Detail'!H47</f>
-        <v/>
+        <v>11900</v>
       </c>
       <c r="D7" s="15">
         <f>'CAPEX Detail'!I47</f>
-        <v/>
+        <v>23800</v>
       </c>
       <c r="E7" s="54">
         <f>IF($C$12=0,0,C7/$C$12)</f>
-        <v/>
+        <v>0.09821853045269664</v>
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
@@ -4361,19 +4361,19 @@
       </c>
       <c r="B8" s="15">
         <f>'CAPEX Detail'!G48</f>
-        <v/>
+        <v>9900</v>
       </c>
       <c r="C8" s="15">
         <f>'CAPEX Detail'!H48</f>
-        <v/>
+        <v>15000</v>
       </c>
       <c r="D8" s="15">
         <f>'CAPEX Detail'!I48</f>
-        <v/>
+        <v>24300</v>
       </c>
       <c r="E8" s="54">
         <f>IF($C$12=0,0,C8/$C$12)</f>
-        <v/>
+        <v>0.12380487031852518</v>
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -4389,19 +4389,19 @@
       </c>
       <c r="B9" s="15">
         <f>'CAPEX Detail'!G49</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="C9" s="15">
         <f>'CAPEX Detail'!H49</f>
-        <v/>
+        <v>9800</v>
       </c>
       <c r="D9" s="15">
         <f>'CAPEX Detail'!I49</f>
-        <v/>
+        <v>17500</v>
       </c>
       <c r="E9" s="54">
         <f>IF($C$12=0,0,C9/$C$12)</f>
-        <v/>
+        <v>0.08088584860810312</v>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
@@ -4417,19 +4417,19 @@
       </c>
       <c r="B10" s="15">
         <f>'CAPEX Detail'!G51</f>
-        <v/>
+        <v>6105</v>
       </c>
       <c r="C10" s="15">
         <f>'CAPEX Detail'!H51</f>
-        <v/>
+        <v>9152</v>
       </c>
       <c r="D10" s="15">
         <f>'CAPEX Detail'!I51</f>
-        <v/>
+        <v>13640</v>
       </c>
       <c r="E10" s="54">
         <f>IF($C$12=0,0,C10/$C$12)</f>
-        <v/>
+        <v>0.07553747821034283</v>
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -4445,19 +4445,19 @@
       </c>
       <c r="B11" s="15">
         <f>'CAPEX Detail'!G52</f>
-        <v/>
+        <v>6082.400000000001</v>
       </c>
       <c r="C11" s="15">
         <f>'CAPEX Detail'!H52</f>
-        <v/>
+        <v>10182.400000000001</v>
       </c>
       <c r="D11" s="15">
         <f>'CAPEX Detail'!I52</f>
-        <v/>
+        <v>16632.4</v>
       </c>
       <c r="E11" s="54">
         <f>IF($C$12=0,0,C11/$C$12)</f>
-        <v/>
+        <v>0.0840420474354234</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -4473,19 +4473,19 @@
       </c>
       <c r="B12" s="19">
         <f>SUM(B5:B11)</f>
-        <v/>
+        <v>73011.4</v>
       </c>
       <c r="C12" s="19">
         <f>SUM(C5:C11)</f>
-        <v/>
+        <v>121158.4</v>
       </c>
       <c r="D12" s="19">
         <f>SUM(D5:D11)</f>
-        <v/>
+        <v>196596.4</v>
       </c>
       <c r="E12" s="55">
         <f>IF($C$12=0,0,SUM(E5:E11))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F12" s="5" t="n"/>
     </row>
@@ -4696,15 +4696,15 @@
       </c>
       <c r="G6" s="22">
         <f>$C6*D6</f>
-        <v/>
+        <v>13500</v>
       </c>
       <c r="H6" s="22">
         <f>$C6*E6</f>
-        <v/>
+        <v>17500</v>
       </c>
       <c r="I6" s="22">
         <f>$C6*F6</f>
-        <v/>
+        <v>22000</v>
       </c>
       <c r="J6" s="57" t="inlineStr">
         <is>
@@ -4742,15 +4742,15 @@
       </c>
       <c r="G7" s="22">
         <f>$C7*D7</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="H7" s="22">
         <f>$C7*E7</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="I7" s="22">
         <f>$C7*F7</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="J7" s="57" t="inlineStr">
         <is>
@@ -4788,15 +4788,15 @@
       </c>
       <c r="G8" s="22">
         <f>$C8*D8</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="H8" s="22">
         <f>$C8*E8</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="I8" s="22">
         <f>$C8*F8</f>
-        <v/>
+        <v>3500</v>
       </c>
       <c r="J8" s="57" t="inlineStr">
         <is>
@@ -4834,15 +4834,15 @@
       </c>
       <c r="G9" s="22">
         <f>$C9*D9</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="H9" s="22">
         <f>$C9*E9</f>
-        <v/>
+        <v>2200</v>
       </c>
       <c r="I9" s="22">
         <f>$C9*F9</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="J9" s="57" t="inlineStr">
         <is>
@@ -4880,15 +4880,15 @@
       </c>
       <c r="G10" s="22">
         <f>$C10*D10</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="H10" s="22">
         <f>$C10*E10</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="I10" s="22">
         <f>$C10*F10</f>
-        <v/>
+        <v>2200</v>
       </c>
       <c r="J10" s="57" t="inlineStr">
         <is>
@@ -4926,15 +4926,15 @@
       </c>
       <c r="G11" s="22">
         <f>$C11*D11</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="H11" s="22">
         <f>$C11*E11</f>
-        <v/>
+        <v>2300</v>
       </c>
       <c r="I11" s="22">
         <f>$C11*F11</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="J11" s="57" t="inlineStr">
         <is>
@@ -4972,15 +4972,15 @@
       </c>
       <c r="G12" s="22">
         <f>$C12*D12</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="H12" s="22">
         <f>$C12*E12</f>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="I12" s="22">
         <f>$C12*F12</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="J12" s="57" t="inlineStr">
         <is>
@@ -5018,15 +5018,15 @@
       </c>
       <c r="G13" s="22">
         <f>$C13*D13</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H13" s="22">
         <f>$C13*E13</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="I13" s="22">
         <f>$C13*F13</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="J13" s="57" t="inlineStr">
         <is>
@@ -5064,15 +5064,15 @@
       </c>
       <c r="G14" s="22">
         <f>$C14*D14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H14" s="22">
         <f>$C14*E14</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="I14" s="22">
         <f>$C14*F14</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="J14" s="57" t="inlineStr">
         <is>
@@ -5110,15 +5110,15 @@
       </c>
       <c r="G15" s="22">
         <f>$C15*D15</f>
-        <v/>
+        <v>137</v>
       </c>
       <c r="H15" s="22">
         <f>$C15*E15</f>
-        <v/>
+        <v>137</v>
       </c>
       <c r="I15" s="22">
         <f>$C15*F15</f>
-        <v/>
+        <v>137</v>
       </c>
       <c r="J15" s="57" t="inlineStr">
         <is>
@@ -5156,15 +5156,15 @@
       </c>
       <c r="G16" s="22">
         <f>$C16*D16</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="H16" s="22">
         <f>$C16*E16</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="I16" s="22">
         <f>$C16*F16</f>
-        <v/>
+        <v>8000</v>
       </c>
       <c r="J16" s="57" t="inlineStr">
         <is>
@@ -5202,15 +5202,15 @@
       </c>
       <c r="G17" s="22">
         <f>$C17*D17</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H17" s="22">
         <f>$C17*E17</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="I17" s="22">
         <f>$C17*F17</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="J17" s="57" t="inlineStr">
         <is>
@@ -5265,15 +5265,15 @@
       </c>
       <c r="G19" s="22">
         <f>$C19*D19</f>
-        <v/>
+        <v>387</v>
       </c>
       <c r="H19" s="22">
         <f>$C19*E19</f>
-        <v/>
+        <v>387</v>
       </c>
       <c r="I19" s="22">
         <f>$C19*F19</f>
-        <v/>
+        <v>387</v>
       </c>
       <c r="J19" s="57" t="inlineStr">
         <is>
@@ -5311,15 +5311,15 @@
       </c>
       <c r="G20" s="22">
         <f>$C20*D20</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="H20" s="22">
         <f>$C20*E20</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="I20" s="22">
         <f>$C20*F20</f>
-        <v/>
+        <v>22000</v>
       </c>
       <c r="J20" s="57" t="inlineStr">
         <is>
@@ -5357,15 +5357,15 @@
       </c>
       <c r="G21" s="22">
         <f>$C21*D21</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="H21" s="22">
         <f>$C21*E21</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="I21" s="22">
         <f>$C21*F21</f>
-        <v/>
+        <v>5500</v>
       </c>
       <c r="J21" s="57" t="inlineStr">
         <is>
@@ -5403,15 +5403,15 @@
       </c>
       <c r="G22" s="22">
         <f>$C22*D22</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H22" s="22">
         <f>$C22*E22</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="I22" s="22">
         <f>$C22*F22</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="J22" s="57" t="inlineStr">
         <is>
@@ -5449,15 +5449,15 @@
       </c>
       <c r="G23" s="22">
         <f>$C23*D23</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="H23" s="22">
         <f>$C23*E23</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="I23" s="22">
         <f>$C23*F23</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="J23" s="57" t="inlineStr">
         <is>
@@ -5495,15 +5495,15 @@
       </c>
       <c r="G24" s="22">
         <f>$C24*D24</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="H24" s="22">
         <f>$C24*E24</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="I24" s="22">
         <f>$C24*F24</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="J24" s="57" t="inlineStr">
         <is>
@@ -5541,15 +5541,15 @@
       </c>
       <c r="G25" s="22">
         <f>$C25*D25</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H25" s="22">
         <f>$C25*E25</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="I25" s="22">
         <f>$C25*F25</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="J25" s="57" t="inlineStr">
         <is>
@@ -5604,15 +5604,15 @@
       </c>
       <c r="G27" s="22">
         <f>$C27*D27</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="H27" s="22">
         <f>$C27*E27</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="I27" s="22">
         <f>$C27*F27</f>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="J27" s="57" t="inlineStr">
         <is>
@@ -5650,15 +5650,15 @@
       </c>
       <c r="G28" s="22">
         <f>$C28*D28</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="H28" s="22">
         <f>$C28*E28</f>
-        <v/>
+        <v>3500</v>
       </c>
       <c r="I28" s="22">
         <f>$C28*F28</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="J28" s="57" t="inlineStr">
         <is>
@@ -5696,15 +5696,15 @@
       </c>
       <c r="G29" s="22">
         <f>$C29*D29</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="H29" s="22">
         <f>$C29*E29</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="I29" s="22">
         <f>$C29*F29</f>
-        <v/>
+        <v>3500</v>
       </c>
       <c r="J29" s="57" t="inlineStr">
         <is>
@@ -5742,15 +5742,15 @@
       </c>
       <c r="G30" s="22">
         <f>$C30*D30</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="H30" s="22">
         <f>$C30*E30</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="I30" s="22">
         <f>$C30*F30</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="J30" s="57" t="inlineStr">
         <is>
@@ -5784,15 +5784,15 @@
       </c>
       <c r="G31" s="22">
         <f>$C31*D31</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="H31" s="22">
         <f>$C31*E31</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="I31" s="22">
         <f>$C31*F31</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="J31" s="57" t="inlineStr">
         <is>
@@ -5843,15 +5843,15 @@
       </c>
       <c r="G33" s="22">
         <f>$C33*D33</f>
-        <v/>
+        <v>5600</v>
       </c>
       <c r="H33" s="22">
         <f>$C33*E33</f>
-        <v/>
+        <v>7600</v>
       </c>
       <c r="I33" s="22">
         <f>$C33*F33</f>
-        <v/>
+        <v>11000</v>
       </c>
       <c r="J33" s="57" t="inlineStr">
         <is>
@@ -5889,15 +5889,15 @@
       </c>
       <c r="G34" s="22">
         <f>$C34*D34</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="H34" s="22">
         <f>$C34*E34</f>
-        <v/>
+        <v>1900</v>
       </c>
       <c r="I34" s="22">
         <f>$C34*F34</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="J34" s="57" t="inlineStr">
         <is>
@@ -5935,15 +5935,15 @@
       </c>
       <c r="G35" s="22">
         <f>$C35*D35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="H35" s="22">
         <f>$C35*E35</f>
-        <v/>
+        <v>850</v>
       </c>
       <c r="I35" s="22">
         <f>$C35*F35</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="J35" s="57" t="inlineStr">
         <is>
@@ -5977,15 +5977,15 @@
       </c>
       <c r="G36" s="22">
         <f>$C36*D36</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="H36" s="22">
         <f>$C36*E36</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="I36" s="22">
         <f>$C36*F36</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="J36" s="57" t="inlineStr">
         <is>
@@ -6019,15 +6019,15 @@
       </c>
       <c r="G37" s="22">
         <f>$C37*D37</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="H37" s="22">
         <f>$C37*E37</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="I37" s="22">
         <f>$C37*F37</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="J37" s="57" t="inlineStr">
         <is>
@@ -6065,15 +6065,15 @@
       </c>
       <c r="G38" s="22">
         <f>$C38*D38</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="H38" s="22">
         <f>$C38*E38</f>
-        <v/>
+        <v>550</v>
       </c>
       <c r="I38" s="22">
         <f>$C38*F38</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="J38" s="57" t="inlineStr">
         <is>
@@ -6124,15 +6124,15 @@
       </c>
       <c r="G40" s="22">
         <f>$C40*D40</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="H40" s="22">
         <f>$C40*E40</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="I40" s="22">
         <f>$C40*F40</f>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="J40" s="57" t="inlineStr">
         <is>
@@ -6170,15 +6170,15 @@
       </c>
       <c r="G41" s="22">
         <f>$C41*D41</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="H41" s="22">
         <f>$C41*E41</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="I41" s="22">
         <f>$C41*F41</f>
-        <v/>
+        <v>3500</v>
       </c>
       <c r="J41" s="57" t="inlineStr">
         <is>
@@ -6216,15 +6216,15 @@
       </c>
       <c r="G42" s="22">
         <f>$C42*D42</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="H42" s="22">
         <f>$C42*E42</f>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="I42" s="22">
         <f>$C42*F42</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="J42" s="57" t="inlineStr">
         <is>
@@ -6267,15 +6267,15 @@
       <c r="F45" s="17" t="n"/>
       <c r="G45" s="25">
         <f>SUM(G6:G17)</f>
-        <v/>
+        <v>29437</v>
       </c>
       <c r="H45" s="25">
         <f>SUM(H6:H17)</f>
-        <v/>
+        <v>45337</v>
       </c>
       <c r="I45" s="25">
         <f>SUM(I6:I17)</f>
-        <v/>
+        <v>62837</v>
       </c>
       <c r="J45" s="17" t="n"/>
       <c r="K45" s="17" t="n"/>
@@ -6293,15 +6293,15 @@
       <c r="F46" s="17" t="n"/>
       <c r="G46" s="25">
         <f>SUM(G19:G25)</f>
-        <v/>
+        <v>10287</v>
       </c>
       <c r="H46" s="25">
         <f>SUM(H19:H25)</f>
-        <v/>
+        <v>19787</v>
       </c>
       <c r="I46" s="25">
         <f>SUM(I19:I25)</f>
-        <v/>
+        <v>37887</v>
       </c>
       <c r="J46" s="17" t="n"/>
       <c r="K46" s="17" t="n"/>
@@ -6319,15 +6319,15 @@
       <c r="F47" s="17" t="n"/>
       <c r="G47" s="25">
         <f>SUM(G27:G31)</f>
-        <v/>
+        <v>6200</v>
       </c>
       <c r="H47" s="25">
         <f>SUM(H27:H31)</f>
-        <v/>
+        <v>11900</v>
       </c>
       <c r="I47" s="25">
         <f>SUM(I27:I31)</f>
-        <v/>
+        <v>23800</v>
       </c>
       <c r="J47" s="17" t="n"/>
       <c r="K47" s="17" t="n"/>
@@ -6345,15 +6345,15 @@
       <c r="F48" s="17" t="n"/>
       <c r="G48" s="25">
         <f>SUM(G33:G38)</f>
-        <v/>
+        <v>9900</v>
       </c>
       <c r="H48" s="25">
         <f>SUM(H33:H38)</f>
-        <v/>
+        <v>15000</v>
       </c>
       <c r="I48" s="25">
         <f>SUM(I33:I38)</f>
-        <v/>
+        <v>24300</v>
       </c>
       <c r="J48" s="17" t="n"/>
       <c r="K48" s="17" t="n"/>
@@ -6371,15 +6371,15 @@
       <c r="F49" s="17" t="n"/>
       <c r="G49" s="25">
         <f>SUM(G40:G42)</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="H49" s="25">
         <f>SUM(H40:H42)</f>
-        <v/>
+        <v>9800</v>
       </c>
       <c r="I49" s="25">
         <f>SUM(I40:I42)</f>
-        <v/>
+        <v>17500</v>
       </c>
       <c r="J49" s="17" t="n"/>
       <c r="K49" s="17" t="n"/>
@@ -6397,15 +6397,15 @@
       <c r="F50" s="30" t="n"/>
       <c r="G50" s="31">
         <f>G45+G46+G47+G48+G49</f>
-        <v/>
+        <v>60824</v>
       </c>
       <c r="H50" s="31">
         <f>H45+H46+H47+H48+H49</f>
-        <v/>
+        <v>101824</v>
       </c>
       <c r="I50" s="31">
         <f>I45+I46+I47+I48+I49</f>
-        <v/>
+        <v>166324</v>
       </c>
       <c r="J50" s="30" t="n"/>
       <c r="K50" s="30" t="n"/>
@@ -6418,15 +6418,15 @@
       </c>
       <c r="G51" s="58">
         <f>'Unit Setup (1 Unit)'!D17</f>
-        <v/>
+        <v>6105</v>
       </c>
       <c r="H51" s="58">
         <f>'Unit Setup (1 Unit)'!E17</f>
-        <v/>
+        <v>9152</v>
       </c>
       <c r="I51" s="58">
         <f>'Unit Setup (1 Unit)'!F17</f>
-        <v/>
+        <v>13640</v>
       </c>
       <c r="K51" s="36" t="inlineStr">
         <is>
@@ -6445,15 +6445,15 @@
       </c>
       <c r="G52" s="60">
         <f>G50*$C$52</f>
-        <v/>
+        <v>6082.400000000001</v>
       </c>
       <c r="H52" s="60">
         <f>H50*$C$52</f>
-        <v/>
+        <v>10182.400000000001</v>
       </c>
       <c r="I52" s="60">
         <f>I50*$C$52</f>
-        <v/>
+        <v>16632.4</v>
       </c>
       <c r="K52" s="36" t="inlineStr">
         <is>
@@ -6474,15 +6474,15 @@
       <c r="F53" s="5" t="n"/>
       <c r="G53" s="19">
         <f>G50+G51+G52</f>
-        <v/>
+        <v>73011.4</v>
       </c>
       <c r="H53" s="19">
         <f>H50+H51+H52</f>
-        <v/>
+        <v>121158.4</v>
       </c>
       <c r="I53" s="19">
         <f>I50+I51+I52</f>
-        <v/>
+        <v>196596.4</v>
       </c>
       <c r="J53" s="5" t="n"/>
       <c r="K53" s="5" t="n"/>
@@ -6523,15 +6523,15 @@
       </c>
       <c r="G57" s="60">
         <f>G17+G40+G41</f>
-        <v/>
+        <v>3500</v>
       </c>
       <c r="H57" s="60">
         <f>H17+H40+H41</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="I57" s="60">
         <f>I17+I40+I41</f>
-        <v/>
+        <v>15500</v>
       </c>
       <c r="K57" s="63" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G5" s="22">
         <f>C5*E5</f>
-        <v/>
+        <v>1520</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="G6" s="22">
         <f>C6*E6</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="G7" s="22">
         <f>C7*E7</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="G8" s="22">
         <f>C8*E8</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="G9" s="22">
         <f>C9*E9</f>
-        <v/>
+        <v>450</v>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="G10" s="22">
         <f>C10*E10</f>
-        <v/>
+        <v>550</v>
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G11" s="22">
         <f>C11*E11</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G12" s="22">
         <f>C12*E12</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="G13" s="22">
         <f>C13*E13</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="G14" s="22">
         <f>C14*E14</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
@@ -6983,19 +6983,19 @@
       <c r="C15" s="30" t="n"/>
       <c r="D15" s="31">
         <f>SUMPRODUCT($C$5:$C$14,D5:D14)</f>
-        <v/>
+        <v>5550</v>
       </c>
       <c r="E15" s="31">
         <f>SUMPRODUCT($C$5:$C$14,E5:E14)</f>
-        <v/>
+        <v>8320</v>
       </c>
       <c r="F15" s="31">
         <f>SUMPRODUCT($C$5:$C$14,F5:F14)</f>
-        <v/>
+        <v>12400</v>
       </c>
       <c r="G15" s="31">
         <f>SUM(G5:G14)</f>
-        <v/>
+        <v>8320</v>
       </c>
       <c r="H15" s="30" t="n"/>
     </row>
@@ -7010,19 +7010,19 @@
       </c>
       <c r="D16" s="60">
         <f>D15*$C$16</f>
-        <v/>
+        <v>555</v>
       </c>
       <c r="E16" s="60">
         <f>E15*$C$16</f>
-        <v/>
+        <v>832</v>
       </c>
       <c r="F16" s="60">
         <f>F15*$C$16</f>
-        <v/>
+        <v>1240</v>
       </c>
       <c r="G16" s="60">
         <f>G15*$C$16</f>
-        <v/>
+        <v>832</v>
       </c>
       <c r="H16" s="36" t="inlineStr">
         <is>
@@ -7040,19 +7040,19 @@
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="19">
         <f>D15+D16</f>
-        <v/>
+        <v>6105</v>
       </c>
       <c r="E17" s="19">
         <f>E15+E16</f>
-        <v/>
+        <v>9152</v>
       </c>
       <c r="F17" s="19">
         <f>F15+F16</f>
-        <v/>
+        <v>13640</v>
       </c>
       <c r="G17" s="19">
         <f>G15+G16</f>
-        <v/>
+        <v>9152</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
@@ -7105,15 +7105,15 @@
       </c>
       <c r="B24" s="60">
         <f>$A24*D$17</f>
-        <v/>
+        <v>6105</v>
       </c>
       <c r="C24" s="60">
         <f>$A24*E$17</f>
-        <v/>
+        <v>9152</v>
       </c>
       <c r="D24" s="60">
         <f>$A24*F$17</f>
-        <v/>
+        <v>13640</v>
       </c>
     </row>
     <row r="25">
@@ -7122,15 +7122,15 @@
       </c>
       <c r="B25" s="60">
         <f>$A25*D$17</f>
-        <v/>
+        <v>30525</v>
       </c>
       <c r="C25" s="60">
         <f>$A25*E$17</f>
-        <v/>
+        <v>45760</v>
       </c>
       <c r="D25" s="60">
         <f>$A25*F$17</f>
-        <v/>
+        <v>68200</v>
       </c>
     </row>
     <row r="26">
@@ -7139,15 +7139,15 @@
       </c>
       <c r="B26" s="60">
         <f>$A26*D$17</f>
-        <v/>
+        <v>61050</v>
       </c>
       <c r="C26" s="60">
         <f>$A26*E$17</f>
-        <v/>
+        <v>91520</v>
       </c>
       <c r="D26" s="60">
         <f>$A26*F$17</f>
-        <v/>
+        <v>136400</v>
       </c>
     </row>
     <row r="27">
@@ -7156,15 +7156,15 @@
       </c>
       <c r="B27" s="60">
         <f>$A27*D$17</f>
-        <v/>
+        <v>152625</v>
       </c>
       <c r="C27" s="60">
         <f>$A27*E$17</f>
-        <v/>
+        <v>228800</v>
       </c>
       <c r="D27" s="60">
         <f>$A27*F$17</f>
-        <v/>
+        <v>341000</v>
       </c>
     </row>
     <row r="28">
@@ -7173,15 +7173,15 @@
       </c>
       <c r="B28" s="60">
         <f>$A28*D$17</f>
-        <v/>
+        <v>305250</v>
       </c>
       <c r="C28" s="60">
         <f>$A28*E$17</f>
-        <v/>
+        <v>457600</v>
       </c>
       <c r="D28" s="60">
         <f>$A28*F$17</f>
-        <v/>
+        <v>682000</v>
       </c>
     </row>
     <row r="29">
@@ -7190,15 +7190,15 @@
       </c>
       <c r="B29" s="67">
         <f>$A29*D$17</f>
-        <v/>
+        <v>488400</v>
       </c>
       <c r="C29" s="67">
         <f>$A29*E$17</f>
-        <v/>
+        <v>732160</v>
       </c>
       <c r="D29" s="67">
         <f>$A29*F$17</f>
-        <v/>
+        <v>1091200</v>
       </c>
     </row>
   </sheetData>
@@ -7289,15 +7289,15 @@
       </c>
       <c r="B5" s="15">
         <f>'OPEX Monthly'!O21</f>
-        <v/>
+        <v>42828</v>
       </c>
       <c r="C5" s="22">
         <f>B5/12</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="D5" s="54">
         <f>IF($B$14=0,0,B5/$B$14)</f>
-        <v/>
+        <v>0.061957026608948</v>
       </c>
       <c r="E5" s="17" t="n"/>
       <c r="F5" s="21" t="inlineStr">
@@ -7314,15 +7314,15 @@
       </c>
       <c r="B6" s="15">
         <f>'OPEX Monthly'!O28</f>
-        <v/>
+        <v>7760</v>
       </c>
       <c r="C6" s="22">
         <f>B6/12</f>
-        <v/>
+        <v>646.6666666666666</v>
       </c>
       <c r="D6" s="54">
         <f>IF($B$14=0,0,B6/$B$14)</f>
-        <v/>
+        <v>0.011225985955109659</v>
       </c>
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="21" t="inlineStr">
@@ -7339,15 +7339,15 @@
       </c>
       <c r="B7" s="15">
         <f>'OPEX Monthly'!O37</f>
-        <v/>
+        <v>57300</v>
       </c>
       <c r="C7" s="22">
         <f>B7/12</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="D7" s="54">
         <f>IF($B$14=0,0,B7/$B$14)</f>
-        <v/>
+        <v>0.08289291175615766</v>
       </c>
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="21" t="inlineStr">
@@ -7364,15 +7364,15 @@
       </c>
       <c r="B8" s="15">
         <f>'OPEX Monthly'!O41</f>
-        <v/>
+        <v>75103.20000000001</v>
       </c>
       <c r="C8" s="22">
         <f>B8/12</f>
-        <v/>
+        <v>6258.600000000001</v>
       </c>
       <c r="D8" s="54">
         <f>IF($B$14=0,0,B8/$B$14)</f>
-        <v/>
+        <v>0.10864786963708659</v>
       </c>
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="21" t="inlineStr">
@@ -7389,15 +7389,15 @@
       </c>
       <c r="B9" s="15">
         <f>'OPEX Monthly'!O52</f>
-        <v/>
+        <v>70331.12999999999</v>
       </c>
       <c r="C9" s="22">
         <f>B9/12</f>
-        <v/>
+        <v>5860.927499999999</v>
       </c>
       <c r="D9" s="54">
         <f>IF($B$14=0,0,B9/$B$14)</f>
-        <v/>
+        <v>0.10174436566842673</v>
       </c>
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="21" t="inlineStr">
@@ -7414,15 +7414,15 @@
       </c>
       <c r="B10" s="15">
         <f>'OPEX Monthly'!O60</f>
-        <v/>
+        <v>196420.00000000003</v>
       </c>
       <c r="C10" s="22">
         <f>B10/12</f>
-        <v/>
+        <v>16368.333333333336</v>
       </c>
       <c r="D10" s="54">
         <f>IF($B$14=0,0,B10/$B$14)</f>
-        <v/>
+        <v>0.28415053625034015</v>
       </c>
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="21" t="inlineStr">
@@ -7439,15 +7439,15 @@
       </c>
       <c r="B11" s="15">
         <f>'OPEX Monthly'!O70</f>
-        <v/>
+        <v>154694.16</v>
       </c>
       <c r="C11" s="22">
         <f>B11/12</f>
-        <v/>
+        <v>12891.18</v>
       </c>
       <c r="D11" s="54">
         <f>IF($B$14=0,0,B11/$B$14)</f>
-        <v/>
+        <v>0.2237879468424596</v>
       </c>
       <c r="E11" s="17" t="n"/>
       <c r="F11" s="21" t="inlineStr">
@@ -7464,15 +7464,15 @@
       </c>
       <c r="B12" s="15">
         <f>'OPEX Monthly'!O81</f>
-        <v/>
+        <v>53900.00000000001</v>
       </c>
       <c r="C12" s="22">
         <f>B12/12</f>
-        <v/>
+        <v>4491.666666666667</v>
       </c>
       <c r="D12" s="54">
         <f>IF($B$14=0,0,B12/$B$14)</f>
-        <v/>
+        <v>0.07797430966242407</v>
       </c>
       <c r="E12" s="17" t="n"/>
       <c r="F12" s="21" t="inlineStr">
@@ -7489,15 +7489,15 @@
       </c>
       <c r="B13" s="15">
         <f>'OPEX Monthly'!O85</f>
-        <v/>
+        <v>32916.8245</v>
       </c>
       <c r="C13" s="22">
         <f>B13/12</f>
-        <v/>
+        <v>2743.0687083333337</v>
       </c>
       <c r="D13" s="54">
         <f>IF($B$14=0,0,B13/$B$14)</f>
-        <v/>
+        <v>0.04761904761904762</v>
       </c>
       <c r="E13" s="17" t="n"/>
       <c r="F13" s="16" t="inlineStr">
@@ -7514,15 +7514,15 @@
       </c>
       <c r="B14" s="19">
         <f>SUM(B5:B13)</f>
-        <v/>
+        <v>691253.3145</v>
       </c>
       <c r="C14" s="19">
         <f>B14/12</f>
-        <v/>
+        <v>57604.442875</v>
       </c>
       <c r="D14" s="55">
         <f>IF($B$14=0,0,SUM(D5:D13))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="B17" s="24">
         <f>'OPEX Monthly'!N8</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="C17" s="17" t="n"/>
       <c r="D17" s="17" t="n"/>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="B18" s="15">
         <f>'OPEX Monthly'!O10</f>
-        <v/>
+        <v>3755160</v>
       </c>
       <c r="C18" s="17" t="n"/>
       <c r="D18" s="17" t="n"/>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B19" s="15">
         <f>'OPEX Monthly'!O11</f>
-        <v/>
+        <v>751032</v>
       </c>
       <c r="C19" s="17" t="n"/>
       <c r="D19" s="17" t="n"/>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B20" s="22">
         <f>B14</f>
-        <v/>
+        <v>691253.3145</v>
       </c>
       <c r="C20" s="17" t="n"/>
       <c r="D20" s="17" t="n"/>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="B21" s="15">
         <f>'OPEX Monthly'!O91</f>
-        <v/>
+        <v>59778.6855</v>
       </c>
       <c r="C21" s="17" t="n"/>
       <c r="D21" s="17" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B22" s="15">
         <f>MIN('OPEX Monthly'!C92:N92)</f>
-        <v/>
+        <v>-76726.00524999999</v>
       </c>
       <c r="C22" s="17" t="n"/>
       <c r="D22" s="17" t="n"/>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="B23" s="26">
         <f>IF(B19=0,0,B20/B19)</f>
-        <v/>
+        <v>0.9204046092576614</v>
       </c>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="n"/>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="B24" s="15">
         <f>'OPEX Monthly'!N86</f>
-        <v/>
+        <v>105622.916875</v>
       </c>
       <c r="C24" s="17" t="n"/>
       <c r="D24" s="17" t="n"/>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="B25" s="15">
         <f>'OPEX Monthly'!N94</f>
-        <v/>
+        <v>1487.6467165492957</v>
       </c>
       <c r="C25" s="17" t="n"/>
       <c r="D25" s="17" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="O7" s="50">
         <f>SUM(C7:N7)</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="P7" s="17" t="n"/>
     </row>
@@ -8117,55 +8117,55 @@
       </c>
       <c r="C8" s="74">
         <f>C7</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D8" s="74">
         <f>C8+D7</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="E8" s="74">
         <f>D8+E7</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="F8" s="74">
         <f>E8+F7</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="G8" s="74">
         <f>F8+G7</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="H8" s="74">
         <f>G8+H7</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="I8" s="74">
         <f>H8+I7</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="J8" s="74">
         <f>I8+J7</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="K8" s="74">
         <f>J8+K7</f>
-        <v/>
+        <v>54</v>
       </c>
       <c r="L8" s="74">
         <f>K8+L7</f>
-        <v/>
+        <v>62</v>
       </c>
       <c r="M8" s="74">
         <f>L8+M7</f>
-        <v/>
+        <v>71</v>
       </c>
       <c r="N8" s="74">
         <f>M8+N7</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="O8" s="50">
         <f>N8</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="P8" s="17" t="n"/>
     </row>
@@ -8185,51 +8185,51 @@
       </c>
       <c r="D9" s="74">
         <f>C8</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E9" s="74">
         <f>D8</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F9" s="74">
         <f>E8</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="G9" s="74">
         <f>F8</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="H9" s="74">
         <f>G8</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="I9" s="74">
         <f>H8</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="J9" s="74">
         <f>I8</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="K9" s="74">
         <f>J8</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="L9" s="74">
         <f>K8</f>
-        <v/>
+        <v>54</v>
       </c>
       <c r="M9" s="74">
         <f>L8</f>
-        <v/>
+        <v>62</v>
       </c>
       <c r="N9" s="74">
         <f>M8</f>
-        <v/>
+        <v>71</v>
       </c>
       <c r="O9" s="50">
         <f>N9</f>
-        <v/>
+        <v>71</v>
       </c>
       <c r="P9" s="17" t="n"/>
     </row>
@@ -8246,55 +8246,55 @@
       </c>
       <c r="C10" s="22">
         <f>C9*Assumptions!$F$14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D10" s="22">
         <f>D9*Assumptions!$F$14</f>
-        <v/>
+        <v>30780</v>
       </c>
       <c r="E10" s="22">
         <f>E9*Assumptions!$F$14</f>
-        <v/>
+        <v>71820</v>
       </c>
       <c r="F10" s="22">
         <f>F9*Assumptions!$F$14</f>
-        <v/>
+        <v>123120</v>
       </c>
       <c r="G10" s="22">
         <f>G9*Assumptions!$F$14</f>
-        <v/>
+        <v>184680</v>
       </c>
       <c r="H10" s="22">
         <f>H9*Assumptions!$F$14</f>
-        <v/>
+        <v>246240</v>
       </c>
       <c r="I10" s="22">
         <f>I9*Assumptions!$F$14</f>
-        <v/>
+        <v>318060</v>
       </c>
       <c r="J10" s="22">
         <f>J9*Assumptions!$F$14</f>
-        <v/>
+        <v>389880</v>
       </c>
       <c r="K10" s="22">
         <f>K9*Assumptions!$F$14</f>
-        <v/>
+        <v>471960</v>
       </c>
       <c r="L10" s="22">
         <f>L9*Assumptions!$F$14</f>
-        <v/>
+        <v>554040</v>
       </c>
       <c r="M10" s="22">
         <f>M9*Assumptions!$F$14</f>
-        <v/>
+        <v>636120</v>
       </c>
       <c r="N10" s="22">
         <f>N9*Assumptions!$F$14</f>
-        <v/>
+        <v>728460</v>
       </c>
       <c r="O10" s="44">
         <f>SUM(C10:N10)</f>
-        <v/>
+        <v>3755160</v>
       </c>
       <c r="P10" s="17" t="n"/>
     </row>
@@ -8311,55 +8311,55 @@
       </c>
       <c r="C11" s="22">
         <f>C10*Assumptions!$F$15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D11" s="22">
         <f>D10*Assumptions!$F$15</f>
-        <v/>
+        <v>6156</v>
       </c>
       <c r="E11" s="22">
         <f>E10*Assumptions!$F$15</f>
-        <v/>
+        <v>14364</v>
       </c>
       <c r="F11" s="22">
         <f>F10*Assumptions!$F$15</f>
-        <v/>
+        <v>24624</v>
       </c>
       <c r="G11" s="22">
         <f>G10*Assumptions!$F$15</f>
-        <v/>
+        <v>36936</v>
       </c>
       <c r="H11" s="22">
         <f>H10*Assumptions!$F$15</f>
-        <v/>
+        <v>49248</v>
       </c>
       <c r="I11" s="22">
         <f>I10*Assumptions!$F$15</f>
-        <v/>
+        <v>63612</v>
       </c>
       <c r="J11" s="22">
         <f>J10*Assumptions!$F$15</f>
-        <v/>
+        <v>77976</v>
       </c>
       <c r="K11" s="22">
         <f>K10*Assumptions!$F$15</f>
-        <v/>
+        <v>94392</v>
       </c>
       <c r="L11" s="22">
         <f>L10*Assumptions!$F$15</f>
-        <v/>
+        <v>110808</v>
       </c>
       <c r="M11" s="22">
         <f>M10*Assumptions!$F$15</f>
-        <v/>
+        <v>127224</v>
       </c>
       <c r="N11" s="22">
         <f>N10*Assumptions!$F$15</f>
-        <v/>
+        <v>145692</v>
       </c>
       <c r="O11" s="44">
         <f>SUM(C11:N11)</f>
-        <v/>
+        <v>751032</v>
       </c>
       <c r="P11" s="17" t="n"/>
     </row>
@@ -8376,51 +8376,51 @@
       </c>
       <c r="C12" s="77">
         <f>IF(OR(C6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D12" s="77">
         <f>IF(OR(D6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E12" s="77">
         <f>IF(OR(E6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F12" s="77">
         <f>IF(OR(F6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G12" s="77">
         <f>IF(OR(G6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H12" s="77">
         <f>IF(OR(H6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I12" s="77">
         <f>IF(OR(I6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J12" s="77">
         <f>IF(OR(J6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K12" s="77">
         <f>IF(OR(K6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L12" s="77">
         <f>IF(OR(L6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M12" s="77">
         <f>IF(OR(M6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N12" s="77">
         <f>IF(OR(N6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 1",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O12" s="17" t="n"/>
       <c r="P12" s="17" t="n"/>
@@ -8438,51 +8438,51 @@
       </c>
       <c r="C13" s="77">
         <f>IF(OR(C6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D13" s="77">
         <f>IF(OR(D6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E13" s="77">
         <f>IF(OR(E6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F13" s="77">
         <f>IF(OR(F6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G13" s="77">
         <f>IF(OR(G6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H13" s="77">
         <f>IF(OR(H6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I13" s="77">
         <f>IF(OR(I6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J13" s="77">
         <f>IF(OR(J6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K13" s="77">
         <f>IF(OR(K6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L13" s="77">
         <f>IF(OR(L6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M13" s="77">
         <f>IF(OR(M6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N13" s="77">
         <f>IF(OR(N6&lt;=Assumptions!$B$7,Assumptions!$B$6="Option 2",Assumptions!$B$6="Both"),1,0)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O13" s="17" t="n"/>
       <c r="P13" s="17" t="n"/>
@@ -8522,55 +8522,55 @@
       </c>
       <c r="C16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N16" s="22">
         <f>Assumptions!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O16" s="44">
         <f>SUM(C16:N16)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P16" s="17" t="n"/>
     </row>
@@ -8587,55 +8587,55 @@
       </c>
       <c r="C17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="E17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="F17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="G17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="H17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="I17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="J17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="L17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="M17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="N17" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$20</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="O17" s="44">
         <f>SUM(C17:N17)</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="P17" s="17" t="n"/>
     </row>
@@ -8652,55 +8652,55 @@
       </c>
       <c r="C18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="D18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="E18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="F18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="G18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="H18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="I18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="J18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="K18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="L18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="M18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="N18" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$21</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="O18" s="44">
         <f>SUM(C18:N18)</f>
-        <v/>
+        <v>4560</v>
       </c>
       <c r="P18" s="17" t="n"/>
     </row>
@@ -8717,55 +8717,55 @@
       </c>
       <c r="C19" s="22">
         <f>C17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="D19" s="22">
         <f>D17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="E19" s="22">
         <f>E17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="F19" s="22">
         <f>F17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="G19" s="22">
         <f>G17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="H19" s="22">
         <f>H17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="I19" s="22">
         <f>I17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="J19" s="22">
         <f>J17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="K19" s="22">
         <f>K17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="L19" s="22">
         <f>L17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="M19" s="22">
         <f>M17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="N19" s="22">
         <f>N17*Assumptions!$F$22</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="O19" s="44">
         <f>SUM(C19:N19)</f>
-        <v/>
+        <v>2088</v>
       </c>
       <c r="P19" s="17" t="n"/>
     </row>
@@ -8782,55 +8782,55 @@
       </c>
       <c r="C20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="D20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="E20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="F20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="G20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="H20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="I20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="J20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="K20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="L20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="M20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="N20" s="22">
         <f>Assumptions!$F$19*Assumptions!$F$23</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="O20" s="44">
         <f>SUM(C20:N20)</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="P20" s="17" t="n"/>
     </row>
@@ -8843,59 +8843,59 @@
       <c r="B21" s="30" t="n"/>
       <c r="C21" s="31">
         <f>SUM(C16:C20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="D21" s="31">
         <f>SUM(D16:D20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="E21" s="31">
         <f>SUM(E16:E20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="F21" s="31">
         <f>SUM(F16:F20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="G21" s="31">
         <f>SUM(G16:G20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="H21" s="31">
         <f>SUM(H16:H20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="I21" s="31">
         <f>SUM(I16:I20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="J21" s="31">
         <f>SUM(J16:J20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="K21" s="31">
         <f>SUM(K16:K20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="L21" s="31">
         <f>SUM(L16:L20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="M21" s="31">
         <f>SUM(M16:M20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="N21" s="31">
         <f>SUM(N16:N20)</f>
-        <v/>
+        <v>3569</v>
       </c>
       <c r="O21" s="31">
         <f>SUM(C21:N21)</f>
-        <v/>
+        <v>42828</v>
       </c>
       <c r="P21" s="79">
         <f>IF($O$86=0,0,$O21/$O$86)</f>
-        <v/>
+        <v>0.061957026608948</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -8933,55 +8933,55 @@
       </c>
       <c r="C24" s="80">
         <f>C12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="D24" s="80">
         <f>D12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="E24" s="80">
         <f>E12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F24" s="80">
         <f>F12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G24" s="80">
         <f>G12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H24" s="80">
         <f>H12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I24" s="80">
         <f>I12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J24" s="80">
         <f>J12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K24" s="80">
         <f>K12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L24" s="80">
         <f>L12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M24" s="80">
         <f>M12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N24" s="80">
         <f>N12*Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O24" s="44">
         <f>SUM(C24:N24)</f>
-        <v/>
+        <v>3600</v>
       </c>
       <c r="P24" s="17" t="n"/>
     </row>
@@ -8994,55 +8994,55 @@
       <c r="B25" s="70" t="inlineStr"/>
       <c r="C25" s="80">
         <f>C12*Assumptions!$F$27</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="D25" s="80">
         <f>D12*Assumptions!$F$27</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="E25" s="80">
         <f>E12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F25" s="80">
         <f>F12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G25" s="80">
         <f>G12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H25" s="80">
         <f>H12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I25" s="80">
         <f>I12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J25" s="80">
         <f>J12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K25" s="80">
         <f>K12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L25" s="80">
         <f>L12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M25" s="80">
         <f>M12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N25" s="80">
         <f>N12*Assumptions!$F$27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O25" s="44">
         <f>SUM(C25:N25)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="P25" s="17" t="n"/>
     </row>
@@ -9055,55 +9055,55 @@
       <c r="B26" s="70" t="inlineStr"/>
       <c r="C26" s="80">
         <f>C12*Assumptions!$F$28</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="D26" s="80">
         <f>D12*Assumptions!$F$28</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="E26" s="80">
         <f>E12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F26" s="80">
         <f>F12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G26" s="80">
         <f>G12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H26" s="80">
         <f>H12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I26" s="80">
         <f>I12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J26" s="80">
         <f>J12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K26" s="80">
         <f>K12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L26" s="80">
         <f>L12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M26" s="80">
         <f>M12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N26" s="80">
         <f>N12*Assumptions!$F$28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O26" s="44">
         <f>SUM(C26:N26)</f>
-        <v/>
+        <v>560</v>
       </c>
       <c r="P26" s="17" t="n"/>
     </row>
@@ -9116,55 +9116,55 @@
       <c r="B27" s="70" t="inlineStr"/>
       <c r="C27" s="80">
         <f>C12*Assumptions!$F$29</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="D27" s="80">
         <f>D12*Assumptions!$F$29</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="E27" s="80">
         <f>E12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F27" s="80">
         <f>F12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G27" s="80">
         <f>G12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H27" s="80">
         <f>H12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I27" s="80">
         <f>I12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J27" s="80">
         <f>J12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K27" s="80">
         <f>K12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L27" s="80">
         <f>L12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M27" s="80">
         <f>M12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N27" s="80">
         <f>N12*Assumptions!$F$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O27" s="44">
         <f>SUM(C27:N27)</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="P27" s="17" t="n"/>
     </row>
@@ -9177,59 +9177,59 @@
       <c r="B28" s="30" t="n"/>
       <c r="C28" s="31">
         <f>SUM(C24:C27)</f>
-        <v/>
+        <v>3880</v>
       </c>
       <c r="D28" s="31">
         <f>SUM(D24:D27)</f>
-        <v/>
+        <v>3880</v>
       </c>
       <c r="E28" s="31">
         <f>SUM(E24:E27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F28" s="31">
         <f>SUM(F24:F27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G28" s="31">
         <f>SUM(G24:G27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H28" s="31">
         <f>SUM(H24:H27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I28" s="31">
         <f>SUM(I24:I27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J28" s="31">
         <f>SUM(J24:J27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K28" s="31">
         <f>SUM(K24:K27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L28" s="31">
         <f>SUM(L24:L27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M28" s="31">
         <f>SUM(M24:M27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N28" s="31">
         <f>SUM(N24:N27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O28" s="31">
         <f>SUM(C28:N28)</f>
-        <v/>
+        <v>7760</v>
       </c>
       <c r="P28" s="79">
         <f>IF($O$86=0,0,$O28/$O$86)</f>
-        <v/>
+        <v>0.011225985955109659</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -9267,55 +9267,55 @@
       </c>
       <c r="C31" s="81">
         <f>C13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="D31" s="81">
         <f>D13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="E31" s="81">
         <f>E13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="F31" s="81">
         <f>F13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="G31" s="81">
         <f>G13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="H31" s="81">
         <f>H13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="I31" s="81">
         <f>I13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="J31" s="81">
         <f>J13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K31" s="81">
         <f>K13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="L31" s="81">
         <f>L13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="M31" s="81">
         <f>M13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="N31" s="81">
         <f>N13*Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="O31" s="44">
         <f>SUM(C31:N31)</f>
-        <v/>
+        <v>14400</v>
       </c>
       <c r="P31" s="17" t="n"/>
     </row>
@@ -9332,55 +9332,55 @@
       </c>
       <c r="C32" s="81">
         <f>C13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="D32" s="81">
         <f>D13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="E32" s="81">
         <f>E13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="F32" s="81">
         <f>F13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="G32" s="81">
         <f>G13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="H32" s="81">
         <f>H13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="I32" s="81">
         <f>I13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="J32" s="81">
         <f>J13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="K32" s="81">
         <f>K13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="L32" s="81">
         <f>L13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="M32" s="81">
         <f>M13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="N32" s="81">
         <f>N13*Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="O32" s="44">
         <f>SUM(C32:N32)</f>
-        <v/>
+        <v>17100</v>
       </c>
       <c r="P32" s="17" t="n"/>
     </row>
@@ -9397,55 +9397,55 @@
       </c>
       <c r="C33" s="81">
         <f>C13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="D33" s="81">
         <f>D13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="E33" s="81">
         <f>E13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="F33" s="81">
         <f>F13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="G33" s="81">
         <f>G13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="H33" s="81">
         <f>H13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="I33" s="81">
         <f>I13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="J33" s="81">
         <f>J13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="K33" s="81">
         <f>K13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="L33" s="81">
         <f>L13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="M33" s="81">
         <f>M13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="N33" s="81">
         <f>N13*Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="O33" s="44">
         <f>SUM(C33:N33)</f>
-        <v/>
+        <v>4200</v>
       </c>
       <c r="P33" s="17" t="n"/>
     </row>
@@ -9462,55 +9462,55 @@
       </c>
       <c r="C34" s="81">
         <f>C13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="D34" s="81">
         <f>D13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="E34" s="81">
         <f>E13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="F34" s="81">
         <f>F13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="G34" s="81">
         <f>G13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="H34" s="81">
         <f>H13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="I34" s="81">
         <f>I13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="J34" s="81">
         <f>J13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="K34" s="81">
         <f>K13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="L34" s="81">
         <f>L13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="M34" s="81">
         <f>M13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="N34" s="81">
         <f>N13*Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="O34" s="44">
         <f>SUM(C34:N34)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="P34" s="17" t="n"/>
     </row>
@@ -9523,55 +9523,55 @@
       <c r="B35" s="70" t="inlineStr"/>
       <c r="C35" s="81">
         <f>C13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="D35" s="81">
         <f>D13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="E35" s="81">
         <f>E13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="F35" s="81">
         <f>F13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G35" s="81">
         <f>G13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="H35" s="81">
         <f>H13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="I35" s="81">
         <f>I13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="J35" s="81">
         <f>J13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="K35" s="81">
         <f>K13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="L35" s="81">
         <f>L13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="M35" s="81">
         <f>M13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="N35" s="81">
         <f>N13*Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="O35" s="44">
         <f>SUM(C35:N35)</f>
-        <v/>
+        <v>10800</v>
       </c>
       <c r="P35" s="17" t="n"/>
     </row>
@@ -9588,55 +9588,55 @@
       </c>
       <c r="C36" s="81">
         <f>C13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="D36" s="81">
         <f>D13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="E36" s="81">
         <f>E13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="F36" s="81">
         <f>F13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="G36" s="81">
         <f>G13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="H36" s="81">
         <f>H13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="I36" s="81">
         <f>I13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="J36" s="81">
         <f>J13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="K36" s="81">
         <f>K13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="L36" s="81">
         <f>L13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="M36" s="81">
         <f>M13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="N36" s="81">
         <f>N13*Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="O36" s="44">
         <f>SUM(C36:N36)</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="P36" s="17" t="n"/>
     </row>
@@ -9649,59 +9649,59 @@
       <c r="B37" s="30" t="n"/>
       <c r="C37" s="31">
         <f>SUM(C31:C36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="D37" s="31">
         <f>SUM(D31:D36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="E37" s="31">
         <f>SUM(E31:E36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="F37" s="31">
         <f>SUM(F31:F36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="G37" s="31">
         <f>SUM(G31:G36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="H37" s="31">
         <f>SUM(H31:H36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="I37" s="31">
         <f>SUM(I31:I36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="J37" s="31">
         <f>SUM(J31:J36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="K37" s="31">
         <f>SUM(K31:K36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="L37" s="31">
         <f>SUM(L31:L36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="M37" s="31">
         <f>SUM(M31:M36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="N37" s="31">
         <f>SUM(N31:N36)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="O37" s="31">
         <f>SUM(C37:N37)</f>
-        <v/>
+        <v>57300</v>
       </c>
       <c r="P37" s="79">
         <f>IF($O$86=0,0,$O37/$O$86)</f>
-        <v/>
+        <v>0.08289291175615766</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -9739,55 +9739,55 @@
       </c>
       <c r="C40" s="22">
         <f>IF(Assumptions!$F$40=1,C10,C11)*Assumptions!$F$39</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D40" s="22">
         <f>IF(Assumptions!$F$40=1,D10,D11)*Assumptions!$F$39</f>
-        <v/>
+        <v>615.6</v>
       </c>
       <c r="E40" s="22">
         <f>IF(Assumptions!$F$40=1,E10,E11)*Assumptions!$F$39</f>
-        <v/>
+        <v>1436.4</v>
       </c>
       <c r="F40" s="22">
         <f>IF(Assumptions!$F$40=1,F10,F11)*Assumptions!$F$39</f>
-        <v/>
+        <v>2462.4</v>
       </c>
       <c r="G40" s="22">
         <f>IF(Assumptions!$F$40=1,G10,G11)*Assumptions!$F$39</f>
-        <v/>
+        <v>3693.6</v>
       </c>
       <c r="H40" s="22">
         <f>IF(Assumptions!$F$40=1,H10,H11)*Assumptions!$F$39</f>
-        <v/>
+        <v>4924.8</v>
       </c>
       <c r="I40" s="22">
         <f>IF(Assumptions!$F$40=1,I10,I11)*Assumptions!$F$39</f>
-        <v/>
+        <v>6361.2</v>
       </c>
       <c r="J40" s="22">
         <f>IF(Assumptions!$F$40=1,J10,J11)*Assumptions!$F$39</f>
-        <v/>
+        <v>7797.6</v>
       </c>
       <c r="K40" s="22">
         <f>IF(Assumptions!$F$40=1,K10,K11)*Assumptions!$F$39</f>
-        <v/>
+        <v>9439.2</v>
       </c>
       <c r="L40" s="22">
         <f>IF(Assumptions!$F$40=1,L10,L11)*Assumptions!$F$39</f>
-        <v/>
+        <v>11080.800000000001</v>
       </c>
       <c r="M40" s="22">
         <f>IF(Assumptions!$F$40=1,M10,M11)*Assumptions!$F$39</f>
-        <v/>
+        <v>12722.4</v>
       </c>
       <c r="N40" s="22">
         <f>IF(Assumptions!$F$40=1,N10,N11)*Assumptions!$F$39</f>
-        <v/>
+        <v>14569.2</v>
       </c>
       <c r="O40" s="44">
         <f>SUM(C40:N40)</f>
-        <v/>
+        <v>75103.20000000001</v>
       </c>
       <c r="P40" s="17" t="n"/>
     </row>
@@ -9800,59 +9800,59 @@
       <c r="B41" s="30" t="n"/>
       <c r="C41" s="31">
         <f>SUM(C40:C40)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D41" s="31">
         <f>SUM(D40:D40)</f>
-        <v/>
+        <v>615.6</v>
       </c>
       <c r="E41" s="31">
         <f>SUM(E40:E40)</f>
-        <v/>
+        <v>1436.4</v>
       </c>
       <c r="F41" s="31">
         <f>SUM(F40:F40)</f>
-        <v/>
+        <v>2462.4</v>
       </c>
       <c r="G41" s="31">
         <f>SUM(G40:G40)</f>
-        <v/>
+        <v>3693.6</v>
       </c>
       <c r="H41" s="31">
         <f>SUM(H40:H40)</f>
-        <v/>
+        <v>4924.8</v>
       </c>
       <c r="I41" s="31">
         <f>SUM(I40:I40)</f>
-        <v/>
+        <v>6361.2</v>
       </c>
       <c r="J41" s="31">
         <f>SUM(J40:J40)</f>
-        <v/>
+        <v>7797.6</v>
       </c>
       <c r="K41" s="31">
         <f>SUM(K40:K40)</f>
-        <v/>
+        <v>9439.2</v>
       </c>
       <c r="L41" s="31">
         <f>SUM(L40:L40)</f>
-        <v/>
+        <v>11080.800000000001</v>
       </c>
       <c r="M41" s="31">
         <f>SUM(M40:M40)</f>
-        <v/>
+        <v>12722.4</v>
       </c>
       <c r="N41" s="31">
         <f>SUM(N40:N40)</f>
-        <v/>
+        <v>14569.2</v>
       </c>
       <c r="O41" s="31">
         <f>SUM(C41:N41)</f>
-        <v/>
+        <v>75103.20000000001</v>
       </c>
       <c r="P41" s="79">
         <f>IF($O$86=0,0,$O41/$O$86)</f>
-        <v/>
+        <v>0.10864786963708659</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -9890,55 +9890,55 @@
       </c>
       <c r="C44" s="22">
         <f>C9*Assumptions!$F$42</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D44" s="22">
         <f>D9*Assumptions!$F$42</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="E44" s="22">
         <f>E9*Assumptions!$F$42</f>
-        <v/>
+        <v>525</v>
       </c>
       <c r="F44" s="22">
         <f>F9*Assumptions!$F$42</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G44" s="22">
         <f>G9*Assumptions!$F$42</f>
-        <v/>
+        <v>1350</v>
       </c>
       <c r="H44" s="22">
         <f>H9*Assumptions!$F$42</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="I44" s="22">
         <f>I9*Assumptions!$F$42</f>
-        <v/>
+        <v>2325</v>
       </c>
       <c r="J44" s="22">
         <f>J9*Assumptions!$F$42</f>
-        <v/>
+        <v>2850</v>
       </c>
       <c r="K44" s="22">
         <f>K9*Assumptions!$F$42</f>
-        <v/>
+        <v>3450</v>
       </c>
       <c r="L44" s="22">
         <f>L9*Assumptions!$F$42</f>
-        <v/>
+        <v>4050</v>
       </c>
       <c r="M44" s="22">
         <f>M9*Assumptions!$F$42</f>
-        <v/>
+        <v>4650</v>
       </c>
       <c r="N44" s="22">
         <f>N9*Assumptions!$F$42</f>
-        <v/>
+        <v>5325</v>
       </c>
       <c r="O44" s="44">
         <f>SUM(C44:N44)</f>
-        <v/>
+        <v>27450</v>
       </c>
       <c r="P44" s="17" t="n"/>
     </row>
@@ -9955,55 +9955,55 @@
       </c>
       <c r="C45" s="22">
         <f>C9*Assumptions!$F$43</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D45" s="22">
         <f>D9*Assumptions!$F$43</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="E45" s="22">
         <f>E9*Assumptions!$F$43</f>
-        <v/>
+        <v>224</v>
       </c>
       <c r="F45" s="22">
         <f>F9*Assumptions!$F$43</f>
-        <v/>
+        <v>384</v>
       </c>
       <c r="G45" s="22">
         <f>G9*Assumptions!$F$43</f>
-        <v/>
+        <v>576</v>
       </c>
       <c r="H45" s="22">
         <f>H9*Assumptions!$F$43</f>
-        <v/>
+        <v>768</v>
       </c>
       <c r="I45" s="22">
         <f>I9*Assumptions!$F$43</f>
-        <v/>
+        <v>992</v>
       </c>
       <c r="J45" s="22">
         <f>J9*Assumptions!$F$43</f>
-        <v/>
+        <v>1216</v>
       </c>
       <c r="K45" s="22">
         <f>K9*Assumptions!$F$43</f>
-        <v/>
+        <v>1472</v>
       </c>
       <c r="L45" s="22">
         <f>L9*Assumptions!$F$43</f>
-        <v/>
+        <v>1728</v>
       </c>
       <c r="M45" s="22">
         <f>M9*Assumptions!$F$43</f>
-        <v/>
+        <v>1984</v>
       </c>
       <c r="N45" s="22">
         <f>N9*Assumptions!$F$43</f>
-        <v/>
+        <v>2272</v>
       </c>
       <c r="O45" s="44">
         <f>SUM(C45:N45)</f>
-        <v/>
+        <v>11712</v>
       </c>
       <c r="P45" s="17" t="n"/>
     </row>
@@ -10020,55 +10020,55 @@
       </c>
       <c r="C46" s="22">
         <f>C9*Assumptions!$F$44</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D46" s="22">
         <f>D9*Assumptions!$F$44</f>
-        <v/>
+        <v>54</v>
       </c>
       <c r="E46" s="22">
         <f>E9*Assumptions!$F$44</f>
-        <v/>
+        <v>126</v>
       </c>
       <c r="F46" s="22">
         <f>F9*Assumptions!$F$44</f>
-        <v/>
+        <v>216</v>
       </c>
       <c r="G46" s="22">
         <f>G9*Assumptions!$F$44</f>
-        <v/>
+        <v>324</v>
       </c>
       <c r="H46" s="22">
         <f>H9*Assumptions!$F$44</f>
-        <v/>
+        <v>432</v>
       </c>
       <c r="I46" s="22">
         <f>I9*Assumptions!$F$44</f>
-        <v/>
+        <v>558</v>
       </c>
       <c r="J46" s="22">
         <f>J9*Assumptions!$F$44</f>
-        <v/>
+        <v>684</v>
       </c>
       <c r="K46" s="22">
         <f>K9*Assumptions!$F$44</f>
-        <v/>
+        <v>828</v>
       </c>
       <c r="L46" s="22">
         <f>L9*Assumptions!$F$44</f>
-        <v/>
+        <v>972</v>
       </c>
       <c r="M46" s="22">
         <f>M9*Assumptions!$F$44</f>
-        <v/>
+        <v>1116</v>
       </c>
       <c r="N46" s="22">
         <f>N9*Assumptions!$F$44</f>
-        <v/>
+        <v>1278</v>
       </c>
       <c r="O46" s="44">
         <f>SUM(C46:N46)</f>
-        <v/>
+        <v>6588</v>
       </c>
       <c r="P46" s="17" t="n"/>
     </row>
@@ -10085,55 +10085,55 @@
       </c>
       <c r="C47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="D47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="E47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="F47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="G47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="H47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="I47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="J47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="K47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="L47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="M47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="N47" s="82">
         <f>Assumptions!$F$45</f>
-        <v/>
+        <v>1318.4275</v>
       </c>
       <c r="O47" s="44">
         <f>SUM(C47:N47)</f>
-        <v/>
+        <v>15821.13</v>
       </c>
       <c r="P47" s="17" t="n"/>
     </row>
@@ -10146,55 +10146,55 @@
       <c r="B48" s="70" t="inlineStr"/>
       <c r="C48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="D48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="E48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="F48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="H48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="I48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="J48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="K48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="L48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="M48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="N48" s="22">
         <f>Assumptions!$F$46</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="O48" s="44">
         <f>SUM(C48:N48)</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="P48" s="17" t="n"/>
     </row>
@@ -10207,55 +10207,55 @@
       <c r="B49" s="70" t="inlineStr"/>
       <c r="C49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="D49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="E49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="F49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="G49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="H49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="I49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="J49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="K49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="L49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="M49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="N49" s="22">
         <f>Assumptions!$F$47</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="O49" s="44">
         <f>SUM(C49:N49)</f>
-        <v/>
+        <v>1920</v>
       </c>
       <c r="P49" s="17" t="n"/>
     </row>
@@ -10268,55 +10268,55 @@
       <c r="B50" s="70" t="inlineStr"/>
       <c r="C50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="D50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="E50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="F50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="G50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="H50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="I50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="J50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="K50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="L50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="M50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="N50" s="22">
         <f>Assumptions!$F$48</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="O50" s="44">
         <f>SUM(C50:N50)</f>
-        <v/>
+        <v>2280</v>
       </c>
       <c r="P50" s="17" t="n"/>
     </row>
@@ -10333,55 +10333,55 @@
       </c>
       <c r="C51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="D51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="E51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="F51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="G51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="H51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="I51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="J51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="K51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="L51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="M51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="N51" s="22">
         <f>Assumptions!$F$49</f>
-        <v/>
+        <v>230</v>
       </c>
       <c r="O51" s="44">
         <f>SUM(C51:N51)</f>
-        <v/>
+        <v>2760</v>
       </c>
       <c r="P51" s="17" t="n"/>
     </row>
@@ -10394,59 +10394,59 @@
       <c r="B52" s="30" t="n"/>
       <c r="C52" s="31">
         <f>SUM(C44:C51)</f>
-        <v/>
+        <v>2048.4275</v>
       </c>
       <c r="D52" s="31">
         <f>SUM(D44:D51)</f>
-        <v/>
+        <v>2423.4275</v>
       </c>
       <c r="E52" s="31">
         <f>SUM(E44:E51)</f>
-        <v/>
+        <v>2923.4275</v>
       </c>
       <c r="F52" s="31">
         <f>SUM(F44:F51)</f>
-        <v/>
+        <v>3548.4275</v>
       </c>
       <c r="G52" s="31">
         <f>SUM(G44:G51)</f>
-        <v/>
+        <v>4298.4275</v>
       </c>
       <c r="H52" s="31">
         <f>SUM(H44:H51)</f>
-        <v/>
+        <v>5048.4275</v>
       </c>
       <c r="I52" s="31">
         <f>SUM(I44:I51)</f>
-        <v/>
+        <v>5923.4275</v>
       </c>
       <c r="J52" s="31">
         <f>SUM(J44:J51)</f>
-        <v/>
+        <v>6798.4275</v>
       </c>
       <c r="K52" s="31">
         <f>SUM(K44:K51)</f>
-        <v/>
+        <v>7798.4275</v>
       </c>
       <c r="L52" s="31">
         <f>SUM(L44:L51)</f>
-        <v/>
+        <v>8798.4275</v>
       </c>
       <c r="M52" s="31">
         <f>SUM(M44:M51)</f>
-        <v/>
+        <v>9798.4275</v>
       </c>
       <c r="N52" s="31">
         <f>SUM(N44:N51)</f>
-        <v/>
+        <v>10923.4275</v>
       </c>
       <c r="O52" s="31">
         <f>SUM(C52:N52)</f>
-        <v/>
+        <v>70331.12999999999</v>
       </c>
       <c r="P52" s="79">
         <f>IF($O$86=0,0,$O52/$O$86)</f>
-        <v/>
+        <v>0.10174436566842673</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10484,55 +10484,55 @@
       </c>
       <c r="C55" s="22">
         <f>C9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D55" s="22">
         <f>D9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>380</v>
       </c>
       <c r="E55" s="22">
         <f>E9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>886.6666666666666</v>
       </c>
       <c r="F55" s="22">
         <f>F9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>1520</v>
       </c>
       <c r="G55" s="22">
         <f>G9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>2280</v>
       </c>
       <c r="H55" s="22">
         <f>H9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>3040</v>
       </c>
       <c r="I55" s="22">
         <f>I9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>3926.6666666666665</v>
       </c>
       <c r="J55" s="22">
         <f>J9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>4813.333333333333</v>
       </c>
       <c r="K55" s="22">
         <f>K9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>5826.666666666667</v>
       </c>
       <c r="L55" s="22">
         <f>L9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>6840</v>
       </c>
       <c r="M55" s="22">
         <f>M9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>7853.333333333333</v>
       </c>
       <c r="N55" s="22">
         <f>N9*Assumptions!$F$51/12</f>
-        <v/>
+        <v>8993.333333333334</v>
       </c>
       <c r="O55" s="44">
         <f>SUM(C55:N55)</f>
-        <v/>
+        <v>46360.00000000001</v>
       </c>
       <c r="P55" s="17" t="n"/>
     </row>
@@ -10549,55 +10549,55 @@
       </c>
       <c r="C56" s="22">
         <f>C9*Assumptions!$F$52</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D56" s="22">
         <f>D9*Assumptions!$F$52</f>
-        <v/>
+        <v>540</v>
       </c>
       <c r="E56" s="22">
         <f>E9*Assumptions!$F$52</f>
-        <v/>
+        <v>1260</v>
       </c>
       <c r="F56" s="22">
         <f>F9*Assumptions!$F$52</f>
-        <v/>
+        <v>2160</v>
       </c>
       <c r="G56" s="22">
         <f>G9*Assumptions!$F$52</f>
-        <v/>
+        <v>3240</v>
       </c>
       <c r="H56" s="22">
         <f>H9*Assumptions!$F$52</f>
-        <v/>
+        <v>4320</v>
       </c>
       <c r="I56" s="22">
         <f>I9*Assumptions!$F$52</f>
-        <v/>
+        <v>5580</v>
       </c>
       <c r="J56" s="22">
         <f>J9*Assumptions!$F$52</f>
-        <v/>
+        <v>6840</v>
       </c>
       <c r="K56" s="22">
         <f>K9*Assumptions!$F$52</f>
-        <v/>
+        <v>8280</v>
       </c>
       <c r="L56" s="22">
         <f>L9*Assumptions!$F$52</f>
-        <v/>
+        <v>9720</v>
       </c>
       <c r="M56" s="22">
         <f>M9*Assumptions!$F$52</f>
-        <v/>
+        <v>11160</v>
       </c>
       <c r="N56" s="22">
         <f>N9*Assumptions!$F$52</f>
-        <v/>
+        <v>12780</v>
       </c>
       <c r="O56" s="44">
         <f>SUM(C56:N56)</f>
-        <v/>
+        <v>65880</v>
       </c>
       <c r="P56" s="17" t="n"/>
     </row>
@@ -10614,55 +10614,55 @@
       </c>
       <c r="C57" s="22">
         <f>C9*Assumptions!$F$53</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D57" s="22">
         <f>D9*Assumptions!$F$53</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="E57" s="22">
         <f>E9*Assumptions!$F$53</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="F57" s="22">
         <f>F9*Assumptions!$F$53</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="G57" s="22">
         <f>G9*Assumptions!$F$53</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="H57" s="22">
         <f>H9*Assumptions!$F$53</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="I57" s="22">
         <f>I9*Assumptions!$F$53</f>
-        <v/>
+        <v>3100</v>
       </c>
       <c r="J57" s="22">
         <f>J9*Assumptions!$F$53</f>
-        <v/>
+        <v>3800</v>
       </c>
       <c r="K57" s="22">
         <f>K9*Assumptions!$F$53</f>
-        <v/>
+        <v>4600</v>
       </c>
       <c r="L57" s="22">
         <f>L9*Assumptions!$F$53</f>
-        <v/>
+        <v>5400</v>
       </c>
       <c r="M57" s="22">
         <f>M9*Assumptions!$F$53</f>
-        <v/>
+        <v>6200</v>
       </c>
       <c r="N57" s="22">
         <f>N9*Assumptions!$F$53</f>
-        <v/>
+        <v>7100</v>
       </c>
       <c r="O57" s="44">
         <f>SUM(C57:N57)</f>
-        <v/>
+        <v>36600</v>
       </c>
       <c r="P57" s="17" t="n"/>
     </row>
@@ -10679,55 +10679,55 @@
       </c>
       <c r="C58" s="22">
         <f>C9*Assumptions!$F$54</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D58" s="22">
         <f>D9*Assumptions!$F$54</f>
-        <v/>
+        <v>270</v>
       </c>
       <c r="E58" s="22">
         <f>E9*Assumptions!$F$54</f>
-        <v/>
+        <v>630</v>
       </c>
       <c r="F58" s="22">
         <f>F9*Assumptions!$F$54</f>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="G58" s="22">
         <f>G9*Assumptions!$F$54</f>
-        <v/>
+        <v>1620</v>
       </c>
       <c r="H58" s="22">
         <f>H9*Assumptions!$F$54</f>
-        <v/>
+        <v>2160</v>
       </c>
       <c r="I58" s="22">
         <f>I9*Assumptions!$F$54</f>
-        <v/>
+        <v>2790</v>
       </c>
       <c r="J58" s="22">
         <f>J9*Assumptions!$F$54</f>
-        <v/>
+        <v>3420</v>
       </c>
       <c r="K58" s="22">
         <f>K9*Assumptions!$F$54</f>
-        <v/>
+        <v>4140</v>
       </c>
       <c r="L58" s="22">
         <f>L9*Assumptions!$F$54</f>
-        <v/>
+        <v>4860</v>
       </c>
       <c r="M58" s="22">
         <f>M9*Assumptions!$F$54</f>
-        <v/>
+        <v>5580</v>
       </c>
       <c r="N58" s="22">
         <f>N9*Assumptions!$F$54</f>
-        <v/>
+        <v>6390</v>
       </c>
       <c r="O58" s="44">
         <f>SUM(C58:N58)</f>
-        <v/>
+        <v>32940</v>
       </c>
       <c r="P58" s="17" t="n"/>
     </row>
@@ -10744,55 +10744,55 @@
       </c>
       <c r="C59" s="22">
         <f>C9*Assumptions!$F$55</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D59" s="22">
         <f>D9*Assumptions!$F$55</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="E59" s="22">
         <f>E9*Assumptions!$F$55</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="F59" s="22">
         <f>F9*Assumptions!$F$55</f>
-        <v/>
+        <v>480</v>
       </c>
       <c r="G59" s="22">
         <f>G9*Assumptions!$F$55</f>
-        <v/>
+        <v>720</v>
       </c>
       <c r="H59" s="22">
         <f>H9*Assumptions!$F$55</f>
-        <v/>
+        <v>960</v>
       </c>
       <c r="I59" s="22">
         <f>I9*Assumptions!$F$55</f>
-        <v/>
+        <v>1240</v>
       </c>
       <c r="J59" s="22">
         <f>J9*Assumptions!$F$55</f>
-        <v/>
+        <v>1520</v>
       </c>
       <c r="K59" s="22">
         <f>K9*Assumptions!$F$55</f>
-        <v/>
+        <v>1840</v>
       </c>
       <c r="L59" s="22">
         <f>L9*Assumptions!$F$55</f>
-        <v/>
+        <v>2160</v>
       </c>
       <c r="M59" s="22">
         <f>M9*Assumptions!$F$55</f>
-        <v/>
+        <v>2480</v>
       </c>
       <c r="N59" s="22">
         <f>N9*Assumptions!$F$55</f>
-        <v/>
+        <v>2840</v>
       </c>
       <c r="O59" s="44">
         <f>SUM(C59:N59)</f>
-        <v/>
+        <v>14640</v>
       </c>
       <c r="P59" s="17" t="n"/>
     </row>
@@ -10805,59 +10805,59 @@
       <c r="B60" s="30" t="n"/>
       <c r="C60" s="31">
         <f>SUM(C55:C59)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D60" s="31">
         <f>SUM(D55:D59)</f>
-        <v/>
+        <v>1610</v>
       </c>
       <c r="E60" s="31">
         <f>SUM(E55:E59)</f>
-        <v/>
+        <v>3756.6666666666665</v>
       </c>
       <c r="F60" s="31">
         <f>SUM(F55:F59)</f>
-        <v/>
+        <v>6440</v>
       </c>
       <c r="G60" s="31">
         <f>SUM(G55:G59)</f>
-        <v/>
+        <v>9660</v>
       </c>
       <c r="H60" s="31">
         <f>SUM(H55:H59)</f>
-        <v/>
+        <v>12880</v>
       </c>
       <c r="I60" s="31">
         <f>SUM(I55:I59)</f>
-        <v/>
+        <v>16636.666666666664</v>
       </c>
       <c r="J60" s="31">
         <f>SUM(J55:J59)</f>
-        <v/>
+        <v>20393.333333333332</v>
       </c>
       <c r="K60" s="31">
         <f>SUM(K55:K59)</f>
-        <v/>
+        <v>24686.666666666668</v>
       </c>
       <c r="L60" s="31">
         <f>SUM(L55:L59)</f>
-        <v/>
+        <v>28980</v>
       </c>
       <c r="M60" s="31">
         <f>SUM(M55:M59)</f>
-        <v/>
+        <v>33273.33333333333</v>
       </c>
       <c r="N60" s="31">
         <f>SUM(N55:N59)</f>
-        <v/>
+        <v>38103.333333333336</v>
       </c>
       <c r="O60" s="31">
         <f>SUM(C60:N60)</f>
-        <v/>
+        <v>196420.00000000003</v>
       </c>
       <c r="P60" s="79">
         <f>IF($O$86=0,0,$O60/$O$86)</f>
-        <v/>
+        <v>0.28415053625034015</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -10891,55 +10891,55 @@
       <c r="B63" s="70" t="inlineStr"/>
       <c r="C63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="D63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="E63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="F63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="G63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="H63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="I63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="J63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="K63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="L63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="M63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="N63" s="22">
         <f>Assumptions!$F$57</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="O63" s="44">
         <f>SUM(C63:N63)</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="P63" s="17" t="n"/>
     </row>
@@ -10952,55 +10952,55 @@
       <c r="B64" s="70" t="inlineStr"/>
       <c r="C64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="D64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="E64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="F64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="G64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="H64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="I64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="J64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="K64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="L64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="M64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="N64" s="22">
         <f>Assumptions!$F$58</f>
-        <v/>
+        <v>520</v>
       </c>
       <c r="O64" s="44">
         <f>SUM(C64:N64)</f>
-        <v/>
+        <v>6240</v>
       </c>
       <c r="P64" s="17" t="n"/>
     </row>
@@ -11013,55 +11013,55 @@
       <c r="B65" s="70" t="inlineStr"/>
       <c r="C65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="D65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="E65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="F65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="G65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="H65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="I65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="J65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="K65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="L65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="M65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="N65" s="22">
         <f>Assumptions!$F$59</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="O65" s="44">
         <f>SUM(C65:N65)</f>
-        <v/>
+        <v>3120</v>
       </c>
       <c r="P65" s="17" t="n"/>
     </row>
@@ -11074,55 +11074,55 @@
       <c r="B66" s="70" t="inlineStr"/>
       <c r="C66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="D66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="E66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="F66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="G66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="H66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="I66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="J66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="K66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="L66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="M66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="N66" s="22">
         <f>Assumptions!$F$60</f>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="O66" s="44">
         <f>SUM(C66:N66)</f>
-        <v/>
+        <v>13200</v>
       </c>
       <c r="P66" s="17" t="n"/>
     </row>
@@ -11135,55 +11135,55 @@
       <c r="B67" s="70" t="inlineStr"/>
       <c r="C67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="D67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="E67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="F67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="G67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="H67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="I67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="J67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="K67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="L67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="M67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="N67" s="22">
         <f>Assumptions!$F$61</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="O67" s="44">
         <f>SUM(C67:N67)</f>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="P67" s="17" t="n"/>
     </row>
@@ -11196,55 +11196,55 @@
       <c r="B68" s="70" t="inlineStr"/>
       <c r="C68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="D68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="E68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="F68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="G68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="H68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="I68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="J68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="K68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="L68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="M68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="N68" s="22">
         <f>Assumptions!$F$62</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="O68" s="44">
         <f>SUM(C68:N68)</f>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="P68" s="17" t="n"/>
     </row>
@@ -11261,55 +11261,55 @@
       </c>
       <c r="C69" s="22">
         <f>C10*Assumptions!$F$63</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D69" s="22">
         <f>D10*Assumptions!$F$63</f>
-        <v/>
+        <v>800.28</v>
       </c>
       <c r="E69" s="22">
         <f>E10*Assumptions!$F$63</f>
-        <v/>
+        <v>1867.32</v>
       </c>
       <c r="F69" s="22">
         <f>F10*Assumptions!$F$63</f>
-        <v/>
+        <v>3201.12</v>
       </c>
       <c r="G69" s="22">
         <f>G10*Assumptions!$F$63</f>
-        <v/>
+        <v>4801.679999999999</v>
       </c>
       <c r="H69" s="22">
         <f>H10*Assumptions!$F$63</f>
-        <v/>
+        <v>6402.24</v>
       </c>
       <c r="I69" s="22">
         <f>I10*Assumptions!$F$63</f>
-        <v/>
+        <v>8269.56</v>
       </c>
       <c r="J69" s="22">
         <f>J10*Assumptions!$F$63</f>
-        <v/>
+        <v>10136.88</v>
       </c>
       <c r="K69" s="22">
         <f>K10*Assumptions!$F$63</f>
-        <v/>
+        <v>12270.96</v>
       </c>
       <c r="L69" s="22">
         <f>L10*Assumptions!$F$63</f>
-        <v/>
+        <v>14405.039999999999</v>
       </c>
       <c r="M69" s="22">
         <f>M10*Assumptions!$F$63</f>
-        <v/>
+        <v>16539.12</v>
       </c>
       <c r="N69" s="22">
         <f>N10*Assumptions!$F$63</f>
-        <v/>
+        <v>18939.96</v>
       </c>
       <c r="O69" s="44">
         <f>SUM(C69:N69)</f>
-        <v/>
+        <v>97634.16</v>
       </c>
       <c r="P69" s="17" t="n"/>
     </row>
@@ -11322,59 +11322,59 @@
       <c r="B70" s="30" t="n"/>
       <c r="C70" s="31">
         <f>SUM(C63:C69)</f>
-        <v/>
+        <v>4755</v>
       </c>
       <c r="D70" s="31">
         <f>SUM(D63:D69)</f>
-        <v/>
+        <v>5555.28</v>
       </c>
       <c r="E70" s="31">
         <f>SUM(E63:E69)</f>
-        <v/>
+        <v>6622.32</v>
       </c>
       <c r="F70" s="31">
         <f>SUM(F63:F69)</f>
-        <v/>
+        <v>7956.12</v>
       </c>
       <c r="G70" s="31">
         <f>SUM(G63:G69)</f>
-        <v/>
+        <v>9556.68</v>
       </c>
       <c r="H70" s="31">
         <f>SUM(H63:H69)</f>
-        <v/>
+        <v>11157.24</v>
       </c>
       <c r="I70" s="31">
         <f>SUM(I63:I69)</f>
-        <v/>
+        <v>13024.56</v>
       </c>
       <c r="J70" s="31">
         <f>SUM(J63:J69)</f>
-        <v/>
+        <v>14891.88</v>
       </c>
       <c r="K70" s="31">
         <f>SUM(K63:K69)</f>
-        <v/>
+        <v>17025.96</v>
       </c>
       <c r="L70" s="31">
         <f>SUM(L63:L69)</f>
-        <v/>
+        <v>19160.04</v>
       </c>
       <c r="M70" s="31">
         <f>SUM(M63:M69)</f>
-        <v/>
+        <v>21294.12</v>
       </c>
       <c r="N70" s="31">
         <f>SUM(N63:N69)</f>
-        <v/>
+        <v>23694.96</v>
       </c>
       <c r="O70" s="31">
         <f>SUM(C70:N70)</f>
-        <v/>
+        <v>154694.16</v>
       </c>
       <c r="P70" s="79">
         <f>IF($O$86=0,0,$O70/$O$86)</f>
-        <v/>
+        <v>0.2237879468424596</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -11408,55 +11408,55 @@
       <c r="B73" s="70" t="inlineStr"/>
       <c r="C73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="D73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="E73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="F73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="H73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="I73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="J73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="K73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="L73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="M73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="N73" s="22">
         <f>Assumptions!$F$65</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="O73" s="44">
         <f>SUM(C73:N73)</f>
-        <v/>
+        <v>10800</v>
       </c>
       <c r="P73" s="17" t="n"/>
     </row>
@@ -11473,55 +11473,55 @@
       </c>
       <c r="C74" s="22">
         <f>IF(MOD(C6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D74" s="22">
         <f>IF(MOD(D6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E74" s="22">
         <f>IF(MOD(E6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="F74" s="22">
         <f>IF(MOD(F6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G74" s="22">
         <f>IF(MOD(G6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H74" s="22">
         <f>IF(MOD(H6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="I74" s="22">
         <f>IF(MOD(I6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J74" s="22">
         <f>IF(MOD(J6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K74" s="22">
         <f>IF(MOD(K6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="L74" s="22">
         <f>IF(MOD(L6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M74" s="22">
         <f>IF(MOD(M6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N74" s="22">
         <f>IF(MOD(N6,3)=0,Assumptions!$F$66,0)</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="O74" s="44">
         <f>SUM(C74:N74)</f>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="P74" s="17" t="n"/>
     </row>
@@ -11538,55 +11538,55 @@
       </c>
       <c r="C75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="D75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="E75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="F75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="G75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="H75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="I75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="J75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="K75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="L75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="M75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="N75" s="22">
         <f>Assumptions!$F$67/12</f>
-        <v/>
+        <v>333.3333333333333</v>
       </c>
       <c r="O75" s="44">
         <f>SUM(C75:N75)</f>
-        <v/>
+        <v>4000.0000000000005</v>
       </c>
       <c r="P75" s="17" t="n"/>
     </row>
@@ -11603,55 +11603,55 @@
       </c>
       <c r="C76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="D76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="E76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="F76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="G76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="H76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="I76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="J76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="K76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="L76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="M76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="N76" s="22">
         <f>Assumptions!$F$68/12</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="O76" s="44">
         <f>SUM(C76:N76)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="P76" s="17" t="n"/>
     </row>
@@ -11668,55 +11668,55 @@
       </c>
       <c r="C77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="D77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="E77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="F77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="G77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="H77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="I77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="J77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="K77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="L77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="M77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="N77" s="22">
         <f>Assumptions!$F$69/12</f>
-        <v/>
+        <v>233.33333333333334</v>
       </c>
       <c r="O77" s="44">
         <f>SUM(C77:N77)</f>
-        <v/>
+        <v>2800.0000000000005</v>
       </c>
       <c r="P77" s="17" t="n"/>
     </row>
@@ -11733,55 +11733,55 @@
       </c>
       <c r="C78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="D78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="E78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="F78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="G78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="H78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="I78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="J78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="K78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="L78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="M78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="N78" s="22">
         <f>Assumptions!$F$70/12</f>
-        <v/>
+        <v>1583.3333333333333</v>
       </c>
       <c r="O78" s="44">
         <f>SUM(C78:N78)</f>
-        <v/>
+        <v>19000</v>
       </c>
       <c r="P78" s="17" t="n"/>
     </row>
@@ -11798,55 +11798,55 @@
       </c>
       <c r="C79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="D79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="E79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="F79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="G79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="H79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="I79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="J79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="K79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="L79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="M79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="N79" s="22">
         <f>Assumptions!$F$71/12</f>
-        <v/>
+        <v>458.3333333333333</v>
       </c>
       <c r="O79" s="44">
         <f>SUM(C79:N79)</f>
-        <v/>
+        <v>5499.999999999999</v>
       </c>
       <c r="P79" s="17" t="n"/>
     </row>
@@ -11863,55 +11863,55 @@
       </c>
       <c r="C80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="D80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="E80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="F80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="G80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="H80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="I80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="J80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="K80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="L80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="M80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="N80" s="22">
         <f>Assumptions!$F$72/12</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="O80" s="44">
         <f>SUM(C80:N80)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="P80" s="17" t="n"/>
     </row>
@@ -11924,59 +11924,59 @@
       <c r="B81" s="30" t="n"/>
       <c r="C81" s="31">
         <f>SUM(C73:C80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="D81" s="31">
         <f>SUM(D73:D80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="E81" s="31">
         <f>SUM(E73:E80)</f>
-        <v/>
+        <v>4958.333333333333</v>
       </c>
       <c r="F81" s="31">
         <f>SUM(F73:F80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="G81" s="31">
         <f>SUM(G73:G80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="H81" s="31">
         <f>SUM(H73:H80)</f>
-        <v/>
+        <v>4958.333333333333</v>
       </c>
       <c r="I81" s="31">
         <f>SUM(I73:I80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="J81" s="31">
         <f>SUM(J73:J80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="K81" s="31">
         <f>SUM(K73:K80)</f>
-        <v/>
+        <v>4958.333333333333</v>
       </c>
       <c r="L81" s="31">
         <f>SUM(L73:L80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="M81" s="31">
         <f>SUM(M73:M80)</f>
-        <v/>
+        <v>4258.333333333333</v>
       </c>
       <c r="N81" s="31">
         <f>SUM(N73:N80)</f>
-        <v/>
+        <v>4958.333333333333</v>
       </c>
       <c r="O81" s="31">
         <f>SUM(C81:N81)</f>
-        <v/>
+        <v>53900.00000000001</v>
       </c>
       <c r="P81" s="79">
         <f>IF($O$86=0,0,$O81/$O$86)</f>
-        <v/>
+        <v>0.07797430966242407</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -12010,55 +12010,55 @@
       <c r="B84" s="17" t="n"/>
       <c r="C84" s="25">
         <f>C21+C28+C37+C41+C52+C60+C70+C81</f>
-        <v/>
+        <v>23285.76083333333</v>
       </c>
       <c r="D84" s="25">
         <f>D21+D28+D37+D41+D52+D60+D70+D81</f>
-        <v/>
+        <v>26686.64083333333</v>
       </c>
       <c r="E84" s="25">
         <f>E21+E28+E37+E41+E52+E60+E70+E81</f>
-        <v/>
+        <v>28041.1475</v>
       </c>
       <c r="F84" s="25">
         <f>F21+F28+F37+F41+F52+F60+F70+F81</f>
-        <v/>
+        <v>33009.28083333333</v>
       </c>
       <c r="G84" s="25">
         <f>G21+G28+G37+G41+G52+G60+G70+G81</f>
-        <v/>
+        <v>39811.04083333334</v>
       </c>
       <c r="H84" s="25">
         <f>H21+H28+H37+H41+H52+H60+H70+H81</f>
-        <v/>
+        <v>47312.800833333335</v>
       </c>
       <c r="I84" s="25">
         <f>I21+I28+I37+I41+I52+I60+I70+I81</f>
-        <v/>
+        <v>54548.1875</v>
       </c>
       <c r="J84" s="25">
         <f>J21+J28+J37+J41+J52+J60+J70+J81</f>
-        <v/>
+        <v>62483.574166666665</v>
       </c>
       <c r="K84" s="25">
         <f>K21+K28+K37+K41+K52+K60+K70+K81</f>
-        <v/>
+        <v>72252.58750000001</v>
       </c>
       <c r="L84" s="25">
         <f>L21+L28+L37+L41+L52+L60+L70+L81</f>
-        <v/>
+        <v>80621.60083333333</v>
       </c>
       <c r="M84" s="25">
         <f>M21+M28+M37+M41+M52+M60+M70+M81</f>
-        <v/>
+        <v>89690.61416666665</v>
       </c>
       <c r="N84" s="25">
         <f>N21+N28+N37+N41+N52+N60+N70+N81</f>
-        <v/>
+        <v>100593.25416666667</v>
       </c>
       <c r="O84" s="25">
         <f>SUM(C84:N84)</f>
-        <v/>
+        <v>658336.49</v>
       </c>
       <c r="P84" s="17" t="n"/>
     </row>
@@ -12075,55 +12075,55 @@
       </c>
       <c r="C85" s="22">
         <f>C84*Assumptions!$F$74</f>
-        <v/>
+        <v>1164.2880416666665</v>
       </c>
       <c r="D85" s="22">
         <f>D84*Assumptions!$F$74</f>
-        <v/>
+        <v>1334.3320416666666</v>
       </c>
       <c r="E85" s="22">
         <f>E84*Assumptions!$F$74</f>
-        <v/>
+        <v>1402.057375</v>
       </c>
       <c r="F85" s="22">
         <f>F84*Assumptions!$F$74</f>
-        <v/>
+        <v>1650.4640416666666</v>
       </c>
       <c r="G85" s="22">
         <f>G84*Assumptions!$F$74</f>
-        <v/>
+        <v>1990.552041666667</v>
       </c>
       <c r="H85" s="22">
         <f>H84*Assumptions!$F$74</f>
-        <v/>
+        <v>2365.640041666667</v>
       </c>
       <c r="I85" s="22">
         <f>I84*Assumptions!$F$74</f>
-        <v/>
+        <v>2727.409375</v>
       </c>
       <c r="J85" s="22">
         <f>J84*Assumptions!$F$74</f>
-        <v/>
+        <v>3124.1787083333334</v>
       </c>
       <c r="K85" s="22">
         <f>K84*Assumptions!$F$74</f>
-        <v/>
+        <v>3612.6293750000004</v>
       </c>
       <c r="L85" s="22">
         <f>L84*Assumptions!$F$74</f>
-        <v/>
+        <v>4031.0800416666666</v>
       </c>
       <c r="M85" s="22">
         <f>M84*Assumptions!$F$74</f>
-        <v/>
+        <v>4484.530708333333</v>
       </c>
       <c r="N85" s="22">
         <f>N84*Assumptions!$F$74</f>
-        <v/>
+        <v>5029.662708333333</v>
       </c>
       <c r="O85" s="25">
         <f>SUM(C85:N85)</f>
-        <v/>
+        <v>32916.8245</v>
       </c>
       <c r="P85" s="17" t="n"/>
     </row>
@@ -12136,55 +12136,55 @@
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="19">
         <f>C84+C85</f>
-        <v/>
+        <v>24450.048874999997</v>
       </c>
       <c r="D86" s="19">
         <f>D84+D85</f>
-        <v/>
+        <v>28020.972875</v>
       </c>
       <c r="E86" s="19">
         <f>E84+E85</f>
-        <v/>
+        <v>29443.204875</v>
       </c>
       <c r="F86" s="19">
         <f>F84+F85</f>
-        <v/>
+        <v>34659.744875</v>
       </c>
       <c r="G86" s="19">
         <f>G84+G85</f>
-        <v/>
+        <v>41801.59287500001</v>
       </c>
       <c r="H86" s="19">
         <f>H84+H85</f>
-        <v/>
+        <v>49678.440875</v>
       </c>
       <c r="I86" s="19">
         <f>I84+I85</f>
-        <v/>
+        <v>57275.596875</v>
       </c>
       <c r="J86" s="19">
         <f>J84+J85</f>
-        <v/>
+        <v>65607.752875</v>
       </c>
       <c r="K86" s="19">
         <f>K84+K85</f>
-        <v/>
+        <v>75865.21687500001</v>
       </c>
       <c r="L86" s="19">
         <f>L84+L85</f>
-        <v/>
+        <v>84652.68087499999</v>
       </c>
       <c r="M86" s="19">
         <f>M84+M85</f>
-        <v/>
+        <v>94175.14487499998</v>
       </c>
       <c r="N86" s="19">
         <f>N84+N85</f>
-        <v/>
+        <v>105622.916875</v>
       </c>
       <c r="O86" s="19">
         <f>SUM(C86:N86)</f>
-        <v/>
+        <v>691253.3145</v>
       </c>
       <c r="P86" s="5" t="n"/>
     </row>
@@ -12223,55 +12223,55 @@
       </c>
       <c r="C89" s="22">
         <f>C11</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D89" s="22">
         <f>D11</f>
-        <v/>
+        <v>6156</v>
       </c>
       <c r="E89" s="22">
         <f>E11</f>
-        <v/>
+        <v>14364</v>
       </c>
       <c r="F89" s="22">
         <f>F11</f>
-        <v/>
+        <v>24624</v>
       </c>
       <c r="G89" s="22">
         <f>G11</f>
-        <v/>
+        <v>36936</v>
       </c>
       <c r="H89" s="22">
         <f>H11</f>
-        <v/>
+        <v>49248</v>
       </c>
       <c r="I89" s="22">
         <f>I11</f>
-        <v/>
+        <v>63612</v>
       </c>
       <c r="J89" s="22">
         <f>J11</f>
-        <v/>
+        <v>77976</v>
       </c>
       <c r="K89" s="22">
         <f>K11</f>
-        <v/>
+        <v>94392</v>
       </c>
       <c r="L89" s="22">
         <f>L11</f>
-        <v/>
+        <v>110808</v>
       </c>
       <c r="M89" s="22">
         <f>M11</f>
-        <v/>
+        <v>127224</v>
       </c>
       <c r="N89" s="22">
         <f>N11</f>
-        <v/>
+        <v>145692</v>
       </c>
       <c r="O89" s="86">
         <f>SUM(C89:N89)</f>
-        <v/>
+        <v>751032</v>
       </c>
       <c r="P89" s="17" t="n"/>
     </row>
@@ -12284,55 +12284,55 @@
       <c r="B90" s="70" t="inlineStr"/>
       <c r="C90" s="22">
         <f>C86</f>
-        <v/>
+        <v>24450.048874999997</v>
       </c>
       <c r="D90" s="22">
         <f>D86</f>
-        <v/>
+        <v>28020.972875</v>
       </c>
       <c r="E90" s="22">
         <f>E86</f>
-        <v/>
+        <v>29443.204875</v>
       </c>
       <c r="F90" s="22">
         <f>F86</f>
-        <v/>
+        <v>34659.744875</v>
       </c>
       <c r="G90" s="22">
         <f>G86</f>
-        <v/>
+        <v>41801.59287500001</v>
       </c>
       <c r="H90" s="22">
         <f>H86</f>
-        <v/>
+        <v>49678.440875</v>
       </c>
       <c r="I90" s="22">
         <f>I86</f>
-        <v/>
+        <v>57275.596875</v>
       </c>
       <c r="J90" s="22">
         <f>J86</f>
-        <v/>
+        <v>65607.752875</v>
       </c>
       <c r="K90" s="22">
         <f>K86</f>
-        <v/>
+        <v>75865.21687500001</v>
       </c>
       <c r="L90" s="22">
         <f>L86</f>
-        <v/>
+        <v>84652.68087499999</v>
       </c>
       <c r="M90" s="22">
         <f>M86</f>
-        <v/>
+        <v>94175.14487499998</v>
       </c>
       <c r="N90" s="22">
         <f>N86</f>
-        <v/>
+        <v>105622.916875</v>
       </c>
       <c r="O90" s="86">
         <f>SUM(C90:N90)</f>
-        <v/>
+        <v>691253.3145</v>
       </c>
       <c r="P90" s="17" t="n"/>
     </row>
@@ -12349,55 +12349,55 @@
       </c>
       <c r="C91" s="25">
         <f>C89-C90</f>
-        <v/>
+        <v>-24450.048874999997</v>
       </c>
       <c r="D91" s="25">
         <f>D89-D90</f>
-        <v/>
+        <v>-21864.972875</v>
       </c>
       <c r="E91" s="25">
         <f>E89-E90</f>
-        <v/>
+        <v>-15079.204875</v>
       </c>
       <c r="F91" s="25">
         <f>F89-F90</f>
-        <v/>
+        <v>-10035.744874999997</v>
       </c>
       <c r="G91" s="25">
         <f>G89-G90</f>
-        <v/>
+        <v>-4865.592875000009</v>
       </c>
       <c r="H91" s="25">
         <f>H89-H90</f>
-        <v/>
+        <v>-430.44087500000023</v>
       </c>
       <c r="I91" s="25">
         <f>I89-I90</f>
-        <v/>
+        <v>6336.403124999997</v>
       </c>
       <c r="J91" s="25">
         <f>J89-J90</f>
-        <v/>
+        <v>12368.247124999994</v>
       </c>
       <c r="K91" s="25">
         <f>K89-K90</f>
-        <v/>
+        <v>18526.783124999987</v>
       </c>
       <c r="L91" s="25">
         <f>L89-L90</f>
-        <v/>
+        <v>26155.31912500001</v>
       </c>
       <c r="M91" s="25">
         <f>M89-M90</f>
-        <v/>
+        <v>33048.85512500002</v>
       </c>
       <c r="N91" s="25">
         <f>N89-N90</f>
-        <v/>
+        <v>40069.083125000005</v>
       </c>
       <c r="O91" s="44">
         <f>SUM(C91:N91)</f>
-        <v/>
+        <v>59778.6855</v>
       </c>
       <c r="P91" s="17" t="n"/>
     </row>
@@ -12414,55 +12414,55 @@
       </c>
       <c r="C92" s="25">
         <f>C91</f>
-        <v/>
+        <v>-24450.048874999997</v>
       </c>
       <c r="D92" s="25">
         <f>C92+D91</f>
-        <v/>
+        <v>-46315.02175</v>
       </c>
       <c r="E92" s="25">
         <f>D92+E91</f>
-        <v/>
+        <v>-61394.226624999996</v>
       </c>
       <c r="F92" s="25">
         <f>E92+F91</f>
-        <v/>
+        <v>-71429.97149999999</v>
       </c>
       <c r="G92" s="25">
         <f>F92+G91</f>
-        <v/>
+        <v>-76295.56437499999</v>
       </c>
       <c r="H92" s="25">
         <f>G92+H91</f>
-        <v/>
+        <v>-76726.00524999999</v>
       </c>
       <c r="I92" s="25">
         <f>H92+I91</f>
-        <v/>
+        <v>-70389.60212499999</v>
       </c>
       <c r="J92" s="25">
         <f>I92+J91</f>
-        <v/>
+        <v>-58021.354999999996</v>
       </c>
       <c r="K92" s="25">
         <f>J92+K91</f>
-        <v/>
+        <v>-39494.57187500001</v>
       </c>
       <c r="L92" s="25">
         <f>K92+L91</f>
-        <v/>
+        <v>-13339.25275</v>
       </c>
       <c r="M92" s="25">
         <f>L92+M91</f>
-        <v/>
+        <v>19709.602375000017</v>
       </c>
       <c r="N92" s="25">
         <f>M92+N91</f>
-        <v/>
+        <v>59778.68550000002</v>
       </c>
       <c r="O92" s="44">
         <f>N92</f>
-        <v/>
+        <v>59778.68550000002</v>
       </c>
       <c r="P92" s="17" t="n"/>
     </row>
@@ -12479,55 +12479,55 @@
       </c>
       <c r="C93" s="26">
         <f>IF(C89=0,0,C90/C89)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D93" s="26">
         <f>IF(D89=0,0,D90/D89)</f>
-        <v/>
+        <v>4.551814956952566</v>
       </c>
       <c r="E93" s="26">
         <f>IF(E89=0,0,E90/E89)</f>
-        <v/>
+        <v>2.0497914839181286</v>
       </c>
       <c r="F93" s="26">
         <f>IF(F89=0,0,F90/F89)</f>
-        <v/>
+        <v>1.4075594897254708</v>
       </c>
       <c r="G93" s="26">
         <f>IF(G89=0,0,G90/G89)</f>
-        <v/>
+        <v>1.1317303680690927</v>
       </c>
       <c r="H93" s="26">
         <f>IF(H89=0,0,H90/H89)</f>
-        <v/>
+        <v>1.008740271178525</v>
       </c>
       <c r="I93" s="26">
         <f>IF(I89=0,0,I90/I89)</f>
-        <v/>
+        <v>0.9003898144218072</v>
       </c>
       <c r="J93" s="26">
         <f>IF(J89=0,0,J90/J89)</f>
-        <v/>
+        <v>0.841383924220273</v>
       </c>
       <c r="K93" s="26">
         <f>IF(K89=0,0,K90/K89)</f>
-        <v/>
+        <v>0.8037250707157387</v>
       </c>
       <c r="L93" s="26">
         <f>IF(L89=0,0,L90/L89)</f>
-        <v/>
+        <v>0.7639582058605876</v>
       </c>
       <c r="M93" s="26">
         <f>IF(M89=0,0,M90/M89)</f>
-        <v/>
+        <v>0.7402309695890711</v>
       </c>
       <c r="N93" s="26">
         <f>IF(N89=0,0,N90/N89)</f>
-        <v/>
+        <v>0.7249740334060896</v>
       </c>
       <c r="O93" s="46">
         <f>IF(O89=0,0,O90/O89)</f>
-        <v/>
+        <v>0.9204046092576614</v>
       </c>
       <c r="P93" s="17" t="n"/>
     </row>
@@ -12544,55 +12544,55 @@
       </c>
       <c r="C94" s="22">
         <f>IF(C9=0,0,C90/C9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D94" s="22">
         <f>IF(D9=0,0,D90/D9)</f>
-        <v/>
+        <v>9340.324291666666</v>
       </c>
       <c r="E94" s="22">
         <f>IF(E9=0,0,E90/E9)</f>
-        <v/>
+        <v>4206.172125</v>
       </c>
       <c r="F94" s="22">
         <f>IF(F9=0,0,F90/F9)</f>
-        <v/>
+        <v>2888.3120729166662</v>
       </c>
       <c r="G94" s="22">
         <f>IF(G9=0,0,G90/G9)</f>
-        <v/>
+        <v>2322.3107152777784</v>
       </c>
       <c r="H94" s="22">
         <f>IF(H9=0,0,H90/H9)</f>
-        <v/>
+        <v>2069.9350364583333</v>
       </c>
       <c r="I94" s="22">
         <f>IF(I9=0,0,I90/I9)</f>
-        <v/>
+        <v>1847.5998991935485</v>
       </c>
       <c r="J94" s="22">
         <f>IF(J9=0,0,J90/J9)</f>
-        <v/>
+        <v>1726.5198125000002</v>
       </c>
       <c r="K94" s="22">
         <f>IF(K9=0,0,K90/K9)</f>
-        <v/>
+        <v>1649.243845108696</v>
       </c>
       <c r="L94" s="22">
         <f>IF(L9=0,0,L90/L9)</f>
-        <v/>
+        <v>1567.6422384259258</v>
       </c>
       <c r="M94" s="22">
         <f>IF(M9=0,0,M90/M9)</f>
-        <v/>
+        <v>1518.953949596774</v>
       </c>
       <c r="N94" s="22">
         <f>IF(N9=0,0,N90/N9)</f>
-        <v/>
+        <v>1487.6467165492957</v>
       </c>
       <c r="O94" s="44">
         <f>IF(N9=0,0,N90/N9)</f>
-        <v/>
+        <v>1487.6467165492957</v>
       </c>
       <c r="P94" s="17" t="n"/>
     </row>
@@ -12710,15 +12710,15 @@
       </c>
       <c r="B6" s="22">
         <f>Assumptions!$F$25*Assumptions!$F$26</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="C6" s="22">
         <f>Assumptions!$F$31*Assumptions!$F$32</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="D6" s="22">
         <f>B6-C6</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="17" t="n"/>
@@ -12736,15 +12736,15 @@
       </c>
       <c r="B7" s="22">
         <f>0</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C7" s="22">
         <f>Assumptions!$F$33</f>
-        <v/>
+        <v>1425</v>
       </c>
       <c r="D7" s="22">
         <f>B7-C7</f>
-        <v/>
+        <v>-1425</v>
       </c>
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
@@ -12762,15 +12762,15 @@
       </c>
       <c r="B8" s="22">
         <f>0</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C8" s="22">
         <f>Assumptions!$F$34</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="D8" s="22">
         <f>B8-C8</f>
-        <v/>
+        <v>-350</v>
       </c>
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="17" t="n"/>
@@ -12788,15 +12788,15 @@
       </c>
       <c r="B9" s="22">
         <f>Assumptions!$F$29</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="C9" s="22">
         <f>Assumptions!$F$35</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="D9" s="22">
         <f>B9-C9</f>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
@@ -12814,15 +12814,15 @@
       </c>
       <c r="B10" s="22">
         <f>Assumptions!$F$27</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="C10" s="22">
         <f>Assumptions!$F$36</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="D10" s="22">
         <f>B10-C10</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="17" t="n"/>
@@ -12840,15 +12840,15 @@
       </c>
       <c r="B11" s="22">
         <f>Assumptions!$F$28</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="C11" s="22">
         <f>0</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D11" s="22">
         <f>B11-C11</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="E11" s="17" t="n"/>
       <c r="F11" s="17" t="n"/>
@@ -12866,15 +12866,15 @@
       </c>
       <c r="B12" s="22">
         <f>0</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C12" s="22">
         <f>Assumptions!$F$37</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="D12" s="22">
         <f>B12-C12</f>
-        <v/>
+        <v>-400</v>
       </c>
       <c r="E12" s="17" t="n"/>
       <c r="F12" s="17" t="n"/>
@@ -12892,15 +12892,15 @@
       </c>
       <c r="B13" s="19">
         <f>SUM(B6:B12)</f>
-        <v/>
+        <v>3880</v>
       </c>
       <c r="C13" s="19">
         <f>SUM(C6:C12)</f>
-        <v/>
+        <v>4775</v>
       </c>
       <c r="D13" s="19">
         <f>SUM(D6:D12)</f>
-        <v/>
+        <v>-895</v>
       </c>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
@@ -12914,15 +12914,15 @@
       </c>
       <c r="B14" s="88">
         <f>Assumptions!$F$25</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C14" s="88">
         <f>Assumptions!$F$31</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D14" s="88">
         <f>B14-C14</f>
-        <v/>
+        <v>-2</v>
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
@@ -12938,15 +12938,15 @@
       </c>
       <c r="B15" s="60">
         <f>IF(B14=0,0,B13/B14)</f>
-        <v/>
+        <v>1293.3333333333333</v>
       </c>
       <c r="C15" s="60">
         <f>IF(C14=0,0,C13/C14)</f>
-        <v/>
+        <v>955</v>
       </c>
       <c r="D15" s="60">
         <f>B15-C15</f>
-        <v/>
+        <v>338.33333333333326</v>
       </c>
       <c r="G15" s="63" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="B18" s="58">
         <f>Assumptions!$F$16</f>
-        <v/>
+        <v>2052</v>
       </c>
       <c r="G18" s="36" t="inlineStr">
         <is>
@@ -12991,11 +12991,11 @@
       </c>
       <c r="B19" s="89">
         <f>IF($B$18=0,0,B13/$B$18)</f>
-        <v/>
+        <v>1.8908382066276803</v>
       </c>
       <c r="C19" s="89">
         <f>IF($B$18=0,0,C13/$B$18)</f>
-        <v/>
+        <v>2.326998050682261</v>
       </c>
       <c r="G19" s="63" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B22" s="60">
         <f>(B13+C13)*Assumptions!$B$7</f>
-        <v/>
+        <v>17310</v>
       </c>
       <c r="G22" s="36" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B23" s="60">
         <f>(MAX(B13,C13))*Assumptions!$B$7</f>
-        <v/>
+        <v>9550</v>
       </c>
       <c r="G23" s="63" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="B24" s="89">
         <f>IF($B$18=0,0,B23/$B$18)</f>
-        <v/>
+        <v>4.653996101364522</v>
       </c>
       <c r="G24" s="63" t="inlineStr">
         <is>

--- a/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
+++ b/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Funding Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CAPEX Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CAPEX Detail" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Unit Setup (1 Unit)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="OPEX Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="OPEX Monthly" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Marketing Comparison" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="AI Subscriptions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Setup (1 Unit)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEX Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEX Monthly" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketing Comparison" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Subscriptions" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Key lever, or a figure you supplied.</t>
+          <t>Key lever, or a figure supplied by management.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>HJ item 5. Feeds the 'AI subscriptions' line in the OPEX model. USD converted at the pegged AED rate.</t>
+          <t>Specified by management. Feeds the 'AI subscriptions' line in the OPEX model. USD converted at the pegged AED rate.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2260,7 +2260,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>All figures AED unless stated. Blue = editable input. Yellow = figure supplied by HJ or a key lever.</t>
+          <t>All figures AED unless stated. Blue = editable input. Yellow = figure supplied by management or a key lever.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>Both options run in Months 1–2 per HJ. From Month 3 the model keeps whichever you select here. Select 'Both' to keep running them in parallel all year.</t>
+          <t>Both options run in Months 1–2 per management. From Month 3 the model keeps whichever you select here. Select 'Both' to keep running them in parallel all year.</t>
         </is>
       </c>
       <c r="J6" s="37" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>Per HJ: run both marketing options together for the first 2 months to see which works.</t>
+          <t>Per management: run both marketing options together for the first 2 months to see which works.</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: directors will NOT draw a salary. Note for the bank — this understates the true cost of running the business, since two directors are working unpaid.</t>
+          <t>Per management: directors will NOT draw a salary. Note for the bank — this understates the true cost of running the business, since two directors are working unpaid.</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: 1 person.</t>
+          <t>Per management: 1 person.</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: AED 3,000/month.</t>
+          <t>Per management: AED 3,000/month.</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: 2–4 persons.</t>
+          <t>Per management: 2–4 persons.</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: AED 500–700 per person.</t>
+          <t>Per management: AED 500–700 per person.</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="G31" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: 4–6 persons.</t>
+          <t>Per management: 4–6 persons.</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: AED 180–300 per person.</t>
+          <t>Per management: AED 180–300 per person.</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: AED 1,350–1,500.</t>
+          <t>Per management: AED 1,350–1,500.</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
-          <t>Not in HJ's original list but unavoidable — a physical room needs connectivity and machines.</t>
+          <t>Not in the original brief but unavoidable — a physical room needs connectivity and machines.</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
-          <t>Not in HJ's original list. 4–6 people in a physical room with no supervisor will drift. Recommend keeping this.</t>
+          <t>Not in the original brief. 4–6 people in a physical room with no supervisor will drift. Recommend keeping this.</t>
         </is>
       </c>
     </row>
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
-          <t>Not in HJ's original list. Engaging staff outside the UAE needs a compliant contracting route. Flagging it rather than pretending it is free.</t>
+          <t>Not in the original brief. Engaging staff outside the UAE needs a compliant contracting route. Flagging it rather than pretending it is free.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>5.  UNIT-ACQUISITION COMMISSION  —  the 2% per HJ</t>
+          <t>5.  UNIT-ACQUISITION COMMISSION  —  the 2% per management</t>
         </is>
       </c>
       <c r="B38" s="5" t="n"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: 2% for each unit signed, ONGOING on that unit's monthly revenue.</t>
+          <t>Per management: 2% for each unit signed, ONGOING on that unit's monthly revenue.</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
+    <row r="45" ht="33" customHeight="1">
       <c r="A45" s="41" t="inlineStr">
         <is>
           <t>AI subscriptions</t>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
-          <t>Per HJ item 5. Base links live to the 'AI Subscriptions' tab. Low = trimmed stack; High = full stack plus extra seats as the marketing team scales.</t>
+          <t>Per management (marketing/technology brief, item 5). Base links live to the 'AI Subscriptions' tab. Low = trimmed stack; High = full stack plus extra seats as the marketing team scales.</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Per HJ: one unit only. Multiply on the 'Unit Setup' tab for portfolio scale.</t>
+          <t>Per management: one unit only. Multiply on the 'Unit Setup' tab for portfolio scale.</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>Actual figure supplied by HJ — AED 137.</t>
+          <t>Actual figure supplied by management — AED 137.</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>Actual figure supplied by HJ — AED 387 for 3 years.</t>
+          <t>Actual figure supplied by management — AED 387 for 3 years.</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K25" s="21" t="inlineStr">
         <is>
-          <t>One-off build of the AI operating layer. The recurring subscription cost sits in OPEX per HJ item 5.</t>
+          <t>One-off build of the AI operating layer. The recurring subscription cost sits in OPEX per management item 5.</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="K51" s="36" t="inlineStr">
         <is>
-          <t>Links to 'Unit Setup (1 Unit)'. Per HJ, sized for one unit only.</t>
+          <t>Links to 'Unit Setup (1 Unit)'. Per management, sized for one unit only.</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="63" t="inlineStr">
         <is>
-          <t>Per HJ, the CAPEX total is built for ONE unit. This table shows what the same unit-setup cost becomes at portfolio scale, against the Business Profile's 70–80 unit Year-1 target.</t>
+          <t>Per management, the CAPEX total is built for ONE unit. This table shows what the same unit-setup cost becomes at portfolio scale, against the Business Profile's 70–80 unit Year-1 target.</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       <c r="E5" s="17" t="n"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>Understated by design: directors work unpaid per HJ. One ops person for a 70–80 unit portfolio is thin — see the notes below.</t>
+          <t>Understated by design: directors work unpaid per management. One ops person for a 70–80 unit portfolio is thin — see the notes below.</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t>Part fixed (AI, Workspace, website), part per-unit (PMS, pricing, locks). Includes HJ item 5.</t>
+          <t>Part fixed (AI, Workspace, website), part per-unit (PMS, pricing, locks). Includes the AI subscriptions specified by management.</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B12" s="70" t="inlineStr">
         <is>
-          <t>Both run M1–M2 per HJ</t>
+          <t>Both run M1–M2 per management</t>
         </is>
       </c>
       <c r="C12" s="77">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="B13" s="70" t="inlineStr">
         <is>
-          <t>Both run M1–M2 per HJ</t>
+          <t>Both run M1–M2 per management</t>
         </is>
       </c>
       <c r="C13" s="77">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="B16" s="70" t="inlineStr">
         <is>
-          <t>Per HJ — nil</t>
+          <t>Per management — nil</t>
         </is>
       </c>
       <c r="C16" s="22">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="B17" s="70" t="inlineStr">
         <is>
-          <t>Per HJ — 1 x AED 3,000</t>
+          <t>Per management — 1 x AED 3,000</t>
         </is>
       </c>
       <c r="C17" s="22">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="B32" s="70" t="inlineStr">
         <is>
-          <t>Per HJ</t>
+          <t>Per management</t>
         </is>
       </c>
       <c r="C32" s="81">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="B33" s="70" t="inlineStr">
         <is>
-          <t>Added by Claude</t>
+          <t>Not in original brief</t>
         </is>
       </c>
       <c r="C33" s="81">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="B34" s="70" t="inlineStr">
         <is>
-          <t>Added by Claude</t>
+          <t>Not in original brief</t>
         </is>
       </c>
       <c r="C34" s="81">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="B36" s="70" t="inlineStr">
         <is>
-          <t>Added by Claude</t>
+          <t>Not in original brief</t>
         </is>
       </c>
       <c r="C36" s="81">
@@ -9707,7 +9707,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>D.  UNIT-ACQUISITION COMMISSION  —  the 2% per HJ, ongoing</t>
+          <t>D.  UNIT-ACQUISITION COMMISSION  —  the 2% per management, ongoing</t>
         </is>
       </c>
       <c r="B39" s="5" t="n"/>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="B47" s="70" t="inlineStr">
         <is>
-          <t>Per HJ — see 'AI Subscriptions' tab</t>
+          <t>Per management — see 'AI Subscriptions' tab</t>
         </is>
       </c>
       <c r="C47" s="82">
@@ -12650,7 +12650,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Both options run in parallel for Months 1–2 per HJ. This tab is what you use to pick one.</t>
+          <t>Both options run in parallel for Months 1–2 per management. This tab is what you use to pick one.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
-          <t>Both at 4 hours per day per HJ.</t>
+          <t>Both at 4 hours per day per management.</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="G22" s="36" t="inlineStr">
         <is>
-          <t>The total price of the experiment HJ described.</t>
+          <t>The total price of the experiment specified by management.</t>
         </is>
       </c>
     </row>

--- a/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
+++ b/orizuru/Orizuru_CAPEX_OPEX_Model.xlsx
@@ -1329,7 +1329,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
+    <row r="47" ht="26" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>•</t>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Unit furnishing AND unit setup. Both are funded by the property owner under this model.</t>
+          <t>Unit furnishing, unit setup, AND all recurring unit costs — permit renewals, housekeeping, consumables, maintenance and linen. All are borne by the property owner under this model.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="15">
         <f>'OPEX Summary'!B14</f>
-        <v>713738.0145</v>
+        <v>507497.0145</v>
       </c>
       <c r="D12" s="17" t="n"/>
       <c r="E12" s="21" t="inlineStr">
@@ -2591,7 +2591,7 @@
       <c r="B13" s="17" t="n"/>
       <c r="C13" s="22">
         <f>C12/12</f>
-        <v>59478.16787500001</v>
+        <v>42291.417875</v>
       </c>
       <c r="D13" s="17" t="n"/>
       <c r="E13" s="21" t="inlineStr">
@@ -2609,7 +2609,7 @@
       <c r="B14" s="17" t="n"/>
       <c r="C14" s="15">
         <f>'OPEX Monthly'!N89</f>
-        <v>113117.816875</v>
+        <v>73109.316875</v>
       </c>
       <c r="D14" s="17" t="n"/>
       <c r="E14" s="21" t="inlineStr">
@@ -2692,7 +2692,7 @@
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="22">
         <f>C12</f>
-        <v>713738.0145</v>
+        <v>507497.0145</v>
       </c>
       <c r="D20" s="17" t="n"/>
       <c r="E20" s="21" t="inlineStr"/>
@@ -2706,7 +2706,7 @@
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="25">
         <f>C19-C20</f>
-        <v>157293.98549999995</v>
+        <v>363534.9855</v>
       </c>
       <c r="D21" s="17" t="n"/>
       <c r="E21" s="21" t="inlineStr">
@@ -2724,7 +2724,7 @@
       <c r="B22" s="17" t="n"/>
       <c r="C22" s="26">
         <f>IF(C19=0,0,C20/C19)</f>
-        <v>0.819416524880831</v>
+        <v>0.5826387715950734</v>
       </c>
       <c r="D22" s="17" t="n"/>
       <c r="E22" s="21" t="inlineStr">
@@ -2753,7 +2753,7 @@
       <c r="B25" s="17" t="n"/>
       <c r="C25" s="15">
         <f>MIN(0,MIN('OPEX Monthly'!C95:N95))</f>
-        <v>-44429.97149999999</v>
+        <v>-37759.226624999996</v>
       </c>
       <c r="D25" s="17" t="n"/>
       <c r="E25" s="21" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C27" s="22">
         <f>(ABS(C25)+C26)*B27</f>
-        <v>31287.274299999997</v>
+        <v>29953.125324999997</v>
       </c>
       <c r="D27" s="17" t="n"/>
       <c r="E27" s="16" t="inlineStr">
@@ -2805,7 +2805,7 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="19">
         <f>ABS(C25)+C26+C27</f>
-        <v>187723.64579999997</v>
+        <v>179718.75194999998</v>
       </c>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
@@ -2836,7 +2836,7 @@
       <c r="B30" s="30" t="n"/>
       <c r="C30" s="31">
         <f>C29-C28</f>
-        <v>12276.35420000003</v>
+        <v>20281.248050000024</v>
       </c>
       <c r="D30" s="30" t="n"/>
       <c r="E30" s="32" t="inlineStr">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="47" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
         <is>
-          <t>•  MOST UNIT-LEVEL OPEX IS RE-CHARGEABLE. Housekeeping, DET permit renewals and consumables are commonly billed to the owner or the guest. Set those assumptions to 0 if your management contracts pass them through — it changes the OPEX total substantially.</t>
+          <t>•  ALL RECURRING UNIT COSTS ARE RE-CHARGED TO THE OWNER. Permit renewals, housekeeping, consumables, maintenance and linen are nil in Orizuru's P&amp;L. That is worth roughly AED 196,000 in Year 1 and far more later, so it MUST be written into the management agreement before owners are signed. The Assumptions tab retains the rates so you can price recovery failure; the High scenario stresses 25% leakage.</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
+    <row r="32" ht="33" customHeight="1">
       <c r="A32" s="36" t="inlineStr">
         <is>
           <t>Unit operations (permits, cleaning, consumables, maintenance, linen)</t>
@@ -3698,27 +3698,27 @@
       </c>
       <c r="B32" s="15">
         <f>'OPEX Monthly'!O63</f>
-        <v>196420.00000000003</v>
+        <v>0</v>
       </c>
       <c r="C32" s="42">
-        <f>C8*(Assumptions!$F$55/12+Assumptions!$F$56+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59)*(1+C10)^(1)</f>
-        <v>703248.0000000001</v>
+        <f>C8*(Assumptions!$F$56/12+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59+Assumptions!$F$60)*Assumptions!$F$55*(1+C10)^(1)</f>
+        <v>0</v>
       </c>
       <c r="D32" s="42">
-        <f>D8*(Assumptions!$F$55/12+Assumptions!$F$56+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59)*(1+D10)^(2)</f>
-        <v>1079653.1200000003</v>
+        <f>D8*(Assumptions!$F$56/12+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59+Assumptions!$F$60)*Assumptions!$F$55*(1+D10)^(2)</f>
+        <v>0</v>
       </c>
       <c r="E32" s="42">
-        <f>E8*(Assumptions!$F$55/12+Assumptions!$F$56+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59)*(1+E10)^(3)</f>
-        <v>1448824.8320000004</v>
+        <f>E8*(Assumptions!$F$56/12+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59+Assumptions!$F$60)*Assumptions!$F$55*(1+E10)^(3)</f>
+        <v>0</v>
       </c>
       <c r="F32" s="42">
-        <f>F8*(Assumptions!$F$55/12+Assumptions!$F$56+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59)*(1+F10)^(4)</f>
-        <v>1770463.9447040006</v>
+        <f>F8*(Assumptions!$F$56/12+Assumptions!$F$57+Assumptions!$F$58+Assumptions!$F$59+Assumptions!$F$60)*Assumptions!$F$55*(1+F10)^(4)</f>
+        <v>0</v>
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>Scales directly with the portfolio. Much of it is re-chargeable to owners — see the note at the foot of this tab.</t>
+          <t>NIL — re-charged to the property owner. Governed by the 'share of recurring unit costs borne by Orizuru' input on the Assumptions tab, currently 0%.</t>
         </is>
       </c>
     </row>
@@ -3794,23 +3794,23 @@
       </c>
       <c r="B35" s="55">
         <f>B32+B33+B34</f>
-        <v>317273.20000000007</v>
+        <v>120853.20000000001</v>
       </c>
       <c r="C35" s="55">
         <f>C32+C33+C34</f>
-        <v>1133356.56</v>
+        <v>430108.56</v>
       </c>
       <c r="D35" s="55">
         <f>D32+D33+D34</f>
-        <v>1736040.9448000004</v>
+        <v>656387.8248000001</v>
       </c>
       <c r="E35" s="55">
         <f>E32+E33+E34</f>
-        <v>2324430.2249600003</v>
+        <v>875605.3929600001</v>
       </c>
       <c r="F35" s="55">
         <f>F32+F33+F34</f>
-        <v>2834130.517133841</v>
+        <v>1063666.5724298402</v>
       </c>
       <c r="G35" s="21" t="inlineStr"/>
     </row>
@@ -3822,23 +3822,23 @@
       </c>
       <c r="B36" s="57">
         <f>B30-B35</f>
-        <v>553758.7999999999</v>
+        <v>750178.8</v>
       </c>
       <c r="C36" s="57">
         <f>C30-C35</f>
-        <v>1606979.04</v>
+        <v>2310227.04</v>
       </c>
       <c r="D36" s="57">
         <f>D30-D35</f>
-        <v>2392684.8032</v>
+        <v>3472337.9232000005</v>
       </c>
       <c r="E36" s="57">
         <f>E30-E35</f>
-        <v>3122595.3246400002</v>
+        <v>4571420.156640001</v>
       </c>
       <c r="F36" s="57">
         <f>F30-F35</f>
-        <v>3729431.67961456</v>
+        <v>5499895.624318561</v>
       </c>
       <c r="G36" s="32" t="inlineStr"/>
     </row>
@@ -3850,23 +3850,23 @@
       </c>
       <c r="B37" s="58">
         <f>IF(B30=0,0,B36/B30)</f>
-        <v>0.6357502365010699</v>
+        <v>0.8612528586779821</v>
       </c>
       <c r="C37" s="58">
         <f>IF(C30=0,0,C36/C30)</f>
-        <v>0.5864168753637328</v>
+        <v>0.8430452970796716</v>
       </c>
       <c r="D37" s="58">
         <f>IF(D30=0,0,D36/D30)</f>
-        <v>0.5795213703305535</v>
+        <v>0.8410192720797788</v>
       </c>
       <c r="E37" s="58">
         <f>IF(E30=0,0,E36/E30)</f>
-        <v>0.5732661424489383</v>
+        <v>0.8392507277619986</v>
       </c>
       <c r="F37" s="58">
         <f>IF(F30=0,0,F36/F30)</f>
-        <v>0.5682023827643663</v>
+        <v>0.8379437048746514</v>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
@@ -3921,23 +3921,23 @@
       </c>
       <c r="B40" s="15">
         <f>'OPEX Summary'!B14-B32-B33-B34-B39</f>
-        <v>332222.81450000004</v>
+        <v>322401.8145</v>
       </c>
       <c r="C40" s="42">
         <f>B40*(1+C10)*(1+$B$17*IF(B7=0,0,C7/B7-1))</f>
-        <v>683093.6768171804</v>
+        <v>662900.4128171803</v>
       </c>
       <c r="D40" s="42">
         <f>C40*(1+D10)*(1+$B$17*IF(C7=0,0,D7/C7-1))</f>
-        <v>845735.0284403185</v>
+        <v>820733.8444403184</v>
       </c>
       <c r="E40" s="42">
         <f>D40*(1+E10)*(1+$B$17*IF(D7=0,0,E7/D7-1))</f>
-        <v>981707.3955934331</v>
+        <v>952686.6663980781</v>
       </c>
       <c r="F40" s="42">
         <f>E40*(1+F10)*(1+$B$17*IF(E7=0,0,F7/E7-1))</f>
-        <v>1092443.9898163725</v>
+        <v>1060149.7223677814</v>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -3953,23 +3953,23 @@
       </c>
       <c r="B41" s="55">
         <f>B39+B40</f>
-        <v>396464.81450000004</v>
+        <v>386643.8145</v>
       </c>
       <c r="C41" s="55">
         <f>C39+C40</f>
-        <v>816717.0368171803</v>
+        <v>796523.7728171803</v>
       </c>
       <c r="D41" s="55">
         <f>D39+D40</f>
-        <v>1077348.8524403186</v>
+        <v>1052347.6684403184</v>
       </c>
       <c r="E41" s="55">
         <f>E39+E40</f>
-        <v>1270761.4479454332</v>
+        <v>1241740.7187500782</v>
       </c>
       <c r="F41" s="55">
         <f>F39+F40</f>
-        <v>1443162.9066701327</v>
+        <v>1410868.6392215416</v>
       </c>
       <c r="G41" s="21" t="inlineStr"/>
     </row>
@@ -3981,23 +3981,23 @@
       </c>
       <c r="B42" s="57">
         <f>B36-B41</f>
-        <v>157293.9854999999</v>
+        <v>363534.98550000007</v>
       </c>
       <c r="C42" s="57">
         <f>C36-C41</f>
-        <v>790262.0031828197</v>
+        <v>1513703.2671828198</v>
       </c>
       <c r="D42" s="57">
         <f>D36-D41</f>
-        <v>1315335.9507596814</v>
+        <v>2419990.2547596823</v>
       </c>
       <c r="E42" s="57">
         <f>E36-E41</f>
-        <v>1851833.876694567</v>
+        <v>3329679.4378899224</v>
       </c>
       <c r="F42" s="57">
         <f>F36-F41</f>
-        <v>2286268.7729444276</v>
+        <v>4089026.985097019</v>
       </c>
       <c r="G42" s="32" t="inlineStr">
         <is>
@@ -4013,23 +4013,23 @@
       </c>
       <c r="B43" s="60">
         <f>IF(B30=0,0,B42/B30)</f>
-        <v>0.18058347511916886</v>
+        <v>0.4173612284049266</v>
       </c>
       <c r="C43" s="60">
         <f>IF(C30=0,0,C42/C30)</f>
-        <v>0.28838146801538456</v>
+        <v>0.552378791554881</v>
       </c>
       <c r="D43" s="60">
         <f>IF(D30=0,0,D42/D30)</f>
-        <v>0.3185815748107862</v>
+        <v>0.5861349003217159</v>
       </c>
       <c r="E43" s="60">
         <f>IF(E30=0,0,E42/E30)</f>
-        <v>0.339971578952949</v>
+        <v>0.6112839764694028</v>
       </c>
       <c r="F43" s="60">
         <f>IF(F30=0,0,F42/F30)</f>
-        <v>0.34832743324608834</v>
+        <v>0.6229889902045461</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -4109,23 +4109,23 @@
       </c>
       <c r="B46" s="55">
         <f>B42-B45</f>
-        <v>119958.51883333322</v>
+        <v>326199.5188333334</v>
       </c>
       <c r="C46" s="55">
         <f>C42-C45</f>
-        <v>752926.536516153</v>
+        <v>1476367.8005161532</v>
       </c>
       <c r="D46" s="55">
         <f>D42-D45</f>
-        <v>1278000.4840930148</v>
+        <v>2382654.7880930156</v>
       </c>
       <c r="E46" s="55">
         <f>E42-E45</f>
-        <v>1851833.876694567</v>
+        <v>3329679.4378899224</v>
       </c>
       <c r="F46" s="55">
         <f>F42-F45</f>
-        <v>2286268.7729444276</v>
+        <v>4089026.985097019</v>
       </c>
       <c r="G46" s="21" t="inlineStr"/>
     </row>
@@ -4137,23 +4137,23 @@
       </c>
       <c r="B47" s="42">
         <f>B46</f>
-        <v>119958.51883333322</v>
+        <v>326199.5188333334</v>
       </c>
       <c r="C47" s="42">
         <f>C46</f>
-        <v>752926.536516153</v>
+        <v>1476367.8005161532</v>
       </c>
       <c r="D47" s="42">
         <f>D46</f>
-        <v>1278000.4840930148</v>
+        <v>2382654.7880930156</v>
       </c>
       <c r="E47" s="42">
         <f>E46</f>
-        <v>1851833.876694567</v>
+        <v>3329679.4378899224</v>
       </c>
       <c r="F47" s="42">
         <f>F46</f>
-        <v>2286268.7729444276</v>
+        <v>4089026.985097019</v>
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
@@ -4173,19 +4173,19 @@
       </c>
       <c r="C48" s="42">
         <f>-MAX(0,(C47-375000)*0.09)</f>
-        <v>-34013.38828645377</v>
+        <v>-99123.10204645379</v>
       </c>
       <c r="D48" s="42">
         <f>-MAX(0,(D47-375000)*0.09)</f>
-        <v>-81270.04356837133</v>
+        <v>-180688.93092837138</v>
       </c>
       <c r="E48" s="42">
         <f>-MAX(0,(E47-375000)*0.09)</f>
-        <v>-132915.04890251101</v>
+        <v>-265921.149410093</v>
       </c>
       <c r="F48" s="42">
         <f>-MAX(0,(F47-375000)*0.09)</f>
-        <v>-172014.18956499847</v>
+        <v>-334262.4286587317</v>
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
@@ -4201,23 +4201,23 @@
       </c>
       <c r="B49" s="57">
         <f>B47+B48</f>
-        <v>119958.51883333322</v>
+        <v>326199.5188333334</v>
       </c>
       <c r="C49" s="57">
         <f>C47+C48</f>
-        <v>718913.1482296992</v>
+        <v>1377244.6984696994</v>
       </c>
       <c r="D49" s="57">
         <f>D47+D48</f>
-        <v>1196730.4405246435</v>
+        <v>2201965.857164644</v>
       </c>
       <c r="E49" s="57">
         <f>E47+E48</f>
-        <v>1718918.827792056</v>
+        <v>3063758.288479829</v>
       </c>
       <c r="F49" s="57">
         <f>F47+F48</f>
-        <v>2114254.5833794293</v>
+        <v>3754764.5564382873</v>
       </c>
       <c r="G49" s="32" t="inlineStr"/>
     </row>
@@ -4229,23 +4229,23 @@
       </c>
       <c r="B50" s="58">
         <f>IF(B30=0,0,B49/B30)</f>
-        <v>0.13771999057822584</v>
+        <v>0.37449774386398366</v>
       </c>
       <c r="C50" s="58">
         <f>IF(C30=0,0,C49/C30)</f>
-        <v>0.2623449289312226</v>
+        <v>0.5025824933521643</v>
       </c>
       <c r="D50" s="58">
         <f>IF(D30=0,0,D49/D30)</f>
-        <v>0.28985467031913</v>
+        <v>0.5333281965340759</v>
       </c>
       <c r="E50" s="58">
         <f>IF(E30=0,0,E49/E30)</f>
-        <v>0.31557017901601064</v>
+        <v>0.5624644607559836</v>
       </c>
       <c r="F50" s="58">
         <f>IF(F30=0,0,F49/F30)</f>
-        <v>0.3221199891160983</v>
+        <v>0.5720620059482949</v>
       </c>
       <c r="G50" s="21" t="inlineStr"/>
     </row>
@@ -4307,23 +4307,23 @@
       </c>
       <c r="B53" s="42">
         <f>B42</f>
-        <v>157293.9854999999</v>
+        <v>363534.98550000007</v>
       </c>
       <c r="C53" s="42">
         <f>C42</f>
-        <v>790262.0031828197</v>
+        <v>1513703.2671828198</v>
       </c>
       <c r="D53" s="42">
         <f>D42</f>
-        <v>1315335.9507596814</v>
+        <v>2419990.2547596823</v>
       </c>
       <c r="E53" s="42">
         <f>E42</f>
-        <v>1851833.876694567</v>
+        <v>3329679.4378899224</v>
       </c>
       <c r="F53" s="42">
         <f>F42</f>
-        <v>2286268.7729444276</v>
+        <v>4089026.985097019</v>
       </c>
       <c r="G53" s="21" t="inlineStr"/>
     </row>
@@ -4339,19 +4339,19 @@
       </c>
       <c r="C54" s="42">
         <f>C48</f>
-        <v>-34013.38828645377</v>
+        <v>-99123.10204645379</v>
       </c>
       <c r="D54" s="42">
         <f>D48</f>
-        <v>-81270.04356837133</v>
+        <v>-180688.93092837138</v>
       </c>
       <c r="E54" s="42">
         <f>E48</f>
-        <v>-132915.04890251101</v>
+        <v>-265921.149410093</v>
       </c>
       <c r="F54" s="42">
         <f>F48</f>
-        <v>-172014.18956499847</v>
+        <v>-334262.4286587317</v>
       </c>
       <c r="G54" s="21" t="inlineStr"/>
     </row>
@@ -4423,23 +4423,23 @@
       </c>
       <c r="B57" s="57">
         <f>B53+B54+B55+B56</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="C57" s="57">
         <f>C53+C54+C55+C56</f>
-        <v>662783.4348963659</v>
+        <v>1321114.985136366</v>
       </c>
       <c r="D57" s="57">
         <f>D53+D54+D55+D56</f>
-        <v>1164646.39979131</v>
+        <v>2169881.816431311</v>
       </c>
       <c r="E57" s="57">
         <f>E53+E54+E55+E56</f>
-        <v>1653003.837712056</v>
+        <v>2997843.2983998293</v>
       </c>
       <c r="F57" s="57">
         <f>F53+F54+F55+F56</f>
-        <v>2058427.7510220092</v>
+        <v>3698937.724080867</v>
       </c>
       <c r="G57" s="32" t="inlineStr"/>
     </row>
@@ -4451,23 +4451,23 @@
       </c>
       <c r="B58" s="55">
         <f>B57</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="C58" s="55">
         <f>B58+C57</f>
-        <v>664519.4203963657</v>
+        <v>1529091.970636366</v>
       </c>
       <c r="D58" s="55">
         <f>C58+D57</f>
-        <v>1829165.8201876758</v>
+        <v>3698973.787067677</v>
       </c>
       <c r="E58" s="55">
         <f>D58+E57</f>
-        <v>3482169.657899732</v>
+        <v>6696817.085467506</v>
       </c>
       <c r="F58" s="55">
         <f>E58+F57</f>
-        <v>5540597.408921741</v>
+        <v>10395754.809548374</v>
       </c>
       <c r="G58" s="21" t="inlineStr"/>
     </row>
@@ -4479,23 +4479,23 @@
       </c>
       <c r="B59" s="61">
         <f>'Funding Summary'!C29+B58</f>
-        <v>201735.9854999999</v>
+        <v>407976.98550000007</v>
       </c>
       <c r="C59" s="61">
         <f>'Funding Summary'!C29+C58</f>
-        <v>864519.4203963657</v>
+        <v>1729091.970636366</v>
       </c>
       <c r="D59" s="61">
         <f>'Funding Summary'!C29+D58</f>
-        <v>2029165.8201876758</v>
+        <v>3898973.787067677</v>
       </c>
       <c r="E59" s="61">
         <f>'Funding Summary'!C29+E58</f>
-        <v>3682169.657899732</v>
+        <v>6896817.085467506</v>
       </c>
       <c r="F59" s="61">
         <f>'Funding Summary'!C29+F58</f>
-        <v>5740597.408921741</v>
+        <v>10595754.809548374</v>
       </c>
       <c r="G59" s="21" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B62" s="55">
         <f>F42*B22</f>
-        <v>9145075.09177771</v>
+        <v>16356107.940388076</v>
       </c>
       <c r="C62" s="17" t="n"/>
       <c r="D62" s="17" t="n"/>
@@ -4613,23 +4613,23 @@
       </c>
       <c r="C65" s="31">
         <f>B57</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="D65" s="31">
         <f>C57</f>
-        <v>662783.4348963659</v>
+        <v>1321114.985136366</v>
       </c>
       <c r="E65" s="31">
         <f>D57</f>
-        <v>1164646.39979131</v>
+        <v>2169881.816431311</v>
       </c>
       <c r="F65" s="31">
         <f>E57</f>
-        <v>1653003.837712056</v>
+        <v>2997843.2983998293</v>
       </c>
       <c r="G65" s="31">
         <f>F57+B62</f>
-        <v>11203502.84279972</v>
+        <v>20055045.664468944</v>
       </c>
       <c r="H65" s="30" t="n"/>
       <c r="I65" s="63" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B67" s="64">
         <f>IRR(B65:G65)</f>
-        <v>1.9227857292886679</v>
+        <v>2.997962995666256</v>
       </c>
       <c r="C67" s="17" t="n"/>
       <c r="D67" s="17" t="n"/>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B68" s="55">
         <f>NPV(B21,C65:G65)+B65</f>
-        <v>6235300.837025542</v>
+        <v>11651866.001823831</v>
       </c>
       <c r="C68" s="17" t="n"/>
       <c r="D68" s="17" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B69" s="65">
         <f>IF(B23=0,0,SUM(C65:G65)/B23)</f>
-        <v>73.42836250349725</v>
+        <v>133.75931374968226</v>
       </c>
       <c r="C69" s="17" t="n"/>
       <c r="D69" s="17" t="n"/>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B73" s="40">
         <f>IF(C42&lt;=0,0,(F42/C42)^(1/3)-1)</f>
-        <v>0.4249033073749562</v>
+        <v>0.39270694976411114</v>
       </c>
       <c r="C73" s="17" t="n"/>
       <c r="D73" s="17" t="n"/>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B74" s="40">
         <f>IF((B23+SUM(B49:E49))=0,0,F49/(B23+SUM(B49:E49)))</f>
-        <v>0.5346424049659023</v>
+        <v>0.5237378125814536</v>
       </c>
       <c r="C74" s="17" t="n"/>
       <c r="D74" s="17" t="n"/>
@@ -4888,23 +4888,23 @@
       </c>
       <c r="B78" s="42">
         <f>IF(B7=0,0,(B35+B41)/B7)</f>
-        <v>23401.24637704918</v>
+        <v>16639.24637704918</v>
       </c>
       <c r="C78" s="42">
         <f>IF(C7=0,0,(C35+C41)/C7)</f>
-        <v>18572.129493496956</v>
+        <v>11682.212693496955</v>
       </c>
       <c r="D78" s="42">
         <f>IF(D7=0,0,(D35+D41)/D7)</f>
-        <v>18150.901917679475</v>
+        <v>11024.099956389151</v>
       </c>
       <c r="E78" s="42">
         <f>IF(E7=0,0,(E35+E41)/E7)</f>
-        <v>17975.958364527167</v>
+        <v>10586.730558550391</v>
       </c>
       <c r="F78" s="42">
         <f>IF(F7=0,0,(F35+F41)/F7)</f>
-        <v>18201.248611931805</v>
+        <v>10529.937070856944</v>
       </c>
       <c r="G78" s="21" t="inlineStr">
         <is>
@@ -4920,23 +4920,23 @@
       </c>
       <c r="B79" s="42">
         <f>IF(B7=0,0,B42/B7)</f>
-        <v>5157.179852459013</v>
+        <v>11919.17985245902</v>
       </c>
       <c r="C79" s="42">
         <f>IF(C7=0,0,C42/C7)</f>
-        <v>7526.30479221733</v>
+        <v>14416.22159221733</v>
       </c>
       <c r="D79" s="42">
         <f>IF(D7=0,0,D42/D7)</f>
-        <v>8486.038391997945</v>
+        <v>15612.840353288273</v>
       </c>
       <c r="E79" s="42">
         <f>IF(E7=0,0,E42/E7)</f>
-        <v>9259.169383472836</v>
+        <v>16648.397189449614</v>
       </c>
       <c r="F79" s="42">
         <f>IF(F7=0,0,F42/F7)</f>
-        <v>9728.803289125224</v>
+        <v>17400.11483020008</v>
       </c>
       <c r="G79" s="21" t="inlineStr"/>
     </row>
@@ -4948,23 +4948,23 @@
       </c>
       <c r="B80" s="42">
         <f>IF(B7=0,0,B36/B7)</f>
-        <v>18156.026229508196</v>
+        <v>24596.0262295082</v>
       </c>
       <c r="C80" s="42">
         <f>IF(C7=0,0,C36/C7)</f>
-        <v>15304.562285714286</v>
+        <v>22002.162285714287</v>
       </c>
       <c r="D80" s="42">
         <f>IF(D7=0,0,D36/D7)</f>
-        <v>15436.67614967742</v>
+        <v>22402.180149677424</v>
       </c>
       <c r="E80" s="42">
         <f>IF(E7=0,0,E36/E7)</f>
-        <v>15612.976623200002</v>
+        <v>22857.100783200003</v>
       </c>
       <c r="F80" s="42">
         <f>IF(F7=0,0,F36/F7)</f>
-        <v>15869.922040913023</v>
+        <v>23403.811167313022</v>
       </c>
       <c r="G80" s="21" t="inlineStr">
         <is>
@@ -4980,23 +4980,23 @@
       </c>
       <c r="B81" s="67">
         <f>IF(B80&lt;=0,0,B41/B80)</f>
-        <v>21.836541184085927</v>
+        <v>15.719767530420745</v>
       </c>
       <c r="C81" s="67">
         <f>IF(C80&lt;=0,0,C41/C80)</f>
-        <v>53.364285862623284</v>
+        <v>36.202067891043264</v>
       </c>
       <c r="D81" s="67">
         <f>IF(D80&lt;=0,0,D41/D80)</f>
-        <v>69.79150446599425</v>
+        <v>46.975234615969796</v>
       </c>
       <c r="E81" s="67">
         <f>IF(E80&lt;=0,0,E41/E80)</f>
-        <v>81.39136300615178</v>
+        <v>54.326256445557576</v>
       </c>
       <c r="F81" s="67">
         <f>IF(F80&lt;=0,0,F41/F80)</f>
-        <v>90.93698777786214</v>
+        <v>60.28371315830962</v>
       </c>
       <c r="G81" s="21" t="inlineStr">
         <is>
@@ -5012,23 +5012,23 @@
       </c>
       <c r="B82" s="67">
         <f>B7-B81</f>
-        <v>8.663458815914073</v>
+        <v>14.780232469579255</v>
       </c>
       <c r="C82" s="67">
         <f>C7-C81</f>
-        <v>51.635714137376716</v>
+        <v>68.79793210895673</v>
       </c>
       <c r="D82" s="67">
         <f>D7-D81</f>
-        <v>85.20849553400575</v>
+        <v>108.0247653840302</v>
       </c>
       <c r="E82" s="67">
         <f>E7-E81</f>
-        <v>118.60863699384822</v>
+        <v>145.6737435544424</v>
       </c>
       <c r="F82" s="67">
         <f>F7-F81</f>
-        <v>144.06301222213784</v>
+        <v>174.7162868416904</v>
       </c>
       <c r="G82" s="21" t="inlineStr"/>
     </row>
@@ -5040,23 +5040,23 @@
       </c>
       <c r="B83" s="68">
         <f>IF(B41=0,0,B36/B41)</f>
-        <v>1.3967413494142489</v>
+        <v>1.9402322547694606</v>
       </c>
       <c r="C83" s="68">
         <f>IF(C41=0,0,C36/C41)</f>
-        <v>1.9676080791243706</v>
+        <v>2.9003868043123027</v>
       </c>
       <c r="D83" s="68">
         <f>IF(D41=0,0,D36/D41)</f>
-        <v>2.2209006839152377</v>
+        <v>3.2996109815554995</v>
       </c>
       <c r="E83" s="68">
         <f>IF(E41=0,0,E36/E41)</f>
-        <v>2.457263186327073</v>
+        <v>3.6814611034431883</v>
       </c>
       <c r="F83" s="68">
         <f>IF(F41=0,0,F36/F41)</f>
-        <v>2.58420699588214</v>
+        <v>3.898233663591228</v>
       </c>
       <c r="G83" s="21" t="inlineStr">
         <is>
@@ -5072,23 +5072,23 @@
       </c>
       <c r="B84" s="39">
         <f>IF(B41=0,0,B59/(B41/12))</f>
-        <v>6.106044565525999</v>
+        <v>12.662103058162337</v>
       </c>
       <c r="C84" s="39">
         <f>IF(C41=0,0,C59/(C41/12))</f>
-        <v>12.702359051043807</v>
+        <v>26.049572348920677</v>
       </c>
       <c r="D84" s="39">
         <f>IF(D41=0,0,D59/(D41/12))</f>
-        <v>22.601768950787473</v>
+        <v>44.46029277962484</v>
       </c>
       <c r="E84" s="39">
         <f>IF(E41=0,0,E59/(E41/12))</f>
-        <v>34.77130657861611</v>
+        <v>66.64982775866217</v>
       </c>
       <c r="F84" s="39">
         <f>IF(F41=0,0,F59/(F41/12))</f>
-        <v>47.73346694865308</v>
+        <v>90.12111700543292</v>
       </c>
       <c r="G84" s="21" t="inlineStr">
         <is>
@@ -5142,11 +5142,11 @@
       </c>
       <c r="B87" s="70">
         <f>IRR(I87:N87)</f>
-        <v>1.8722399292723741</v>
+        <v>2.9625521160732653</v>
       </c>
       <c r="C87" s="22">
         <f>NPV(B21,J87:N87)+I87</f>
-        <v>5316500.693577582</v>
+        <v>10008577.76514325</v>
       </c>
       <c r="D87" s="17" t="n"/>
       <c r="E87" s="17" t="n"/>
@@ -5162,23 +5162,23 @@
       </c>
       <c r="J87" s="71">
         <f>C65</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="K87" s="71">
         <f>D65</f>
-        <v>662783.4348963659</v>
+        <v>1321114.985136366</v>
       </c>
       <c r="L87" s="71">
         <f>E65</f>
-        <v>1164646.39979131</v>
+        <v>2169881.816431311</v>
       </c>
       <c r="M87" s="71">
         <f>F65</f>
-        <v>1653003.837712056</v>
+        <v>2997843.2983998293</v>
       </c>
       <c r="N87" s="71">
         <f>F57+F42*3.0</f>
-        <v>8917234.069855291</v>
+        <v>15966018.679371923</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -5189,11 +5189,11 @@
       </c>
       <c r="B88" s="73">
         <f>IRR(I88:N88)</f>
-        <v>1.9227857292886679</v>
+        <v>2.997962995666256</v>
       </c>
       <c r="C88" s="74">
         <f>NPV(B21,J88:N88)+I88</f>
-        <v>6235300.837025542</v>
+        <v>11651866.001823831</v>
       </c>
       <c r="D88" s="75" t="n"/>
       <c r="E88" s="75" t="n"/>
@@ -5205,23 +5205,23 @@
       </c>
       <c r="J88" s="71">
         <f>C65</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="K88" s="71">
         <f>D65</f>
-        <v>662783.4348963659</v>
+        <v>1321114.985136366</v>
       </c>
       <c r="L88" s="71">
         <f>E65</f>
-        <v>1164646.39979131</v>
+        <v>2169881.816431311</v>
       </c>
       <c r="M88" s="71">
         <f>F65</f>
-        <v>1653003.837712056</v>
+        <v>2997843.2983998293</v>
       </c>
       <c r="N88" s="71">
         <f>F57+F42*4.0</f>
-        <v>11203502.84279972</v>
+        <v>20055045.664468944</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -5232,11 +5232,11 @@
       </c>
       <c r="B89" s="70">
         <f>IRR(I89:N89)</f>
-        <v>1.9690874971684922</v>
+        <v>3.031570100560673</v>
       </c>
       <c r="C89" s="22">
         <f>NPV(B21,J89:N89)+I89</f>
-        <v>7154100.980473503</v>
+        <v>13295154.23850441</v>
       </c>
       <c r="D89" s="17" t="n"/>
       <c r="E89" s="17" t="n"/>
@@ -5252,23 +5252,23 @@
       </c>
       <c r="J89" s="71">
         <f>C65</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="K89" s="71">
         <f>D65</f>
-        <v>662783.4348963659</v>
+        <v>1321114.985136366</v>
       </c>
       <c r="L89" s="71">
         <f>E65</f>
-        <v>1164646.39979131</v>
+        <v>2169881.816431311</v>
       </c>
       <c r="M89" s="71">
         <f>F65</f>
-        <v>1653003.837712056</v>
+        <v>2997843.2983998293</v>
       </c>
       <c r="N89" s="71">
         <f>F57+F42*5.0</f>
-        <v>13489771.615744147</v>
+        <v>24144072.649565965</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
@@ -5279,11 +5279,11 @@
       </c>
       <c r="B90" s="70">
         <f>IRR(I90:N90)</f>
-        <v>1.6817126143467145</v>
+        <v>2.84265252609959</v>
       </c>
       <c r="C90" s="22">
         <f>NPV(B21,J90:N90)+I90</f>
-        <v>2560100.2632337017</v>
+        <v>5078713.055101511</v>
       </c>
       <c r="D90" s="17" t="n"/>
       <c r="E90" s="17" t="n"/>
@@ -5299,23 +5299,23 @@
       </c>
       <c r="J90" s="71">
         <f>C65</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="K90" s="71">
         <f>D65</f>
-        <v>662783.4348963659</v>
+        <v>1321114.985136366</v>
       </c>
       <c r="L90" s="71">
         <f>E65</f>
-        <v>1164646.39979131</v>
+        <v>2169881.816431311</v>
       </c>
       <c r="M90" s="71">
         <f>F65</f>
-        <v>1653003.837712056</v>
+        <v>2997843.2983998293</v>
       </c>
       <c r="N90" s="71">
         <f>F57+F42*0.0</f>
-        <v>2058427.7510220092</v>
+        <v>3698937.724080867</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -5326,11 +5326,11 @@
       </c>
       <c r="B91" s="73">
         <f>IRR(I91:N91)</f>
-        <v>1.9227857292886679</v>
+        <v>2.997962995666256</v>
       </c>
       <c r="C91" s="74">
         <f>NPV(B21,J91:N91)+I91</f>
-        <v>6235300.837025542</v>
+        <v>11651866.001823831</v>
       </c>
       <c r="D91" s="75" t="n"/>
       <c r="E91" s="75" t="n"/>
@@ -5346,23 +5346,23 @@
       </c>
       <c r="J91" s="71">
         <f>C65-(C6-B6)*'Unit Setup (1 Unit)'!E17*(0.0-$B$18)</f>
-        <v>1735.9854999998934</v>
+        <v>207976.98550000007</v>
       </c>
       <c r="K91" s="71">
         <f>D65-(D6-C6)*'Unit Setup (1 Unit)'!E17*(0.0-$B$18)</f>
-        <v>662783.4348963659</v>
+        <v>1321114.985136366</v>
       </c>
       <c r="L91" s="71">
         <f>E65-(E6-D6)*'Unit Setup (1 Unit)'!E17*(0.0-$B$18)</f>
-        <v>1164646.39979131</v>
+        <v>2169881.816431311</v>
       </c>
       <c r="M91" s="71">
         <f>F65-(F6-E6)*'Unit Setup (1 Unit)'!E17*(0.0-$B$18)</f>
-        <v>1653003.837712056</v>
+        <v>2997843.2983998293</v>
       </c>
       <c r="N91" s="71">
         <f>G65-(F6-E6)*'Unit Setup (1 Unit)'!E17*(0.0-$B$18)</f>
-        <v>11203502.84279972</v>
+        <v>20055045.664468944</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="B92" s="70">
         <f>IRR(I92:N92)</f>
-        <v>1.4834854135942042</v>
+        <v>2.422459756366848</v>
       </c>
       <c r="C92" s="22">
         <f>NPV(B21,J92:N92)+I92</f>
-        <v>5658445.898753937</v>
+        <v>11075011.063552227</v>
       </c>
       <c r="D92" s="17" t="n"/>
       <c r="E92" s="17" t="n"/>
@@ -5393,23 +5393,23 @@
       </c>
       <c r="J92" s="71">
         <f>C65-(C6-B6)*'Unit Setup (1 Unit)'!E17*(0.5-$B$18)</f>
-        <v>-227064.0145000001</v>
+        <v>-20823.014499999932</v>
       </c>
       <c r="K92" s="71">
         <f>D65-(D6-C6)*'Unit Setup (1 Unit)'!E17*(0.5-$B$18)</f>
-        <v>433983.43489636586</v>
+        <v>1092314.985136366</v>
       </c>
       <c r="L92" s="71">
         <f>E65-(E6-D6)*'Unit Setup (1 Unit)'!E17*(0.5-$B$18)</f>
-        <v>981606.3997913101</v>
+        <v>1986841.816431311</v>
       </c>
       <c r="M92" s="71">
         <f>F65-(F6-E6)*'Unit Setup (1 Unit)'!E17*(0.5-$B$18)</f>
-        <v>1515723.837712056</v>
+        <v>2860563.2983998293</v>
       </c>
       <c r="N92" s="71">
         <f>G65-(F6-E6)*'Unit Setup (1 Unit)'!E17*(0.5-$B$18)</f>
-        <v>11066222.84279972</v>
+        <v>19917765.664468944</v>
       </c>
     </row>
     <row r="93" ht="33" customHeight="1">
@@ -5420,11 +5420,11 @@
       </c>
       <c r="B93" s="70">
         <f>IRR(I93:N93)</f>
-        <v>1.1713758997774164</v>
+        <v>1.9811464431122205</v>
       </c>
       <c r="C93" s="22">
         <f>NPV(B21,J93:N93)+I93</f>
-        <v>5081590.960482332</v>
+        <v>10498156.12528062</v>
       </c>
       <c r="D93" s="17" t="n"/>
       <c r="E93" s="17" t="n"/>
@@ -5440,23 +5440,23 @@
       </c>
       <c r="J93" s="71">
         <f>C65-(C6-B6)*'Unit Setup (1 Unit)'!E17*(1.0-$B$18)</f>
-        <v>-455864.0145000001</v>
+        <v>-249623.01449999993</v>
       </c>
       <c r="K93" s="71">
         <f>D65-(D6-C6)*'Unit Setup (1 Unit)'!E17*(1.0-$B$18)</f>
-        <v>205183.43489636586</v>
+        <v>863514.985136366</v>
       </c>
       <c r="L93" s="71">
         <f>E65-(E6-D6)*'Unit Setup (1 Unit)'!E17*(1.0-$B$18)</f>
-        <v>798566.3997913101</v>
+        <v>1803801.816431311</v>
       </c>
       <c r="M93" s="71">
         <f>F65-(F6-E6)*'Unit Setup (1 Unit)'!E17*(1.0-$B$18)</f>
-        <v>1378443.837712056</v>
+        <v>2723283.2983998293</v>
       </c>
       <c r="N93" s="71">
         <f>G65-(F6-E6)*'Unit Setup (1 Unit)'!E17*(1.0-$B$18)</f>
-        <v>10928942.84279972</v>
+        <v>19780485.664468944</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -5507,10 +5507,10 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="34" customHeight="1">
+    <row r="101" ht="47" customHeight="1">
       <c r="A101" s="33" t="inlineStr">
         <is>
-          <t>•  RE-CHARGEABLE COSTS ARE THE BIGGEST SINGLE LEVER. Housekeeping, DET permit renewals and consumables are all commonly billed to owners or guests. They sit in variable costs here. Re-charging them materially lifts EBITDA at no commercial cost — it is standard Dubai practice.</t>
+          <t>•  THE OWNER BEARS EVERY RECURRING UNIT COST. Permit renewals, housekeeping, consumables, maintenance and linen are all re-charged, so Orizuru's variable cost is limited to per-unit software and the 2% commission. That produces a very high gross margin — expect a lender to test it. Have the management agreement ready to show.</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6912,7 +6912,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>8.  UNIT OPERATIONS  —  variable, per LIVE unit per month</t>
+          <t>8.  UNIT OPERATIONS  —  recurring per-unit costs, RE-CHARGED TO THE OWNER</t>
         </is>
       </c>
       <c r="B54" s="5" t="n"/>
@@ -6922,70 +6922,70 @@
       <c r="F54" s="5" t="n"/>
       <c r="G54" s="5" t="n"/>
     </row>
-    <row r="55" ht="22" customHeight="1">
+    <row r="55" ht="66" customHeight="1">
       <c r="A55" s="82" t="inlineStr">
         <is>
+          <t>Share of recurring unit costs borne by Orizuru</t>
+        </is>
+      </c>
+      <c r="B55" s="83" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C55" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F55" s="73">
+        <f>INDEX(C55:E55,1,Assumptions!$B$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED: all five costs below are borne by the property owner, so at 0% none of them reach Orizuru's P&amp;L. The rates are retained as documentation of what the pass-through is worth and to price the risk of recovery failing. The High scenario carries 25% as a stress case — leakage on unsold nights, owner stays, damage disputes and slow-paying owners. Set High to 0 as well if you want the scenario range to assume perfect recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="82" t="inlineStr">
+        <is>
           <t>DET holiday-home permit renewal</t>
         </is>
       </c>
-      <c r="B55" s="83" t="inlineStr">
+      <c r="B56" s="83" t="inlineStr">
         <is>
           <t>AED/unit/yr</t>
         </is>
       </c>
-      <c r="C55" s="84" t="n">
+      <c r="C56" s="84" t="n">
         <v>1200</v>
       </c>
-      <c r="D55" s="84" t="n">
+      <c r="D56" s="84" t="n">
         <v>1520</v>
       </c>
-      <c r="E55" s="84" t="n">
+      <c r="E56" s="84" t="n">
         <v>1800</v>
-      </c>
-      <c r="F55" s="85">
-        <f>INDEX(C55:E55,1,Assumptions!$B$5)</f>
-        <v>1520</v>
-      </c>
-      <c r="G55" s="21" t="inlineStr">
-        <is>
-          <t>Accrued monthly at 1/12. Re-chargeable to the owner in most contracts — if you re-charge, set this to 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="33" customHeight="1">
-      <c r="A56" s="82" t="inlineStr">
-        <is>
-          <t>Housekeeping &amp; laundry — net of guest recharge</t>
-        </is>
-      </c>
-      <c r="B56" s="83" t="inlineStr">
-        <is>
-          <t>AED/unit/mo</t>
-        </is>
-      </c>
-      <c r="C56" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="84" t="n">
-        <v>180</v>
-      </c>
-      <c r="E56" s="84" t="n">
-        <v>420</v>
       </c>
       <c r="F56" s="85">
         <f>INDEX(C56:E56,1,Assumptions!$B$5)</f>
-        <v>180</v>
+        <v>1520</v>
       </c>
       <c r="G56" s="21" t="inlineStr">
         <is>
-          <t>Cleaning fees are normally charged to the guest and pass straight through. This line is the RESIDUAL Orizuru absorbs on unsold nights, owner stays and disputes. Genuinely 0 if you recharge everything.</t>
+          <t>Owner-borne. A licence attached to the owner's property; they fund the first issue, so they fund renewals.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="82" t="inlineStr">
         <is>
-          <t>Guest consumables &amp; amenities</t>
+          <t>Housekeeping &amp; laundry</t>
         </is>
       </c>
       <c r="B57" s="83" t="inlineStr">
@@ -6994,28 +6994,28 @@
         </is>
       </c>
       <c r="C57" s="84" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="D57" s="84" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E57" s="84" t="n">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="F57" s="85">
         <f>INDEX(C57:E57,1,Assumptions!$B$5)</f>
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="G57" s="21" t="inlineStr">
         <is>
-          <t>Toiletries, coffee, water, welcome items. The Japanese-hospitality positioning makes this a brand cost, not a cost to strip out.</t>
+          <t>Owner-borne. Recovered through the cleaning fee charged to the guest on every booking.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="82" t="inlineStr">
         <is>
-          <t>Maintenance coordination &amp; petty repairs</t>
+          <t>Guest consumables &amp; amenities</t>
         </is>
       </c>
       <c r="B58" s="83" t="inlineStr">
@@ -7024,101 +7024,101 @@
         </is>
       </c>
       <c r="C58" s="84" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D58" s="84" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E58" s="84" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F58" s="85">
         <f>INDEX(C58:E58,1,Assumptions!$B$5)</f>
+        <v>100</v>
+      </c>
+      <c r="G58" s="21" t="inlineStr">
+        <is>
+          <t>Owner-borne. Toiletries, coffee, water, welcome items — normally bundled into the cleaning fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="33" customHeight="1">
+      <c r="A59" s="82" t="inlineStr">
+        <is>
+          <t>Maintenance &amp; petty repairs</t>
+        </is>
+      </c>
+      <c r="B59" s="83" t="inlineStr">
+        <is>
+          <t>AED/unit/mo</t>
+        </is>
+      </c>
+      <c r="C59" s="84" t="n">
+        <v>40</v>
+      </c>
+      <c r="D59" s="84" t="n">
         <v>90</v>
       </c>
-      <c r="G58" s="21" t="inlineStr">
-        <is>
-          <t>Orizuru's coordination cost. Major repairs are billed to the owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="82" t="inlineStr">
-        <is>
-          <t>Linen &amp; towel replacement</t>
-        </is>
-      </c>
-      <c r="B59" s="83" t="inlineStr">
-        <is>
-          <t>AED/unit/mo</t>
-        </is>
-      </c>
-      <c r="C59" s="84" t="n">
-        <v>20</v>
-      </c>
-      <c r="D59" s="84" t="n">
-        <v>40</v>
-      </c>
       <c r="E59" s="84" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="F59" s="85">
         <f>INDEX(C59:E59,1,Assumptions!$B$5)</f>
+        <v>90</v>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>Owner-borne. Repairs to the owner's asset are billed to the owner. Orizuru's coordination TIME is already carried in staff costs, so nothing is lost by excluding this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="82" t="inlineStr">
+        <is>
+          <t>Linen &amp; towel replacement</t>
+        </is>
+      </c>
+      <c r="B60" s="83" t="inlineStr">
+        <is>
+          <t>AED/unit/mo</t>
+        </is>
+      </c>
+      <c r="C60" s="84" t="n">
+        <v>20</v>
+      </c>
+      <c r="D60" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G59" s="21" t="inlineStr">
-        <is>
-          <t>Replacement cycle on the par stock bought at CAPEX. Real and routinely forgotten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="E60" s="84" t="n">
+        <v>70</v>
+      </c>
+      <c r="F60" s="85">
+        <f>INDEX(C60:E60,1,Assumptions!$B$5)</f>
+        <v>40</v>
+      </c>
+      <c r="G60" s="21" t="inlineStr">
+        <is>
+          <t>Owner-borne. Replacement of the owner's own par stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>9.  OFFICE &amp; ADMINISTRATION  —  Dubai</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="82" t="inlineStr">
-        <is>
-          <t>Office rent / registered address</t>
-        </is>
-      </c>
-      <c r="B61" s="83" t="inlineStr">
-        <is>
-          <t>AED/month</t>
-        </is>
-      </c>
-      <c r="C61" s="84" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D61" s="84" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E61" s="84" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F61" s="85">
-        <f>INDEX(C61:E61,1,Assumptions!$B$5)</f>
-        <v>2500</v>
-      </c>
-      <c r="G61" s="21" t="inlineStr">
-        <is>
-          <t>Fronds Building – Office 02. Required to hold the trade licence.</t>
-        </is>
-      </c>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="82" t="inlineStr">
         <is>
-          <t>Office DEWA, internet &amp; chiller</t>
+          <t>Office rent / registered address</t>
         </is>
       </c>
       <c r="B62" s="83" t="inlineStr">
@@ -7127,28 +7127,28 @@
         </is>
       </c>
       <c r="C62" s="84" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="D62" s="84" t="n">
-        <v>520</v>
+        <v>2500</v>
       </c>
       <c r="E62" s="84" t="n">
-        <v>900</v>
+        <v>4200</v>
       </c>
       <c r="F62" s="85">
         <f>INDEX(C62:E62,1,Assumptions!$B$5)</f>
-        <v>520</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="21" t="inlineStr">
         <is>
-          <t>Office only. Unit utilities sit with the owner under the commission-only model.</t>
+          <t>Fronds Building – Office 02. Required to hold the trade licence.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="82" t="inlineStr">
         <is>
-          <t>Mobile &amp; telephone</t>
+          <t>Office DEWA, internet &amp; chiller</t>
         </is>
       </c>
       <c r="B63" s="83" t="inlineStr">
@@ -7157,28 +7157,28 @@
         </is>
       </c>
       <c r="C63" s="84" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D63" s="84" t="n">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="E63" s="84" t="n">
-        <v>420</v>
+        <v>900</v>
       </c>
       <c r="F63" s="85">
         <f>INDEX(C63:E63,1,Assumptions!$B$5)</f>
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="G63" s="21" t="inlineStr">
         <is>
-          <t>Includes the dedicated 24/7 guest line.</t>
+          <t>Office only. Unit utilities sit with the owner under the commission-only model.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="82" t="inlineStr">
         <is>
-          <t>Transport, fuel, Salik &amp; parking</t>
+          <t>Mobile &amp; telephone</t>
         </is>
       </c>
       <c r="B64" s="83" t="inlineStr">
@@ -7187,28 +7187,28 @@
         </is>
       </c>
       <c r="C64" s="84" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="D64" s="84" t="n">
-        <v>1100</v>
+        <v>260</v>
       </c>
       <c r="E64" s="84" t="n">
-        <v>2200</v>
+        <v>420</v>
       </c>
       <c r="F64" s="85">
         <f>INDEX(C64:E64,1,Assumptions!$B$5)</f>
-        <v>1100</v>
+        <v>260</v>
       </c>
       <c r="G64" s="21" t="inlineStr">
         <is>
-          <t>Check-ins, inspections and owner meetings across Dubai. Rises directly with unit count — the most commonly underestimated line in this business.</t>
+          <t>Includes the dedicated 24/7 guest line.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="82" t="inlineStr">
         <is>
-          <t>Office consumables, printing &amp; courier</t>
+          <t>Transport, fuel, Salik &amp; parking</t>
         </is>
       </c>
       <c r="B65" s="83" t="inlineStr">
@@ -7217,28 +7217,28 @@
         </is>
       </c>
       <c r="C65" s="84" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D65" s="84" t="n">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="E65" s="84" t="n">
-        <v>380</v>
+        <v>2200</v>
       </c>
       <c r="F65" s="85">
         <f>INDEX(C65:E65,1,Assumptions!$B$5)</f>
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="G65" s="21" t="inlineStr">
         <is>
-          <t>Contracts, DET paperwork, key courier.</t>
+          <t>Check-ins, inspections and owner meetings across Dubai. Rises directly with unit count — the most commonly underestimated line in this business.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="82" t="inlineStr">
         <is>
-          <t>Bank charges &amp; account maintenance</t>
+          <t>Office consumables, printing &amp; courier</t>
         </is>
       </c>
       <c r="B66" s="83" t="inlineStr">
@@ -7250,158 +7250,158 @@
         <v>100</v>
       </c>
       <c r="D66" s="84" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="E66" s="84" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="F66" s="85">
         <f>INDEX(C66:E66,1,Assumptions!$B$5)</f>
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="G66" s="21" t="inlineStr">
         <is>
-          <t>Multi-currency corporate current account per the Business Profile.</t>
+          <t>Contracts, DET paperwork, key courier.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="82" t="inlineStr">
         <is>
+          <t>Bank charges &amp; account maintenance</t>
+        </is>
+      </c>
+      <c r="B67" s="83" t="inlineStr">
+        <is>
+          <t>AED/month</t>
+        </is>
+      </c>
+      <c r="C67" s="84" t="n">
+        <v>100</v>
+      </c>
+      <c r="D67" s="84" t="n">
+        <v>175</v>
+      </c>
+      <c r="E67" s="84" t="n">
+        <v>320</v>
+      </c>
+      <c r="F67" s="85">
+        <f>INDEX(C67:E67,1,Assumptions!$B$5)</f>
+        <v>175</v>
+      </c>
+      <c r="G67" s="21" t="inlineStr">
+        <is>
+          <t>Multi-currency corporate current account per the Business Profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="82" t="inlineStr">
+        <is>
           <t>Payment gateway / OTA payout fees</t>
         </is>
       </c>
-      <c r="B67" s="83" t="inlineStr">
+      <c r="B68" s="83" t="inlineStr">
         <is>
           <t>% of gross collections</t>
         </is>
       </c>
-      <c r="C67" s="91" t="n">
+      <c r="C68" s="91" t="n">
         <v>0.018</v>
       </c>
-      <c r="D67" s="91" t="n">
+      <c r="D68" s="91" t="n">
         <v>0.026</v>
       </c>
-      <c r="E67" s="91" t="n">
+      <c r="E68" s="91" t="n">
         <v>0.032</v>
       </c>
-      <c r="F67" s="92">
-        <f>INDEX(C67:E67,1,Assumptions!$B$5)</f>
+      <c r="F68" s="92">
+        <f>INDEX(C68:E68,1,Assumptions!$B$5)</f>
         <v>0.026</v>
       </c>
-      <c r="G67" s="21" t="inlineStr">
+      <c r="G68" s="21" t="inlineStr">
         <is>
           <t>Applied to gross booking revenue passing through Orizuru's account. Excluded if the OTA pays the owner directly — set to 0 in that case.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>10.  PROFESSIONAL, COMPLIANCE &amp; INSURANCE</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="82" t="inlineStr">
-        <is>
-          <t>Bookkeeping &amp; management accounts</t>
-        </is>
-      </c>
-      <c r="B69" s="83" t="inlineStr">
-        <is>
-          <t>AED/month</t>
-        </is>
-      </c>
-      <c r="C69" s="84" t="n">
-        <v>500</v>
-      </c>
-      <c r="D69" s="84" t="n">
-        <v>900</v>
-      </c>
-      <c r="E69" s="84" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F69" s="85">
-        <f>INDEX(C69:E69,1,Assumptions!$B$5)</f>
-        <v>900</v>
-      </c>
-      <c r="G69" s="21" t="inlineStr">
-        <is>
-          <t>Outsourced. Cheaper and more reliable than an in-house hire at this scale.</t>
-        </is>
-      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="82" t="inlineStr">
         <is>
-          <t>VAT return preparation &amp; filing</t>
+          <t>Bookkeeping &amp; management accounts</t>
         </is>
       </c>
       <c r="B70" s="83" t="inlineStr">
         <is>
-          <t>AED/quarter</t>
+          <t>AED/month</t>
         </is>
       </c>
       <c r="C70" s="84" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D70" s="84" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E70" s="84" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="F70" s="85">
         <f>INDEX(C70:E70,1,Assumptions!$B$5)</f>
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="G70" s="21" t="inlineStr">
         <is>
-          <t>Quarterly filing. Charged in Months 3, 6, 9 and 12.</t>
+          <t>Outsourced. Cheaper and more reliable than an in-house hire at this scale.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="82" t="inlineStr">
         <is>
-          <t>Corporate Tax compliance &amp; filing</t>
+          <t>VAT return preparation &amp; filing</t>
         </is>
       </c>
       <c r="B71" s="83" t="inlineStr">
         <is>
-          <t>AED/year</t>
+          <t>AED/quarter</t>
         </is>
       </c>
       <c r="C71" s="84" t="n">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="D71" s="84" t="n">
-        <v>4000</v>
+        <v>700</v>
       </c>
       <c r="E71" s="84" t="n">
-        <v>6500</v>
+        <v>1200</v>
       </c>
       <c r="F71" s="85">
         <f>INDEX(C71:E71,1,Assumptions!$B$5)</f>
-        <v>4000</v>
+        <v>700</v>
       </c>
       <c r="G71" s="21" t="inlineStr">
         <is>
-          <t>UAE Corporate Tax at 9% above AED 375,000 taxable profit. Compliance cost only — tax itself is not OPEX.</t>
+          <t>Quarterly filing. Charged in Months 3, 6, 9 and 12.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="82" t="inlineStr">
         <is>
-          <t>External audit</t>
+          <t>Corporate Tax compliance &amp; filing</t>
         </is>
       </c>
       <c r="B72" s="83" t="inlineStr">
@@ -7410,28 +7410,28 @@
         </is>
       </c>
       <c r="C72" s="84" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="D72" s="84" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="E72" s="84" t="n">
-        <v>10000</v>
+        <v>6500</v>
       </c>
       <c r="F72" s="85">
         <f>INDEX(C72:E72,1,Assumptions!$B$5)</f>
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G72" s="21" t="inlineStr">
         <is>
-          <t>Accrued monthly. Banks and owners increasingly require audited accounts.</t>
+          <t>UAE Corporate Tax at 9% above AED 375,000 taxable profit. Compliance cost only — tax itself is not OPEX.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="82" t="inlineStr">
         <is>
-          <t>PRO / government liaison services</t>
+          <t>External audit</t>
         </is>
       </c>
       <c r="B73" s="83" t="inlineStr">
@@ -7440,28 +7440,28 @@
         </is>
       </c>
       <c r="C73" s="84" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="D73" s="84" t="n">
-        <v>2800</v>
+        <v>6000</v>
       </c>
       <c r="E73" s="84" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="F73" s="85">
         <f>INDEX(C73:E73,1,Assumptions!$B$5)</f>
-        <v>2800</v>
+        <v>6000</v>
       </c>
       <c r="G73" s="21" t="inlineStr">
         <is>
-          <t>Visa renewals, licence amendments, DET filings.</t>
+          <t>Accrued monthly. Banks and owners increasingly require audited accounts.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="82" t="inlineStr">
         <is>
-          <t>Trade licence &amp; DET operator permit renewal</t>
+          <t>PRO / government liaison services</t>
         </is>
       </c>
       <c r="B74" s="83" t="inlineStr">
@@ -7470,28 +7470,28 @@
         </is>
       </c>
       <c r="C74" s="84" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
       <c r="D74" s="84" t="n">
-        <v>19000</v>
+        <v>2800</v>
       </c>
       <c r="E74" s="84" t="n">
-        <v>26000</v>
+        <v>4500</v>
       </c>
       <c r="F74" s="85">
         <f>INDEX(C74:E74,1,Assumptions!$B$5)</f>
-        <v>19000</v>
+        <v>2800</v>
       </c>
       <c r="G74" s="21" t="inlineStr">
         <is>
-          <t>Accrued monthly so the renewal does not blow a hole in one month's cash. Combines DED licence and DET operator permit renewal.</t>
+          <t>Visa renewals, licence amendments, DET filings.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="82" t="inlineStr">
         <is>
-          <t>Public liability &amp; professional indemnity insurance</t>
+          <t>Trade licence &amp; DET operator permit renewal</t>
         </is>
       </c>
       <c r="B75" s="83" t="inlineStr">
@@ -7500,28 +7500,28 @@
         </is>
       </c>
       <c r="C75" s="84" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="D75" s="84" t="n">
-        <v>5500</v>
+        <v>19000</v>
       </c>
       <c r="E75" s="84" t="n">
-        <v>9500</v>
+        <v>26000</v>
       </c>
       <c r="F75" s="85">
         <f>INDEX(C75:E75,1,Assumptions!$B$5)</f>
-        <v>5500</v>
+        <v>19000</v>
       </c>
       <c r="G75" s="21" t="inlineStr">
         <is>
-          <t>Essential — Orizuru holds keys to and controls access to other people's property.</t>
+          <t>Accrued monthly so the renewal does not blow a hole in one month's cash. Combines DED licence and DET operator permit renewal.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="82" t="inlineStr">
         <is>
-          <t>Legal, contract templates &amp; disputes</t>
+          <t>Public liability &amp; professional indemnity insurance</t>
         </is>
       </c>
       <c r="B76" s="83" t="inlineStr">
@@ -7530,62 +7530,92 @@
         </is>
       </c>
       <c r="C76" s="84" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D76" s="84" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="E76" s="84" t="n">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="F76" s="85">
         <f>INDEX(C76:E76,1,Assumptions!$B$5)</f>
+        <v>5500</v>
+      </c>
+      <c r="G76" s="21" t="inlineStr">
+        <is>
+          <t>Essential — Orizuru holds keys to and controls access to other people's property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="82" t="inlineStr">
+        <is>
+          <t>Legal, contract templates &amp; disputes</t>
+        </is>
+      </c>
+      <c r="B77" s="83" t="inlineStr">
+        <is>
+          <t>AED/year</t>
+        </is>
+      </c>
+      <c r="C77" s="84" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D77" s="84" t="n">
         <v>3000</v>
       </c>
-      <c r="G76" s="21" t="inlineStr">
+      <c r="E77" s="84" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F77" s="85">
+        <f>INDEX(C77:E77,1,Assumptions!$B$5)</f>
+        <v>3000</v>
+      </c>
+      <c r="G77" s="21" t="inlineStr">
         <is>
           <t>Management agreements, owner disputes, guest damage claims.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>11.  CONTINGENCY</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-    </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="82" t="inlineStr">
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="82" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B78" s="83" t="inlineStr">
+      <c r="B79" s="83" t="inlineStr">
         <is>
           <t>% of total OPEX</t>
         </is>
       </c>
-      <c r="C78" s="86" t="n">
+      <c r="C79" s="86" t="n">
         <v>0.03</v>
       </c>
-      <c r="D78" s="86" t="n">
+      <c r="D79" s="86" t="n">
         <v>0.05</v>
       </c>
-      <c r="E78" s="86" t="n">
+      <c r="E79" s="86" t="n">
         <v>0.08</v>
       </c>
-      <c r="F78" s="73">
-        <f>INDEX(C78:E78,1,Assumptions!$B$5)</f>
+      <c r="F79" s="73">
+        <f>INDEX(C79:E79,1,Assumptions!$B$5)</f>
         <v>0.05</v>
       </c>
-      <c r="G78" s="21" t="inlineStr">
+      <c r="G79" s="21" t="inlineStr">
         <is>
           <t>First-year UAE service company. 5% is the prudent base.</t>
         </is>
@@ -7593,17 +7623,17 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A45:G45"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A78:G78"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:G68"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A42:G42"/>
   </mergeCells>
@@ -10720,7 +10750,7 @@
       </c>
       <c r="D5" s="94">
         <f>IF($B$14=0,0,B5/$B$14)</f>
-        <v>0.09000781616627762</v>
+        <v>0.12658596634956165</v>
       </c>
       <c r="E5" s="17" t="n"/>
       <c r="F5" s="21" t="inlineStr">
@@ -10745,7 +10775,7 @@
       </c>
       <c r="D6" s="94">
         <f>IF($B$14=0,0,B6/$B$14)</f>
-        <v>0.010872336687063205</v>
+        <v>0.015290730345764428</v>
       </c>
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="21" t="inlineStr">
@@ -10770,7 +10800,7 @@
       </c>
       <c r="D7" s="94">
         <f>IF($B$14=0,0,B7/$B$14)</f>
-        <v>0.08028155826916515</v>
+        <v>0.11290706814591517</v>
       </c>
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="21" t="inlineStr">
@@ -10795,7 +10825,7 @@
       </c>
       <c r="D8" s="94">
         <f>IF($B$14=0,0,B8/$B$14)</f>
-        <v>0.10522516452008317</v>
+        <v>0.14798747155979577</v>
       </c>
       <c r="E8" s="17" t="n"/>
       <c r="F8" s="21" t="inlineStr">
@@ -10820,7 +10850,7 @@
       </c>
       <c r="D9" s="94">
         <f>IF($B$14=0,0,B9/$B$14)</f>
-        <v>0.09853913981206333</v>
+        <v>0.1385843226472813</v>
       </c>
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="21" t="inlineStr">
@@ -10837,20 +10867,20 @@
       </c>
       <c r="B10" s="15">
         <f>'OPEX Monthly'!O63</f>
-        <v>196420.00000000003</v>
+        <v>0</v>
       </c>
       <c r="C10" s="22">
         <f>B10/12</f>
-        <v>16368.333333333336</v>
+        <v>0</v>
       </c>
       <c r="D10" s="94">
         <f>IF($B$14=0,0,B10/$B$14)</f>
-        <v>0.27519901701971067</v>
+        <v>0</v>
       </c>
       <c r="E10" s="17" t="n"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>Fully variable. Much of it is re-chargeable to owners or guests — set the relevant assumptions to 0 if you recharge.</t>
+          <t>NIL in the Base case: permit renewals, housekeeping, consumables, maintenance and linen are all re-charged to the owner. Rates retained on Assumptions to price recovery risk.</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10900,7 @@
       </c>
       <c r="D11" s="94">
         <f>IF($B$14=0,0,B11/$B$14)</f>
-        <v>0.2167380143095909</v>
+        <v>0.30481787198769816</v>
       </c>
       <c r="E11" s="17" t="n"/>
       <c r="F11" s="21" t="inlineStr">
@@ -10895,7 +10925,7 @@
       </c>
       <c r="D12" s="94">
         <f>IF($B$14=0,0,B12/$B$14)</f>
-        <v>0.0755179055969983</v>
+        <v>0.10620752134493593</v>
       </c>
       <c r="E12" s="17" t="n"/>
       <c r="F12" s="21" t="inlineStr">
@@ -10912,11 +10942,11 @@
       </c>
       <c r="B13" s="15">
         <f>'OPEX Monthly'!O88</f>
-        <v>33987.5245</v>
+        <v>24166.5245</v>
       </c>
       <c r="C13" s="22">
         <f>B13/12</f>
-        <v>2832.293708333333</v>
+        <v>2013.8770416666666</v>
       </c>
       <c r="D13" s="94">
         <f>IF($B$14=0,0,B13/$B$14)</f>
@@ -10937,11 +10967,11 @@
       </c>
       <c r="B14" s="19">
         <f>SUM(B5:B13)</f>
-        <v>713738.0145</v>
+        <v>507497.0145</v>
       </c>
       <c r="C14" s="19">
         <f>B14/12</f>
-        <v>59478.16787500001</v>
+        <v>42291.417875</v>
       </c>
       <c r="D14" s="95">
         <f>IF($B$14=0,0,SUM(D5:D13))</f>
@@ -11027,7 +11057,7 @@
       </c>
       <c r="B20" s="22">
         <f>B14</f>
-        <v>713738.0145</v>
+        <v>507497.0145</v>
       </c>
       <c r="C20" s="17" t="n"/>
       <c r="D20" s="17" t="n"/>
@@ -11042,7 +11072,7 @@
       </c>
       <c r="B21" s="15">
         <f>'OPEX Monthly'!O94</f>
-        <v>157293.9855</v>
+        <v>363534.98549999995</v>
       </c>
       <c r="C21" s="17" t="n"/>
       <c r="D21" s="17" t="n"/>
@@ -11061,7 +11091,7 @@
       </c>
       <c r="B22" s="15">
         <f>MIN('OPEX Monthly'!C95:N95)</f>
-        <v>-44429.97149999999</v>
+        <v>-37759.226624999996</v>
       </c>
       <c r="C22" s="17" t="n"/>
       <c r="D22" s="17" t="n"/>
@@ -11080,7 +11110,7 @@
       </c>
       <c r="B23" s="26">
         <f>IF(B19=0,0,B20/B19)</f>
-        <v>0.819416524880831</v>
+        <v>0.5826387715950734</v>
       </c>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="n"/>
@@ -11099,7 +11129,7 @@
       </c>
       <c r="B24" s="15">
         <f>'OPEX Monthly'!N89</f>
-        <v>113117.816875</v>
+        <v>73109.316875</v>
       </c>
       <c r="C24" s="17" t="n"/>
       <c r="D24" s="17" t="n"/>
@@ -11118,7 +11148,7 @@
       </c>
       <c r="B25" s="15">
         <f>'OPEX Monthly'!N97</f>
-        <v>1593.2086883802817</v>
+        <v>1029.7086883802817</v>
       </c>
       <c r="C25" s="17" t="n"/>
       <c r="D25" s="17" t="n"/>
@@ -12513,7 +12543,7 @@
       </c>
       <c r="P24" s="114">
         <f>IF($O$89=0,0,$O24/$O$89)</f>
-        <v>0.09000781616627765</v>
+        <v>0.12658596634956165</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -12847,7 +12877,7 @@
       </c>
       <c r="P31" s="114">
         <f>IF($O$89=0,0,$O31/$O$89)</f>
-        <v>0.010872336687063206</v>
+        <v>0.015290730345764428</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -13319,7 +13349,7 @@
       </c>
       <c r="P40" s="114">
         <f>IF($O$89=0,0,$O40/$O$89)</f>
-        <v>0.08028155826916517</v>
+        <v>0.11290706814591517</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -13470,7 +13500,7 @@
       </c>
       <c r="P44" s="114">
         <f>IF($O$89=0,0,$O44/$O$89)</f>
-        <v>0.10522516452008318</v>
+        <v>0.14798747155979577</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -14064,13 +14094,13 @@
       </c>
       <c r="P55" s="114">
         <f>IF($O$89=0,0,$O55/$O$89)</f>
-        <v>0.09853913981206334</v>
+        <v>0.1385843226472813</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>F.  UNIT OPERATIONS  —  variable with portfolio size</t>
+          <t>F.  UNIT OPERATIONS  —  re-charged to the owner, nil to Orizuru</t>
         </is>
       </c>
       <c r="B57" s="5" t="n"/>
@@ -14097,125 +14127,125 @@
       </c>
       <c r="B58" s="108" t="inlineStr">
         <is>
-          <t>Per live unit, 1/12 of annual</t>
+          <t>Owner-borne x share</t>
         </is>
       </c>
       <c r="C58" s="22">
-        <f>C9*Assumptions!$F$55/12</f>
+        <f>C9*Assumptions!$F$56/12*Assumptions!$F$55</f>
         <v>0</v>
       </c>
       <c r="D58" s="22">
-        <f>D9*Assumptions!$F$55/12</f>
-        <v>380</v>
+        <f>D9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="E58" s="22">
-        <f>E9*Assumptions!$F$55/12</f>
-        <v>886.6666666666666</v>
+        <f>E9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="F58" s="22">
-        <f>F9*Assumptions!$F$55/12</f>
-        <v>1520</v>
+        <f>F9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="G58" s="22">
-        <f>G9*Assumptions!$F$55/12</f>
-        <v>2280</v>
+        <f>G9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="H58" s="22">
-        <f>H9*Assumptions!$F$55/12</f>
-        <v>3040</v>
+        <f>H9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="I58" s="22">
-        <f>I9*Assumptions!$F$55/12</f>
-        <v>3926.6666666666665</v>
+        <f>I9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="J58" s="22">
-        <f>J9*Assumptions!$F$55/12</f>
-        <v>4813.333333333333</v>
+        <f>J9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="K58" s="22">
-        <f>K9*Assumptions!$F$55/12</f>
-        <v>5826.666666666667</v>
+        <f>K9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="L58" s="22">
-        <f>L9*Assumptions!$F$55/12</f>
-        <v>6840</v>
+        <f>L9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="M58" s="22">
-        <f>M9*Assumptions!$F$55/12</f>
-        <v>7853.333333333333</v>
+        <f>M9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="N58" s="22">
-        <f>N9*Assumptions!$F$55/12</f>
-        <v>8993.333333333334</v>
+        <f>N9*Assumptions!$F$56/12*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="O58" s="85">
         <f>SUM(C58:N58)</f>
-        <v>46360.00000000001</v>
+        <v>0</v>
       </c>
       <c r="P58" s="17" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="36" t="inlineStr">
         <is>
-          <t>Housekeeping &amp; laundry — net of guest recharge</t>
+          <t>Housekeeping &amp; laundry</t>
         </is>
       </c>
       <c r="B59" s="108" t="inlineStr">
         <is>
-          <t>Per live unit</t>
+          <t>Owner-borne x share</t>
         </is>
       </c>
       <c r="C59" s="22">
-        <f>C9*Assumptions!$F$56</f>
+        <f>C9*Assumptions!$F$57*Assumptions!$F$55</f>
         <v>0</v>
       </c>
       <c r="D59" s="22">
-        <f>D9*Assumptions!$F$56</f>
-        <v>540</v>
+        <f>D9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="E59" s="22">
-        <f>E9*Assumptions!$F$56</f>
-        <v>1260</v>
+        <f>E9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="F59" s="22">
-        <f>F9*Assumptions!$F$56</f>
-        <v>2160</v>
+        <f>F9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="G59" s="22">
-        <f>G9*Assumptions!$F$56</f>
-        <v>3240</v>
+        <f>G9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="H59" s="22">
-        <f>H9*Assumptions!$F$56</f>
-        <v>4320</v>
+        <f>H9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="I59" s="22">
-        <f>I9*Assumptions!$F$56</f>
-        <v>5580</v>
+        <f>I9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="J59" s="22">
-        <f>J9*Assumptions!$F$56</f>
-        <v>6840</v>
+        <f>J9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="K59" s="22">
-        <f>K9*Assumptions!$F$56</f>
-        <v>8280</v>
+        <f>K9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="L59" s="22">
-        <f>L9*Assumptions!$F$56</f>
-        <v>9720</v>
+        <f>L9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="M59" s="22">
-        <f>M9*Assumptions!$F$56</f>
-        <v>11160</v>
+        <f>M9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="N59" s="22">
-        <f>N9*Assumptions!$F$56</f>
-        <v>12780</v>
+        <f>N9*Assumptions!$F$57*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="O59" s="85">
         <f>SUM(C59:N59)</f>
-        <v>65880</v>
+        <v>0</v>
       </c>
       <c r="P59" s="17" t="n"/>
     </row>
@@ -14227,125 +14257,125 @@
       </c>
       <c r="B60" s="108" t="inlineStr">
         <is>
-          <t>Per live unit</t>
+          <t>Owner-borne x share</t>
         </is>
       </c>
       <c r="C60" s="22">
-        <f>C9*Assumptions!$F$57</f>
+        <f>C9*Assumptions!$F$58*Assumptions!$F$55</f>
         <v>0</v>
       </c>
       <c r="D60" s="22">
-        <f>D9*Assumptions!$F$57</f>
-        <v>300</v>
+        <f>D9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="E60" s="22">
-        <f>E9*Assumptions!$F$57</f>
-        <v>700</v>
+        <f>E9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="F60" s="22">
-        <f>F9*Assumptions!$F$57</f>
-        <v>1200</v>
+        <f>F9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="G60" s="22">
-        <f>G9*Assumptions!$F$57</f>
-        <v>1800</v>
+        <f>G9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="H60" s="22">
-        <f>H9*Assumptions!$F$57</f>
-        <v>2400</v>
+        <f>H9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="I60" s="22">
-        <f>I9*Assumptions!$F$57</f>
-        <v>3100</v>
+        <f>I9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="J60" s="22">
-        <f>J9*Assumptions!$F$57</f>
-        <v>3800</v>
+        <f>J9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="K60" s="22">
-        <f>K9*Assumptions!$F$57</f>
-        <v>4600</v>
+        <f>K9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="L60" s="22">
-        <f>L9*Assumptions!$F$57</f>
-        <v>5400</v>
+        <f>L9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="M60" s="22">
-        <f>M9*Assumptions!$F$57</f>
-        <v>6200</v>
+        <f>M9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="N60" s="22">
-        <f>N9*Assumptions!$F$57</f>
-        <v>7100</v>
+        <f>N9*Assumptions!$F$58*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="O60" s="85">
         <f>SUM(C60:N60)</f>
-        <v>36600</v>
+        <v>0</v>
       </c>
       <c r="P60" s="17" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="36" t="inlineStr">
         <is>
-          <t>Maintenance coordination &amp; petty repairs</t>
+          <t>Maintenance &amp; petty repairs</t>
         </is>
       </c>
       <c r="B61" s="108" t="inlineStr">
         <is>
-          <t>Per live unit</t>
+          <t>Owner-borne x share</t>
         </is>
       </c>
       <c r="C61" s="22">
-        <f>C9*Assumptions!$F$58</f>
+        <f>C9*Assumptions!$F$59*Assumptions!$F$55</f>
         <v>0</v>
       </c>
       <c r="D61" s="22">
-        <f>D9*Assumptions!$F$58</f>
-        <v>270</v>
+        <f>D9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="E61" s="22">
-        <f>E9*Assumptions!$F$58</f>
-        <v>630</v>
+        <f>E9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="F61" s="22">
-        <f>F9*Assumptions!$F$58</f>
-        <v>1080</v>
+        <f>F9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="G61" s="22">
-        <f>G9*Assumptions!$F$58</f>
-        <v>1620</v>
+        <f>G9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="H61" s="22">
-        <f>H9*Assumptions!$F$58</f>
-        <v>2160</v>
+        <f>H9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="I61" s="22">
-        <f>I9*Assumptions!$F$58</f>
-        <v>2790</v>
+        <f>I9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="J61" s="22">
-        <f>J9*Assumptions!$F$58</f>
-        <v>3420</v>
+        <f>J9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="K61" s="22">
-        <f>K9*Assumptions!$F$58</f>
-        <v>4140</v>
+        <f>K9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="L61" s="22">
-        <f>L9*Assumptions!$F$58</f>
-        <v>4860</v>
+        <f>L9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="M61" s="22">
-        <f>M9*Assumptions!$F$58</f>
-        <v>5580</v>
+        <f>M9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="N61" s="22">
-        <f>N9*Assumptions!$F$58</f>
-        <v>6390</v>
+        <f>N9*Assumptions!$F$59*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="O61" s="85">
         <f>SUM(C61:N61)</f>
-        <v>32940</v>
+        <v>0</v>
       </c>
       <c r="P61" s="17" t="n"/>
     </row>
@@ -14357,60 +14387,60 @@
       </c>
       <c r="B62" s="108" t="inlineStr">
         <is>
-          <t>Per live unit</t>
+          <t>Owner-borne x share</t>
         </is>
       </c>
       <c r="C62" s="22">
-        <f>C9*Assumptions!$F$59</f>
+        <f>C9*Assumptions!$F$60*Assumptions!$F$55</f>
         <v>0</v>
       </c>
       <c r="D62" s="22">
-        <f>D9*Assumptions!$F$59</f>
-        <v>120</v>
+        <f>D9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="E62" s="22">
-        <f>E9*Assumptions!$F$59</f>
-        <v>280</v>
+        <f>E9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="F62" s="22">
-        <f>F9*Assumptions!$F$59</f>
-        <v>480</v>
+        <f>F9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="G62" s="22">
-        <f>G9*Assumptions!$F$59</f>
-        <v>720</v>
+        <f>G9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="H62" s="22">
-        <f>H9*Assumptions!$F$59</f>
-        <v>960</v>
+        <f>H9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="I62" s="22">
-        <f>I9*Assumptions!$F$59</f>
-        <v>1240</v>
+        <f>I9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="J62" s="22">
-        <f>J9*Assumptions!$F$59</f>
-        <v>1520</v>
+        <f>J9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="K62" s="22">
-        <f>K9*Assumptions!$F$59</f>
-        <v>1840</v>
+        <f>K9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="L62" s="22">
-        <f>L9*Assumptions!$F$59</f>
-        <v>2160</v>
+        <f>L9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="M62" s="22">
-        <f>M9*Assumptions!$F$59</f>
-        <v>2480</v>
+        <f>M9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="N62" s="22">
-        <f>N9*Assumptions!$F$59</f>
-        <v>2840</v>
+        <f>N9*Assumptions!$F$60*Assumptions!$F$55</f>
+        <v>0</v>
       </c>
       <c r="O62" s="85">
         <f>SUM(C62:N62)</f>
-        <v>14640</v>
+        <v>0</v>
       </c>
       <c r="P62" s="17" t="n"/>
     </row>
@@ -14427,55 +14457,55 @@
       </c>
       <c r="D63" s="31">
         <f>SUM(D58:D62)</f>
-        <v>1610</v>
+        <v>0</v>
       </c>
       <c r="E63" s="31">
         <f>SUM(E58:E62)</f>
-        <v>3756.6666666666665</v>
+        <v>0</v>
       </c>
       <c r="F63" s="31">
         <f>SUM(F58:F62)</f>
-        <v>6440</v>
+        <v>0</v>
       </c>
       <c r="G63" s="31">
         <f>SUM(G58:G62)</f>
-        <v>9660</v>
+        <v>0</v>
       </c>
       <c r="H63" s="31">
         <f>SUM(H58:H62)</f>
-        <v>12880</v>
+        <v>0</v>
       </c>
       <c r="I63" s="31">
         <f>SUM(I58:I62)</f>
-        <v>16636.666666666664</v>
+        <v>0</v>
       </c>
       <c r="J63" s="31">
         <f>SUM(J58:J62)</f>
-        <v>20393.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K63" s="31">
         <f>SUM(K58:K62)</f>
-        <v>24686.666666666668</v>
+        <v>0</v>
       </c>
       <c r="L63" s="31">
         <f>SUM(L58:L62)</f>
-        <v>28980</v>
+        <v>0</v>
       </c>
       <c r="M63" s="31">
         <f>SUM(M58:M62)</f>
-        <v>33273.33333333333</v>
+        <v>0</v>
       </c>
       <c r="N63" s="31">
         <f>SUM(N58:N62)</f>
-        <v>38103.333333333336</v>
+        <v>0</v>
       </c>
       <c r="O63" s="31">
         <f>SUM(C63:N63)</f>
-        <v>196420.00000000003</v>
+        <v>0</v>
       </c>
       <c r="P63" s="114">
         <f>IF($O$89=0,0,$O63/$O$89)</f>
-        <v>0.2751990170197107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -14508,51 +14538,51 @@
       </c>
       <c r="B66" s="108" t="inlineStr"/>
       <c r="C66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="D66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="E66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="F66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="G66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="H66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="I66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="J66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="K66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="L66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="M66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="N66" s="22">
-        <f>Assumptions!$F$61</f>
+        <f>Assumptions!$F$62</f>
         <v>2500</v>
       </c>
       <c r="O66" s="85">
@@ -14569,51 +14599,51 @@
       </c>
       <c r="B67" s="108" t="inlineStr"/>
       <c r="C67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="D67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="E67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="F67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="G67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="H67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="I67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="J67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="K67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="L67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="M67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="N67" s="22">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$63</f>
         <v>520</v>
       </c>
       <c r="O67" s="85">
@@ -14630,51 +14660,51 @@
       </c>
       <c r="B68" s="108" t="inlineStr"/>
       <c r="C68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="D68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="E68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="F68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="G68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="H68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="I68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="J68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="K68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="L68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="M68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="N68" s="22">
-        <f>Assumptions!$F$63</f>
+        <f>Assumptions!$F$64</f>
         <v>260</v>
       </c>
       <c r="O68" s="85">
@@ -14691,51 +14721,51 @@
       </c>
       <c r="B69" s="108" t="inlineStr"/>
       <c r="C69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="D69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="E69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="F69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="G69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="H69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="I69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="J69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="K69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="L69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="M69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="N69" s="22">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$65</f>
         <v>1100</v>
       </c>
       <c r="O69" s="85">
@@ -14752,51 +14782,51 @@
       </c>
       <c r="B70" s="108" t="inlineStr"/>
       <c r="C70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="D70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="E70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="F70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="G70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="H70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="I70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="J70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="K70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="L70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="M70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="N70" s="22">
-        <f>Assumptions!$F$65</f>
+        <f>Assumptions!$F$66</f>
         <v>200</v>
       </c>
       <c r="O70" s="85">
@@ -14813,51 +14843,51 @@
       </c>
       <c r="B71" s="108" t="inlineStr"/>
       <c r="C71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="D71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="E71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="F71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="G71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="H71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="I71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="J71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="K71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="L71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="M71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="N71" s="22">
-        <f>Assumptions!$F$66</f>
+        <f>Assumptions!$F$67</f>
         <v>175</v>
       </c>
       <c r="O71" s="85">
@@ -14878,51 +14908,51 @@
         </is>
       </c>
       <c r="C72" s="22">
-        <f>C11*Assumptions!$F$67</f>
+        <f>C11*Assumptions!$F$68</f>
         <v>0</v>
       </c>
       <c r="D72" s="22">
-        <f>D11*Assumptions!$F$67</f>
+        <f>D11*Assumptions!$F$68</f>
         <v>800.28</v>
       </c>
       <c r="E72" s="22">
-        <f>E11*Assumptions!$F$67</f>
+        <f>E11*Assumptions!$F$68</f>
         <v>1867.32</v>
       </c>
       <c r="F72" s="22">
-        <f>F11*Assumptions!$F$67</f>
+        <f>F11*Assumptions!$F$68</f>
         <v>3201.12</v>
       </c>
       <c r="G72" s="22">
-        <f>G11*Assumptions!$F$67</f>
+        <f>G11*Assumptions!$F$68</f>
         <v>4801.679999999999</v>
       </c>
       <c r="H72" s="22">
-        <f>H11*Assumptions!$F$67</f>
+        <f>H11*Assumptions!$F$68</f>
         <v>6402.24</v>
       </c>
       <c r="I72" s="22">
-        <f>I11*Assumptions!$F$67</f>
+        <f>I11*Assumptions!$F$68</f>
         <v>8269.56</v>
       </c>
       <c r="J72" s="22">
-        <f>J11*Assumptions!$F$67</f>
+        <f>J11*Assumptions!$F$68</f>
         <v>10136.88</v>
       </c>
       <c r="K72" s="22">
-        <f>K11*Assumptions!$F$67</f>
+        <f>K11*Assumptions!$F$68</f>
         <v>12270.96</v>
       </c>
       <c r="L72" s="22">
-        <f>L11*Assumptions!$F$67</f>
+        <f>L11*Assumptions!$F$68</f>
         <v>14405.039999999999</v>
       </c>
       <c r="M72" s="22">
-        <f>M11*Assumptions!$F$67</f>
+        <f>M11*Assumptions!$F$68</f>
         <v>16539.12</v>
       </c>
       <c r="N72" s="22">
-        <f>N11*Assumptions!$F$67</f>
+        <f>N11*Assumptions!$F$68</f>
         <v>18939.96</v>
       </c>
       <c r="O72" s="85">
@@ -14992,7 +15022,7 @@
       </c>
       <c r="P73" s="114">
         <f>IF($O$89=0,0,$O73/$O$89)</f>
-        <v>0.21673801430959094</v>
+        <v>0.30481787198769816</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -15025,51 +15055,51 @@
       </c>
       <c r="B76" s="108" t="inlineStr"/>
       <c r="C76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="D76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="E76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="F76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="G76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="H76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="I76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="J76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="K76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="L76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="M76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="N76" s="22">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$70</f>
         <v>900</v>
       </c>
       <c r="O76" s="85">
@@ -15090,51 +15120,51 @@
         </is>
       </c>
       <c r="C77" s="22">
-        <f>IF(MOD(C6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(C6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="D77" s="22">
-        <f>IF(MOD(D6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(D6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="E77" s="22">
-        <f>IF(MOD(E6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(E6,3)=0,Assumptions!$F$71,0)</f>
         <v>700</v>
       </c>
       <c r="F77" s="22">
-        <f>IF(MOD(F6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(F6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="G77" s="22">
-        <f>IF(MOD(G6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(G6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="H77" s="22">
-        <f>IF(MOD(H6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(H6,3)=0,Assumptions!$F$71,0)</f>
         <v>700</v>
       </c>
       <c r="I77" s="22">
-        <f>IF(MOD(I6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(I6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="J77" s="22">
-        <f>IF(MOD(J6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(J6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="K77" s="22">
-        <f>IF(MOD(K6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(K6,3)=0,Assumptions!$F$71,0)</f>
         <v>700</v>
       </c>
       <c r="L77" s="22">
-        <f>IF(MOD(L6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(L6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="M77" s="22">
-        <f>IF(MOD(M6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(M6,3)=0,Assumptions!$F$71,0)</f>
         <v>0</v>
       </c>
       <c r="N77" s="22">
-        <f>IF(MOD(N6,3)=0,Assumptions!$F$70,0)</f>
+        <f>IF(MOD(N6,3)=0,Assumptions!$F$71,0)</f>
         <v>700</v>
       </c>
       <c r="O77" s="85">
@@ -15155,51 +15185,51 @@
         </is>
       </c>
       <c r="C78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="D78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="E78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="F78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="G78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="H78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="I78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="J78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="K78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="L78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="M78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="N78" s="22">
-        <f>Assumptions!$F$71/12</f>
+        <f>Assumptions!$F$72/12</f>
         <v>333.3333333333333</v>
       </c>
       <c r="O78" s="85">
@@ -15220,51 +15250,51 @@
         </is>
       </c>
       <c r="C79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="D79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="E79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="F79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="G79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="H79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="I79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="J79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="K79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="L79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="M79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="N79" s="22">
-        <f>Assumptions!$F$72/12</f>
+        <f>Assumptions!$F$73/12</f>
         <v>500</v>
       </c>
       <c r="O79" s="85">
@@ -15285,51 +15315,51 @@
         </is>
       </c>
       <c r="C80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="D80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="E80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="F80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="G80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="H80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="I80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="J80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="K80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="L80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="M80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="N80" s="22">
-        <f>Assumptions!$F$73/12</f>
+        <f>Assumptions!$F$74/12</f>
         <v>233.33333333333334</v>
       </c>
       <c r="O80" s="85">
@@ -15350,51 +15380,51 @@
         </is>
       </c>
       <c r="C81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="D81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="E81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="F81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="G81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="H81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="I81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="J81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="K81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="L81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="M81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="N81" s="22">
-        <f>Assumptions!$F$74/12</f>
+        <f>Assumptions!$F$75/12</f>
         <v>1583.3333333333333</v>
       </c>
       <c r="O81" s="85">
@@ -15415,51 +15445,51 @@
         </is>
       </c>
       <c r="C82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="D82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="E82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="F82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="G82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="H82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="I82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="J82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="K82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="L82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="M82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="N82" s="22">
-        <f>Assumptions!$F$75/12</f>
+        <f>Assumptions!$F$76/12</f>
         <v>458.3333333333333</v>
       </c>
       <c r="O82" s="85">
@@ -15480,51 +15510,51 @@
         </is>
       </c>
       <c r="C83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="D83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="E83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="F83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="G83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="H83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="I83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="J83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="K83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="L83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="M83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="N83" s="22">
-        <f>Assumptions!$F$76/12</f>
+        <f>Assumptions!$F$77/12</f>
         <v>250</v>
       </c>
       <c r="O83" s="85">
@@ -15594,7 +15624,7 @@
       </c>
       <c r="P84" s="114">
         <f>IF($O$89=0,0,$O84/$O$89)</f>
-        <v>0.07551790559699831</v>
+        <v>0.10620752134493593</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15632,51 +15662,51 @@
       </c>
       <c r="D87" s="25">
         <f>D24+D31+D40+D44+D55+D63+D73+D84</f>
-        <v>26686.64083333333</v>
+        <v>25076.64083333333</v>
       </c>
       <c r="E87" s="25">
         <f>E24+E31+E40+E44+E55+E63+E73+E84</f>
-        <v>28041.1475</v>
+        <v>24284.48083333333</v>
       </c>
       <c r="F87" s="25">
         <f>F24+F31+F40+F44+F55+F63+F73+F84</f>
-        <v>33009.28083333333</v>
+        <v>26569.28083333333</v>
       </c>
       <c r="G87" s="25">
         <f>G24+G31+G40+G44+G55+G63+G73+G84</f>
-        <v>39811.04083333334</v>
+        <v>30151.040833333333</v>
       </c>
       <c r="H87" s="25">
         <f>H24+H31+H40+H44+H55+H63+H73+H84</f>
-        <v>47312.800833333335</v>
+        <v>34432.800833333335</v>
       </c>
       <c r="I87" s="25">
         <f>I24+I31+I40+I44+I55+I63+I73+I84</f>
-        <v>54548.1875</v>
+        <v>37911.520833333336</v>
       </c>
       <c r="J87" s="25">
         <f>J24+J31+J40+J44+J55+J63+J73+J84</f>
-        <v>66052.57416666666</v>
+        <v>45659.24083333333</v>
       </c>
       <c r="K87" s="25">
         <f>K24+K31+K40+K44+K55+K63+K73+K84</f>
-        <v>75821.58750000001</v>
+        <v>51134.92083333334</v>
       </c>
       <c r="L87" s="25">
         <f>L24+L31+L40+L44+L55+L63+L73+L84</f>
-        <v>84190.60083333333</v>
+        <v>55210.60083333334</v>
       </c>
       <c r="M87" s="25">
         <f>M24+M31+M40+M44+M55+M63+M73+M84</f>
-        <v>93259.61416666665</v>
+        <v>59986.28083333333</v>
       </c>
       <c r="N87" s="25">
         <f>N24+N31+N40+N44+N55+N63+N73+N84</f>
-        <v>107731.25416666667</v>
+        <v>69627.92083333334</v>
       </c>
       <c r="O87" s="25">
         <f>SUM(C87:N87)</f>
-        <v>679750.49</v>
+        <v>483330.49</v>
       </c>
       <c r="P87" s="17" t="n"/>
     </row>
@@ -15692,56 +15722,56 @@
         </is>
       </c>
       <c r="C88" s="22">
-        <f>C87*Assumptions!$F$78</f>
+        <f>C87*Assumptions!$F$79</f>
         <v>1164.2880416666665</v>
       </c>
       <c r="D88" s="22">
-        <f>D87*Assumptions!$F$78</f>
-        <v>1334.3320416666666</v>
+        <f>D87*Assumptions!$F$79</f>
+        <v>1253.8320416666666</v>
       </c>
       <c r="E88" s="22">
-        <f>E87*Assumptions!$F$78</f>
-        <v>1402.057375</v>
+        <f>E87*Assumptions!$F$79</f>
+        <v>1214.2240416666666</v>
       </c>
       <c r="F88" s="22">
-        <f>F87*Assumptions!$F$78</f>
-        <v>1650.4640416666666</v>
+        <f>F87*Assumptions!$F$79</f>
+        <v>1328.4640416666666</v>
       </c>
       <c r="G88" s="22">
-        <f>G87*Assumptions!$F$78</f>
-        <v>1990.552041666667</v>
+        <f>G87*Assumptions!$F$79</f>
+        <v>1507.5520416666668</v>
       </c>
       <c r="H88" s="22">
-        <f>H87*Assumptions!$F$78</f>
-        <v>2365.640041666667</v>
+        <f>H87*Assumptions!$F$79</f>
+        <v>1721.6400416666668</v>
       </c>
       <c r="I88" s="22">
-        <f>I87*Assumptions!$F$78</f>
-        <v>2727.409375</v>
+        <f>I87*Assumptions!$F$79</f>
+        <v>1895.576041666667</v>
       </c>
       <c r="J88" s="22">
-        <f>J87*Assumptions!$F$78</f>
-        <v>3302.628708333333</v>
+        <f>J87*Assumptions!$F$79</f>
+        <v>2282.9620416666667</v>
       </c>
       <c r="K88" s="22">
-        <f>K87*Assumptions!$F$78</f>
-        <v>3791.0793750000007</v>
+        <f>K87*Assumptions!$F$79</f>
+        <v>2556.746041666667</v>
       </c>
       <c r="L88" s="22">
-        <f>L87*Assumptions!$F$78</f>
-        <v>4209.530041666667</v>
+        <f>L87*Assumptions!$F$79</f>
+        <v>2760.530041666667</v>
       </c>
       <c r="M88" s="22">
-        <f>M87*Assumptions!$F$78</f>
-        <v>4662.980708333333</v>
+        <f>M87*Assumptions!$F$79</f>
+        <v>2999.3140416666665</v>
       </c>
       <c r="N88" s="22">
-        <f>N87*Assumptions!$F$78</f>
-        <v>5386.562708333334</v>
+        <f>N87*Assumptions!$F$79</f>
+        <v>3481.396041666667</v>
       </c>
       <c r="O88" s="25">
         <f>SUM(C88:N88)</f>
-        <v>33987.5245</v>
+        <v>24166.5245</v>
       </c>
       <c r="P88" s="17" t="n"/>
     </row>
@@ -15758,51 +15788,51 @@
       </c>
       <c r="D89" s="19">
         <f>D87+D88</f>
-        <v>28020.972875</v>
+        <v>26330.472875</v>
       </c>
       <c r="E89" s="19">
         <f>E87+E88</f>
-        <v>29443.204875</v>
+        <v>25498.704875</v>
       </c>
       <c r="F89" s="19">
         <f>F87+F88</f>
-        <v>34659.744875</v>
+        <v>27897.744874999997</v>
       </c>
       <c r="G89" s="19">
         <f>G87+G88</f>
-        <v>41801.59287500001</v>
+        <v>31658.592875</v>
       </c>
       <c r="H89" s="19">
         <f>H87+H88</f>
-        <v>49678.440875</v>
+        <v>36154.440875</v>
       </c>
       <c r="I89" s="19">
         <f>I87+I88</f>
-        <v>57275.596875</v>
+        <v>39807.096875</v>
       </c>
       <c r="J89" s="19">
         <f>J87+J88</f>
-        <v>69355.20287499999</v>
+        <v>47942.202874999995</v>
       </c>
       <c r="K89" s="19">
         <f>K87+K88</f>
-        <v>79612.66687500001</v>
+        <v>53691.666875</v>
       </c>
       <c r="L89" s="19">
         <f>L87+L88</f>
-        <v>88400.130875</v>
+        <v>57971.130875</v>
       </c>
       <c r="M89" s="19">
         <f>M87+M88</f>
-        <v>97922.59487499998</v>
+        <v>62985.594874999995</v>
       </c>
       <c r="N89" s="19">
         <f>N87+N88</f>
-        <v>113117.816875</v>
+        <v>73109.316875</v>
       </c>
       <c r="O89" s="19">
         <f>SUM(C89:N89)</f>
-        <v>713738.0144999999</v>
+        <v>507497.0145</v>
       </c>
       <c r="P89" s="5" t="n"/>
     </row>
@@ -15906,51 +15936,51 @@
       </c>
       <c r="D93" s="22">
         <f>D89</f>
-        <v>28020.972875</v>
+        <v>26330.472875</v>
       </c>
       <c r="E93" s="22">
         <f>E89</f>
-        <v>29443.204875</v>
+        <v>25498.704875</v>
       </c>
       <c r="F93" s="22">
         <f>F89</f>
-        <v>34659.744875</v>
+        <v>27897.744874999997</v>
       </c>
       <c r="G93" s="22">
         <f>G89</f>
-        <v>41801.59287500001</v>
+        <v>31658.592875</v>
       </c>
       <c r="H93" s="22">
         <f>H89</f>
-        <v>49678.440875</v>
+        <v>36154.440875</v>
       </c>
       <c r="I93" s="22">
         <f>I89</f>
-        <v>57275.596875</v>
+        <v>39807.096875</v>
       </c>
       <c r="J93" s="22">
         <f>J89</f>
-        <v>69355.20287499999</v>
+        <v>47942.202874999995</v>
       </c>
       <c r="K93" s="22">
         <f>K89</f>
-        <v>79612.66687500001</v>
+        <v>53691.666875</v>
       </c>
       <c r="L93" s="22">
         <f>L89</f>
-        <v>88400.130875</v>
+        <v>57971.130875</v>
       </c>
       <c r="M93" s="22">
         <f>M89</f>
-        <v>97922.59487499998</v>
+        <v>62985.594874999995</v>
       </c>
       <c r="N93" s="22">
         <f>N89</f>
-        <v>113117.816875</v>
+        <v>73109.316875</v>
       </c>
       <c r="O93" s="74">
         <f>SUM(C93:N93)</f>
-        <v>713738.0144999999</v>
+        <v>507497.0145</v>
       </c>
       <c r="P93" s="17" t="n"/>
     </row>
@@ -15971,51 +16001,51 @@
       </c>
       <c r="D94" s="25">
         <f>D92-D93</f>
-        <v>-15864.972875</v>
+        <v>-14174.472875</v>
       </c>
       <c r="E94" s="25">
         <f>E92-E93</f>
-        <v>-7579.204874999999</v>
+        <v>-3634.7048749999994</v>
       </c>
       <c r="F94" s="25">
         <f>F92-F93</f>
-        <v>-1035.7448749999967</v>
+        <v>5726.255125000003</v>
       </c>
       <c r="G94" s="25">
         <f>G92-G93</f>
-        <v>4134.407124999991</v>
+        <v>14277.407125000002</v>
       </c>
       <c r="H94" s="25">
         <f>H92-H93</f>
-        <v>10069.559125</v>
+        <v>23593.559125</v>
       </c>
       <c r="I94" s="25">
         <f>I92-I93</f>
-        <v>16836.403124999997</v>
+        <v>34304.903125</v>
       </c>
       <c r="J94" s="25">
         <f>J92-J93</f>
-        <v>20620.797125000012</v>
+        <v>42033.797125000005</v>
       </c>
       <c r="K94" s="25">
         <f>K92-K93</f>
-        <v>26779.33312499999</v>
+        <v>52700.333125</v>
       </c>
       <c r="L94" s="25">
         <f>L92-L93</f>
-        <v>34407.869125</v>
+        <v>64836.869125</v>
       </c>
       <c r="M94" s="25">
         <f>M92-M93</f>
-        <v>42801.40512500002</v>
+        <v>77738.405125</v>
       </c>
       <c r="N94" s="25">
         <f>N92-N93</f>
-        <v>46074.183124999996</v>
+        <v>86082.683125</v>
       </c>
       <c r="O94" s="85">
         <f>SUM(C94:N94)</f>
-        <v>157293.9855</v>
+        <v>363534.98549999995</v>
       </c>
       <c r="P94" s="17" t="n"/>
     </row>
@@ -16036,51 +16066,51 @@
       </c>
       <c r="D95" s="25">
         <f>C95+D94</f>
-        <v>-35815.02175</v>
+        <v>-34124.52175</v>
       </c>
       <c r="E95" s="25">
         <f>D95+E94</f>
-        <v>-43394.226624999996</v>
+        <v>-37759.226624999996</v>
       </c>
       <c r="F95" s="25">
         <f>E95+F94</f>
-        <v>-44429.97149999999</v>
+        <v>-32032.971499999992</v>
       </c>
       <c r="G95" s="25">
         <f>F95+G94</f>
-        <v>-40295.564375</v>
+        <v>-17755.56437499999</v>
       </c>
       <c r="H95" s="25">
         <f>G95+H94</f>
-        <v>-30226.005250000002</v>
+        <v>5837.994750000009</v>
       </c>
       <c r="I95" s="25">
         <f>H95+I94</f>
-        <v>-13389.602125000005</v>
+        <v>40142.89787500001</v>
       </c>
       <c r="J95" s="25">
         <f>I95+J94</f>
-        <v>7231.195000000007</v>
+        <v>82176.695</v>
       </c>
       <c r="K95" s="25">
         <f>J95+K94</f>
-        <v>34010.528125</v>
+        <v>134877.028125</v>
       </c>
       <c r="L95" s="25">
         <f>K95+L94</f>
-        <v>68418.39725</v>
+        <v>199713.89725</v>
       </c>
       <c r="M95" s="25">
         <f>L95+M94</f>
-        <v>111219.80237500001</v>
+        <v>277452.302375</v>
       </c>
       <c r="N95" s="25">
         <f>M95+N94</f>
-        <v>157293.9855</v>
+        <v>363534.9855</v>
       </c>
       <c r="O95" s="85">
         <f>N95</f>
-        <v>157293.9855</v>
+        <v>363534.9855</v>
       </c>
       <c r="P95" s="17" t="n"/>
     </row>
@@ -16101,51 +16131,51 @@
       </c>
       <c r="D96" s="26">
         <f>IF(D92=0,0,D93/D92)</f>
-        <v>2.3051145833333333</v>
+        <v>2.166047455988812</v>
       </c>
       <c r="E96" s="26">
         <f>IF(E92=0,0,E93/E92)</f>
-        <v>1.34665225370472</v>
+        <v>1.166241532885108</v>
       </c>
       <c r="F96" s="26">
         <f>IF(F92=0,0,F93/F92)</f>
-        <v>1.0308037376576253</v>
+        <v>0.8296973850523435</v>
       </c>
       <c r="G96" s="26">
         <f>IF(G92=0,0,G93/G92)</f>
-        <v>0.9099963617859633</v>
+        <v>0.689189151754615</v>
       </c>
       <c r="H96" s="26">
         <f>IF(H92=0,0,H93/H92)</f>
-        <v>0.8314661725078664</v>
+        <v>0.6051154996819977</v>
       </c>
       <c r="I96" s="26">
         <f>IF(I92=0,0,I93/I92)</f>
-        <v>0.7728248714783031</v>
+        <v>0.5371208019618956</v>
       </c>
       <c r="J96" s="26">
         <f>IF(J92=0,0,J93/J92)</f>
-        <v>0.7708189169889748</v>
+        <v>0.5328332319174002</v>
       </c>
       <c r="K96" s="26">
         <f>IF(K92=0,0,K93/K92)</f>
-        <v>0.7482956131570043</v>
+        <v>0.5046588735525228</v>
       </c>
       <c r="L96" s="26">
         <f>IF(L92=0,0,L93/L92)</f>
-        <v>0.7198238785339718</v>
+        <v>0.47204686075011404</v>
       </c>
       <c r="M96" s="26">
         <f>IF(M92=0,0,M93/M92)</f>
-        <v>0.6958485750476108</v>
+        <v>0.44758246549984365</v>
       </c>
       <c r="N96" s="26">
         <f>IF(N92=0,0,N93/N92)</f>
-        <v>0.710574757996633</v>
+        <v>0.45925245536836024</v>
       </c>
       <c r="O96" s="73">
         <f>IF(O92=0,0,O93/O92)</f>
-        <v>0.8194165248808309</v>
+        <v>0.5826387715950734</v>
       </c>
       <c r="P96" s="17" t="n"/>
     </row>
@@ -16166,51 +16196,51 @@
       </c>
       <c r="D97" s="22">
         <f>IF(D9=0,0,D93/D9)</f>
-        <v>9340.324291666666</v>
+        <v>8776.824291666666</v>
       </c>
       <c r="E97" s="22">
         <f>IF(E9=0,0,E93/E9)</f>
-        <v>4206.172125</v>
+        <v>3642.672125</v>
       </c>
       <c r="F97" s="22">
         <f>IF(F9=0,0,F93/F9)</f>
-        <v>2888.3120729166662</v>
+        <v>2324.8120729166662</v>
       </c>
       <c r="G97" s="22">
         <f>IF(G9=0,0,G93/G9)</f>
-        <v>2322.3107152777784</v>
+        <v>1758.8107152777777</v>
       </c>
       <c r="H97" s="22">
         <f>IF(H9=0,0,H93/H9)</f>
-        <v>2069.9350364583333</v>
+        <v>1506.4350364583333</v>
       </c>
       <c r="I97" s="22">
         <f>IF(I9=0,0,I93/I9)</f>
-        <v>1847.5998991935485</v>
+        <v>1284.0998991935485</v>
       </c>
       <c r="J97" s="22">
         <f>IF(J9=0,0,J93/J9)</f>
-        <v>1825.1369177631575</v>
+        <v>1261.6369177631577</v>
       </c>
       <c r="K97" s="22">
         <f>IF(K9=0,0,K93/K9)</f>
-        <v>1730.710149456522</v>
+        <v>1167.2101494565218</v>
       </c>
       <c r="L97" s="22">
         <f>IF(L9=0,0,L93/L9)</f>
-        <v>1637.0394606481482</v>
+        <v>1073.5394606481482</v>
       </c>
       <c r="M97" s="22">
         <f>IF(M9=0,0,M93/M9)</f>
-        <v>1579.3966915322578</v>
+        <v>1015.8966915322579</v>
       </c>
       <c r="N97" s="22">
         <f>IF(N9=0,0,N93/N9)</f>
-        <v>1593.2086883802817</v>
+        <v>1029.7086883802817</v>
       </c>
       <c r="O97" s="85">
         <f>IF(N9=0,0,N93/N9)</f>
-        <v>1593.2086883802817</v>
+        <v>1029.7086883802817</v>
       </c>
       <c r="P97" s="17" t="n"/>
     </row>
